--- a/study_methods/행정학_공부방법.xlsx
+++ b/study_methods/행정학_공부방법.xlsx
@@ -17,14 +17,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기타" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체'!$A$1:$H$293</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기출 위주'!$A$1:$H$88</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'이론_개념 정리 위주'!$A$1:$H$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'암기 위주'!$A$1:$H$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'기본서 위주'!$A$1:$H$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'단권화 전략'!$A$1:$H$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'모의고사 활용'!$A$1:$H$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'기타'!$A$1:$H$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체'!$A$1:$I$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기출 위주'!$A$1:$I$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'이론_개념 정리 위주'!$A$1:$I$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'암기 위주'!$A$1:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'기본서 위주'!$A$1:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'단권화 전략'!$A$1:$I$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'모의고사 활용'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'기타'!$A$1:$I$100</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H293"/>
+  <dimension ref="A1:I293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -486,6 +486,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -529,6 +530,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -563,6 +569,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41696&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -593,6 +604,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41542&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=3</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -631,6 +647,11 @@
           <t>- 2024.07 ~ 2025.06 (약 1년)   2. 기본 베이스 지거국 영어영문학과 / 토익 900점대 후반 / 한능검 1급   3. 하루 루틴 수험 생활 초기에는 집 근처 도서관에서 공부를 했는데 집중이 잘 안 돼, 해커스 스파르타 독서실을 다녔습니다. 월요일부터 토요일까지는 아침 7시에 기상 후 아침 8시부터 밤 10시까지 독서실에서 공부했고 일요일은 쉬었습니다.   4. 공부 방향 공부 방향을 잘 설정하는 것이 단기 합격의 지름길이라고 생각합니다. 국어, 영어는 제가 자신 있어 하는 과목이었고 기초도 어느 정도 있었기 때문에 공부 시간을 최대한 줄이고 남는 시간을 한국사, 행정법, 행정학에 할애했습니다. 한국사 또한 제가 자신 있어 하는 과목으로 기초도 있었지만 국어, 영어와는 다르게 암기 과목이라 휘발성이 강해 공부량을 줄이지는 않았습니다. 공부 시간을 대략적으로 따져본다면 행정학 &gt; 행정법 &gt; 한국사 &gt; 영어 &gt; 국어 순으로 시간을 투자했습니다.   5. 과목별 공부법 국어 95점 국어는 학창 시절 열심히 했었기 때문에 자신 있는 과목이었습니다. 인사혁신처 예시 문제를 풀어보니 별다른 공부 없이도 충분히 풀 수 있는 난도여서 국어에 많은 시간을</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41522&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -665,6 +686,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41520&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -703,6 +729,11 @@
           <t>2025년 공무원 시험 합격수기:  강사님들 덕분입니다!! 안녕하십니까. 이번 공무원 시험에 최종 합격한 수험생입니다. 제가 합격이라는 결실을 맺을 수 있었던 가장 큰 비결은, 바로 해커스공무원의 훌륭한 강사진과 커리큘럼을 믿고 흔들림 없이 따라간 덕분입니다. 특히, 제가 선택했던 국어 신민숙, 영어 비비안, 행정법 김대현, 행정학 서현 선생님의 강의는 저의 수험 생활을 관통하는 핵심이었습니다.(한국사는 독학으로 공부했습니다)</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41463&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=6</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -737,6 +768,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41453&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=6</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -775,6 +811,11 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41440&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -817,6 +858,11 @@
           <t>저는 보통 10~11시 사이에 기상 후, 새벽 3-4시까지 공부하는 편이었습니다. 전공과목 '행정학' &amp; '행정법'은 2일에 1번 반복, 남은 공용과목을 골고루 돌아가면서 공부할 수 있게 1주일 단위로 계획을 주로 짰습니다. 예를 들어,  월 화 수 목 금 토 일 행정학 행정법 행정학 행정법 행정학 행정법 복습DAY 국어 영어 한국사 국어 영어 한국사 이런 식으로 짜서 진행했고 후반 문제풀이 과정으로 넘어갔을 때는 국어와 영어 비중을 줄이고 암기 과목인 '한국사' 에 시간을 더 투자했습니다.</t>
         </is>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41438&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -855,6 +901,11 @@
           <t>4년제 지방 국립대에서 공과대학을 졸업하였고, 1년 반 수험생활을 하였습니다. ■인강 국어: 조은정 국어 쌩기초 입문특강/ 조은정 국어 신유형대비 문제풀이 영어: 비비안 선생님의 기출해설강의 한국사: 이중석 선생님의 기본강의(올인원) 행정법,행정학은 기출문제와 여러 선생님들의 모의고사 문제로 해결 ■교재</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41429&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -889,6 +940,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41397&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -931,6 +987,11 @@
           <t>행정학: 서현쌤 기본,심화,기출 강의 다 수강함. 이거는 내용은 괜찮은데 외울게 진짜 너무 많고 방대해서 너무 막막해서 속이 답답했다. 하지만 정공법으로 그냥 강의도 공부다 생각하고 배속으로 듣고 그날 배운건 당일 복습하고 하니 기출까지 완강하니까 대충 뭔지 알겠어서 기출강의 끝나고는 서현쌤 기출문제집 무지성 회독함. 5회독 정도. 이것도 wox회독 나만의 변형버전으로 했음. 국가직때 65점 받고 충격 먹어서 지방직까지 열심히했더니 지방직은 95점 받음.</t>
         </is>
       </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41396&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -965,6 +1026,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41345&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=11</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -999,6 +1065,11 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41344&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=11</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1035,6 +1106,11 @@
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>처음 시험 공부를 시작했을 때, 국어와 한국사, 영어는 비교적 자신 있는 과목들이었습니다. 특히 국어와 한국사는 기본기가 있었고, 영어도 평소에 꾸준히 공부해왔기 때문에 큰 장벽 없이 진입할 수 있었습니다. 하지만 선택과목인 행정법과 행정학은 전혀 다른 이야기였습니다. 생소한 용어와 복잡한 이론들 앞에서 처음에는 막막함을 느꼈고, 두 과목 모두 기본 강의와 심화 강의를 각각 두 번씩 반복하며 이해를 다졌습니다. 이후에는 기출문제 풀이 강의로 넘어가 실전 적용 능력을 키우는 데 집중했습니다. 공부는 결국 반복과 정리, 그리고 지속적인 피드백이 핵심이라는 것을 느꼈습니다.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41324&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=12</t>
         </is>
       </c>
     </row>
@@ -1067,6 +1143,11 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41298&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=13</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -1101,6 +1182,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41289&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=14</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1135,6 +1221,11 @@
           <t>- 행정법 &amp; 행정학 정말 무슨 자신감인지는 모르겠지만 단 한번도 공부하지 않았었지만 고등학교를 문과로 나오고 선택과목도 법정이었어서 걱정은 많이 없었던 것 같네요.. (근거 없는 자신감이 최고조였던...ㅎㅎ, 마지막까지 발목잡은 행정법...)</t>
         </is>
       </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41258&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -1173,6 +1264,11 @@
           <t>4년정도 공시생활을 하였네요. 직장 특성상 야근이 잦은편이라, 공부시간확보가 상당히 어려웠습니다. 퇴근 후 밥먹고 씻고하면 공부시간 3~4시간정도,새벽2시까지는해야 5~6시간 겨우 확보되더군요. 야근하는 날에는 거의 공부를 못했구요.(회식있는날도 패스..) 국어는 신민숙선생님 영어는 김송희 선생님 한국사는 이중석 선생님 행정법은 함수민 선생님 행정학은 서현 선생님 강의로 시작했던것 같습니다.</t>
         </is>
       </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41250&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=16</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1215,6 +1311,11 @@
           <t>약 6개월 간 강의를 수강하며 준비를 한 끝에 지방직에 최종합격하였습니다. 대학교 학과가 행정학과라 어느정도 베이스는 있었지만 강의를 수강하며 저만의 방법으로 암기하고, 학습한 끝에 최종합격이라는 결과를 얻어낸 것 같습니다. 지금부터 6개월간 강의를 수강하며 어떻게 지내왔는지를 소개해보려고 합니다.  - 매일 아침 6시 기상. 기상 후 30분 간 스트레칭 &amp; 걸으며 하루를 시작. 23시 30분 취침. 우선 주말도 예외없이 칼같이 기상시간을 지켰으며 저는 무엇보다 건강이 가장 중요하다고 생각했기에 기상 후 간단하게 조깅을 하거나 스트레칭을 하며 하루를 시작했고 적정한 취침시간을 지켜 강의를 수강하며 피로를 느끼지 않을 수 있도록 하였습니다.  - 오전에는 국어, 영어/ 점심식사 후 한국사/ 이른 저녁 행정학, 행정법 저는 머리가 가장 활발하게 활동하는 시간을 오전과 저녁시간이라고 생각하여 저에게 가장 힘들었던 과목인 국어와 행정법을 활발한 시간에 수강하여 고득점을 얻기 위해 노력하였습니다. 한국사는 제가 가장 좋아하는 과목이었습니다. 그래서 식곤증이 올 수 있는 시간에 수강하여도 재미있고 졸지 않고 수강할 수 있었습니다. 저는 제가 좋아하는 과목이나 잘하는 과</t>
         </is>
       </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41240&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=16</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -1253,6 +1354,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41233&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1291,6 +1397,11 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41227&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -1329,6 +1440,11 @@
           <t>◆행정학- 서현 선생님 개인적으로 행정학이 제일 어려웠습니다... 처음 접하는 개념들이 많은데 또 이것들이 두루뭉실하게 둥둥 떠다니는 느낌이랄까요... 시간이 없다고 판단해서 심화를 듣지 않고 기본이론에서 바로 기출문제풀이로 넘어갔는데, 고득점을 위해서라면 꼭... 심화를 들으시길... 시험 전에는 행정학 단권화 특강으로 전체적인 개념을 쓱 흝을 수 있어서 좋았습니다. 행정학도 외우지 않으면 못푸는 과목이라고 생각해서 시험이 가까워질 수록 개념과 법령등을 외우는 데 시간을 썼습니다.</t>
         </is>
       </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41205&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=18</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1367,6 +1483,11 @@
           <t>행정학/서현 선생님 강의가 좀 길고 방대합니다. 그러나 처음 듣는 사람이 듣기에는 어려움이 없습니다. 기본강의 들을떄는 이해가 되지 않더라도 귀에 익힌다는 생각으로 끝까지 완강을 하는것을 추천드립니다. 서현 선생님의 기출 문제집이 좋습니다. 기본강의 후 기출문제집을 계속 회독하면서 부족한 개념을 계속 암기하는 방법으로 공부하였습니다.</t>
         </is>
       </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41179&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -1405,6 +1526,11 @@
           <t>행정학 기본문제집보고 기겁했던게 엊그제 같네요. 강사님의 강의노트 덕분에 용기내서 시작했습니다. 요약이 정말 잘 되어있어요. 모든 강의 들을 때 강의노트 옆에 두고 들었습니다. 중요도도 체크해주셔서 복습할 때 그나마 순조로웠어요. 심화강의는 문제풀이 위주로 하시는데, 전 인강 들으면서 풀었습니다. 심화문제 단원별로 끝날 때마다 강의노트와 심화문제 번갈아보면서 복습했습니다. 신경향이론도 특강 강추합니다. 문제 여기서 많이 나왔어요. 배속 1.8</t>
         </is>
       </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41174&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1439,6 +1565,11 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41173&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -1477,6 +1608,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41137&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -1515,6 +1651,11 @@
           <t>1. 기본 베이스 / 공무원 준비 계기 &lt;기본 베이스&gt; 국어- 고등학교때까지 꽤 잘하는 편이었음 (모의고사 1~2등급) 영어-못함 (절대평가 모의고사 3~4등급) 한국사 - 한능검 1급 행정법, 행정학 – 노베이스 &lt;공무원 준비 계기&gt; 대학교 졸업반이 되어서 전공을 살릴지 취업을 할지 고민하다가 졸업하기 전에 9급 공무원 시험을 봐보자 라는 생각으로 보게되었습니다.   2. 하루 루틴 (공부&amp;생활습관) 저는 3~4개월 정도 본격적인 공무원 수험생 생활을 했습니다. 제게 주어진 시간이 얼마 없어서 압도적인 공부시간이 필요했습니다. 그래서 저는 순공시간 12시간을 꼭 채우려고 노력했습니다. 매일 아침 8시반쯤에 일어나 준비를 하고 밥을 먹고 10시에 도서관에 도착해서 밤 10시에 집에 갔습니다. 집에 가서 얼른 씻고 다시 12시까지 공부하고 잠에 들었습니다. 점심식사와 저녁식사시간은 30분을 넘기지 않으려고 노력했습니다. 그렇게 공부시간 12시간을 채우려 노력했던 것 같습니다. 10시에 도서관에 도착해서 하루에 내가 했으면 좋겠는 (할 수 있는 x) 공부를 쭉 작성하고 (불가능한 정도의 공부 양이어야 함) 그 불가능한 공부 양을 최대한 하려고 노력했습니다. 그렇</t>
         </is>
       </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41127&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -1553,6 +1694,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41020&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=25</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="55" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -1591,6 +1737,11 @@
           <t>법과목 또한 너무 생소했고 또 남은 기간이 많지 않았기에 시작은 막막했습니다. 하지만 김대현 선생님은 컴팩트한 교재와 강의를 사용하시기에 현재 제 상황에 딱 맞는 선생님이였습니다. 행정법에서 가장 중요한 건 흐름을 알고 문제가 풀리는 그 순간까지 참고 버티고 공부해 나아가는 것 같습니다.. 처음에는 아무리 풀어보려해도 안 풀리는게 행정법이지만 나중에 효자과목이 된다는 이유를 알게 됐습니다. 국가직땐 행정법에 빠져서 많이 공부하고 풀다보니 국가직땐 65점 나와서 만족했지만 지방직까지 가는 과정중에 국가직 면접과 행정학 빵구 메우기 때문에 집중을 못해서 지방직땐 성적이 비록 떨어졌습니다. 그래서 행정법 또한 기본강의 듣고 회독하고 문제 풀며 어느정도 성적이 올라왔을때 계속 감을 유지하고 부족한 부분을 채워나가는 것이라 생각합니다. 단원만 보고 한 부분만 본다면 어려운 과목이지만 기본강의가 끝나고 여러번 회독 했을때 과목 전체를 보면 행정학보다 훨씬 효자과목이라 생각합니다(기출회독 필수)</t>
         </is>
       </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40996&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=26</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -1625,6 +1776,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40995&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=27</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -1663,6 +1819,11 @@
           <t>행정학: 서현 수강 강의 내역: 기본 강의, 기출 강의, 법령 특강 전시리즈, 하프 전시리즈, 실전 동형 강의</t>
         </is>
       </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40785&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="55" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -1701,6 +1862,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40721&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=31</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="55" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -1731,6 +1897,11 @@
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40692&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=31</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="55" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -1761,6 +1932,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40687&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="55" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -1791,6 +1967,11 @@
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40683&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="55" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -1825,6 +2006,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40670&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="55" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -1859,6 +2045,11 @@
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40575&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=35</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="55" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -1901,6 +2092,11 @@
           <t>- 수강한 선생님&amp;강의&amp;교재 추천 국어: 신민숙 선생님(신민숙 쉬운국어 논리 강화 150제 교재)  영어: 비비안 선생님(해커스공무원 비비안 올인원 영문법, 2025 해커스공무원 영어 구조 독해 007) 한국사: 이중석 선생님(해커스공무원 이중석 맵핑 한국사 올인원 블랭크노트) 행정법: 홍대겸 선생님(2025 해커스 홍대겸 행정법총론 단원별 기출문제집) 행정학: 서현 선생님(2025 해커스공무원 현 행정학 단원별 기출문제집)  모두 큰 도움이 되었습니다.  교재는 위의 교재 등을 위주로 활용했습니다.</t>
         </is>
       </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40541&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=36</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="55" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -1939,6 +2135,11 @@
           <t>행정학 (90점) 김만희 선생님 기본이론을 먼저 수강하였고, 이후에 기출 문제집 회독하다가 서현 선생님 모의고사 수강했습니다. 행정학은 하나의 문제집을 여러 번 회독하는 것보다는 여러 문제집을 보며 다양한 표현들을 익히는 게 중요한 것 같습니다. 처음보는 단어나 문제가 등장해도 어떻게 풀어나갈지 요령을 익히는 게 필요해요.</t>
         </is>
       </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40498&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=38</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="55" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -1979,6 +2180,11 @@
       <c r="H41" s="3" t="inlineStr">
         <is>
           <t>행정학 - 서현 행정학은 가장 쉬운 과목이면서도 가장 어려운 과목이었습니다. 서현 쌤의 수업을 들으면 해당 개념이 확실히 쉽게 다가왔는데 행정학 문제의 지문 자체가 귀에 걸면 귀걸이... 코에 걸면 코걸이...라서 많이 헤맸던 것 같습니다. 그럴 때 질문을 많이 했는데 그때마다 친절하게 설명해주셔서 감사했습니다. '강의노트'가 도움이 많이 되었는데 이미 체계적으로 정리되어 있는 강의노트에 수업을 들으며 저만의 방식으로 필기한 내용까지 더해지니 든든한 무기를 하나 손에 넣은 느낌이었습니다. 감사합니다!</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40478&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=39</t>
         </is>
       </c>
     </row>
@@ -2015,6 +2221,11 @@
           <t>암기과목(한국사, 행정법, 행정학)의 경우 그날 배운 부분을 복습한 뒤 기출문제에서 어떤 식으로 문제가 출제되는지, 중요한 부분이 무엇인지 확인하세요.</t>
         </is>
       </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=44</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="55" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -2049,6 +2260,11 @@
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
         </is>
       </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="55" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -2083,6 +2299,11 @@
           <t>(행정학) 행정학의 경우에는 대부분의 수험생들이 그렇듯 시험 직전까지도 가장 자신이 없었습니다. 개념의 범위가 너무 넓고 항상 불의타 문제가 나오기 때문에 대비가 어렵다고 느꼈습니다. 행정학의 경우에는 여러 이론들에 대해서 묻기 때문에 이론 간의 비교에 집중하면서 공부하는게 큰 도움이 됐습니다. 간단하게 비유하자면 단순하게 (a 이론의 특성은 키가 작다) 이런 식으로 외우면  혼동이 생길 때가 많습니다. 왜냐하면 a 이론이 b이론과 비교했을 때는 키가 작았지만, 또 다른 c이론과 비교했을 때는 키가 큰 경우가 있기 때문입니다. 행정학은 법 과목의 판례들처럼 딱 정해진 것이 아니어서 어떤 대상과 비교하냐에 따라서 해당 이론의 특성이 아 다르고 어 다르기 때문에  (a 이론은 b 이론과 비교했을 때는 키가 작다) 이런 식으로 유사한 그룹의 개념들끼리 비교를 잡으면서 개념을 유연성 있게 정리하는게 많은 도움이 됐습니다.   (헌법)) 헌법의 경우 처음 기본 강의를 들을 때는 상대적으로 재밌다고 느꼈습니다. 왜냐하면 다양한 판례들이 나오고 아무래도 판례들이 우리 생활과 밀접해 있다 보니 이러한 경우도 있구나 하면서 상대적으로 즐겁게 기본강의를 들었습니다. 하지만 기</t>
         </is>
       </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="55" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -2117,6 +2338,11 @@
           <t>(4) 행정학 [강의] 서현쌤 기본+심화이론 23년 1회 수강 [강의] 서현쌤 법령특강 1회 수강 [강의] 마니쌤 기본이론 24년 1회 수강 [교재] 서현쌤 기본서 [교재] 마니쌤 기본서 [교재] 서현쌤 기출문제집 9회독 [교재] 마니쌤 OX 3회독 [교재] 경간 소간 국회직 등등 각종 시행처 최신기출</t>
         </is>
       </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39626&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="55" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -2159,6 +2385,11 @@
           <t>행정법과 헌법은 황남기 선생님에게 의지했습니다. 교재가 너무 완벽해서 내용이 그 안에서 벗어나지 않았습니다. 역시 기본강의만 들었고, 곧바로 기출회독을 시작했고 이후 모의고사로 법과목을 공부했습니다. 특히 시험을 앞두고 나오는 최신판례 강의에서 그대로 문제가 나왔습니다.  법은 공부하면 하는만큼 나옵니다. 정말 정직합니다. 법에서 최대한 점수 챙긴다고 생각하고 메인으로 공부하세요. 절대 배신 안합니다. 저도 이번에 행정학에서 많이 까먹었지만 헌법 100점, 행정법 92점으로 선방해서 안정적으로 합격할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39624&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="55" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
@@ -2197,6 +2428,11 @@
           <t>7월 28일부터 8월 11일까지 일요일 동안 송상호 선생님의 신경향 흐름의 주요테마 및 단원별 문제풀이를 수강하였습니다. 9월 22일에 해커스공무원이 시행한 2024 대비 제9회 7급 합격예측 모의고사를 응시하였기에 실전연습을 할 수 있었습니다. 10월 11일까지 헌법은 8회, 행정법은 8회, 행정학은 9회, 경제학(16년-23년 국가직7급, 지방직7급, 국회직8급)은 9회 가량 기출문제집 회독을 할 수 있었습니다. 신동욱 선생님의 헌법, 함수민 선생님의 행정법, 송상호 선생님의 행정학, 김종국 선생님의 경제학 기출문제풀이 강의 덕분에 기출문제집 회독을 효율적으로 할 수 있었고, 2차 합격을 할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39621&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="55" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -2239,6 +2475,11 @@
           <t>저는 해커스와 1년 8개월을 함께하여 25년 서울 지방직 9급 일반행정직에 합격하였습니다. 저는 9급 기적의 합격패스 2년짜리를 등록하여 공부를 하였습니다.   저는 올빼미 형이라서 아침 10시 정도에 일어나서 새벽 2시까지 집에서 공부하는 생활 패턴을 반복하였습니다. 초기에는 월~금요일은 저녁식사 전까지 공통과목인 국어, 영어를 공부하였고, 식사 후에 행정법과 행정학을 공부하였으며, 토요일과 일요일에는 진도가 느렸던 과목과 한국사를 조금 공부하였습니다.   국어는 신민숙 선생님 강의를 들었는데, 문법이 약해서 비문학보다는 문법에 시간을 많이 할애하였습니다. 한자는 공부하다가 싫증이 날 때 틈틈이 보았습니다.   영어는 비비안 선생님 강의를 들었으며, 단어와 문법, 독해를 2:3:5 정도의 비율로 공부하였습니다. 단어는 특별하게 외우기보다는 독해를 하면서 모르는 단어를 암기노트에 적고 파생 단어를 공부하는 식으로 외웠습니다.   한국사는 제가 한능검을 공부하였던 경험이 있기에 어느 정도 기초가 되어 있어서, 바로 이중석 선생님의 기출문제풀이로 공부하였습니다.   행정법은 함수민 선생님의 기본과 심화 강의를 3번 들은 후 기출문제 풀이를 들었습니다.. 행정법은</t>
         </is>
       </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39255&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=50</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="55" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
@@ -2277,6 +2518,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39251&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=50</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="55" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -2319,6 +2565,11 @@
           <t>행정학 : 송상호 선생님 저에게 가장 고통스러웠던 과목이었습니다. 행정법과 마찬가지로 쌩노베였지만 행정법과는 다르게 썰을 듣는다는 느낌이 아니라 학자들의 견해를 외워야 한다는 느낌이어서 가장 어렵게 다가왔습니다. 교재는 공무원 명품 행정학을 기본서로 이용했고 시험전까지 총 4회독을 하였습니다. 2회독을 한 이후 해커스 기출문제집을 2회독하고 마지막으로 기본서 2회독으로 마무리하였습니다.</t>
         </is>
       </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39106&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=52</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="55" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
@@ -2353,6 +2604,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39065&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=52</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="55" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -2382,6 +2638,11 @@
         <v/>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39039&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=53</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="55" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
@@ -2424,6 +2685,11 @@
           <t>행정학은 서현쌤 기출문제집이랑 필기노트 보면서 독학으로 공부했습니다. 처음엔 진짜 어려운 과목이긴 한데, 필기노트만 보지 말고, 기출문제도 같이 풀면서 몇 번 회독하다보면 자주 나오는 선지들이 보여서 나름 할만한 과목입니다! 다만, 이번 지방직 시험은 유달리 어렵게 나와서 75점을 받았습니다ㅜ 이렇게 3년 간 공시생 생활의 결실을 국가직 일반행정(교육부), 지방직 일반행정(제주시) 2관왕으로 아름답게 마무리 할 수 있다는 것에 대해 안도감과 동시에 기쁨이 느껴집니다. 공시는 열심히 회독하다보시면 충분히 합격할 수 있으니 이 글을 읽는 여러분들도 꼭 합격하기를 간절히 바랍니다!</t>
         </is>
       </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38968&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=56</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="55" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -2462,6 +2728,11 @@
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38957&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=56</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="55" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
@@ -2492,6 +2763,11 @@
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38932&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=57</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="55" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -2526,6 +2802,11 @@
           <t>안녕하세요. 저는 2024년도 지방직 일반행정에 합격한 합격생입니다. 저는 대학생 4학년 1년간 학교에 다니면서 시험을 준비했습니다. (총 수험기간: 23년 9월~24년 6월) 전 행정학과 학생이고 거의 모든 수업은 아침수업으로 들었고 점심부터는 수험 공부를 시작했습니다. 저는 이동시간이 길어 시간이 부족하다고 생각했기 때문에 점심시간이나 이동시간에는 단어를 외우거나 가벼운 강의를 들으면서 다녔습니다.</t>
         </is>
       </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38915&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=58</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="55" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
@@ -2560,6 +2841,11 @@
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38899&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=59</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="55" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -2594,6 +2880,11 @@
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38878&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=60</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="55" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
@@ -2628,6 +2919,11 @@
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38875&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=60</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="55" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -2662,6 +2958,11 @@
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38846&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=61</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="55" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
@@ -2696,6 +2997,11 @@
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38788&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=64</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="55" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -2730,6 +3036,11 @@
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38776&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=64</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="55" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
@@ -2768,6 +3079,11 @@
           <t>공무원 준비는 부모님 권유로 시작하게 되었습니다. 하루 루틴은 국가직까지 3개월정도가 있었는데 하루에 3~4시간정도 공부했습니다. 국어,영어는 안하고 행정법,행정학,한국사 압축강의(행정법,한국사), 기본강의(행정학)만 봤습니다. 1,4,7,14복습법을 이때만 적용했습니다. 그래도 까먹었는데 깊은 잠재의식속에 남아있지 않았을까 생각됩니다.</t>
         </is>
       </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38757&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=65</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="55" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -2806,6 +3122,11 @@
           <t>9급, 4지 선지선다이기 때문에 모르는 부분이 있더라도 깊이 파고드는 방법은 적합하지 않다고 생각했어요. 반복, 암기, 반복, 암기, 모르는 부분은 넘어가기 식의 공부방법이 더 잘 맞았어요. 그리고 특히 행정학같은 경우는 흐름을 타기 때문에 기출문제에 집착할 필요 없다고 생각합니다. 책이나 강의는 무조건 최신판으로 구해서 보시고, 작년 기출, 국가직, 바뀐 출제 기조 꼭 참고하셔서 흐름을 찾아가며 공부하는 방식을 추천드립니다.</t>
         </is>
       </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38731&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=66</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="55" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
@@ -2840,6 +3161,11 @@
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38725&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=66</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="55" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -2882,6 +3208,11 @@
           <t>2. 베이스 국어 수능 3등급, 영어 수능 2등급 토익 800점대, 한국사 수능1 한국사검정시험1급, 행정법 행정학 처음 공부함</t>
         </is>
       </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38678&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=68</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="55" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
@@ -2920,6 +3251,11 @@
           <t>행정법, 행정학, 한국사는 반복이 답인 것 같습니다. 처음에 강의 들을 때는 포기하고 싶었는데 꾹 참고 다시 들어보고 기출회독을 하면서  왜 다들 회독이 답이라고 하는지 알 수 있었습니다.  행정학과 한국사는 필기노트로 계속 회독했고 행정법은 기본서, 기출문제 선지를 반복해서 학습했습니다.</t>
         </is>
       </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38659&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=69</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="55" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -2958,6 +3294,11 @@
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38646&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=69</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="55" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
@@ -2994,6 +3335,11 @@
       <c r="H69" s="3" t="inlineStr">
         <is>
           <t>-저는 총 3번의 시도 끝에 합격하게 되었는데요, 처음에는 “행정학과 이니, 대학교를 다니면서 붙어보자!” 라고 생각을 하여 휴학을 하고 공무원 공부를 하였는데 결과는 좋지 않았습니다ㅠㅠ 일단 졸업을 해야 하기 때문에 복학을 하고 병행해서 공부도 해보았지만 결국 한 가지에 집중해야 한다는 교훈만 얻은 채 불합격을 하게 됩니다. 그리고 마지막으로 졸업 후 마지막 기회라고 생각해 해커스 공무원 인강과 함께 도전하게 되었는데요, 가격적인 측면에서도 합리적이고 암기 위주가 아니라 이해 중심의 강의로 이루어져 선택하게 되었습니다! 그리고 다행히도 좋은 결과를 얻게 되어 이렇게 합격수기를 적게 되었습니다!</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38144&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=81</t>
         </is>
       </c>
     </row>
@@ -3026,6 +3372,11 @@
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38021&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=87</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="55" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
@@ -3060,6 +3411,11 @@
           <t>행정학은 여러 선생님의 기본강의를 들었는데, 전체적으로 흐름을 잡긴 했지만 이해를 못해서 과감하게 포기했던 것 같습니다. 그래서 기출문제집을 풀면서 강의를 발췌해서 들었고 그 부분을 확실히 이해하려고 노력했습니다. 선생님들만의 암기법도 참고하여 다양한 암기법으로 이론을 외웠습니다. 행정학은 무조건 "암기법" 거의 앞글자 따는 거긴 하지만요, 나름 도움됩니다. 3년 동안 까먹은 적 한 번도 없음 ㅎㅎ 그리고 행정학에서 저의 발목은 잡은 부분은 시험에서의 항상 새로운 이론의 등장이었습니다. 저는 그런 문제만 보면 얼음이 되어서 찍거나 대충 풀어버리는 습관이 있었는데, 저는 이러한 이유로 2년간 불합격을 한 것 같습니다. 이 부분을 고치지 않으면 합격하기 힘들겠다는 생각이 들어서 이 부분에 대해 열심히 분석하였습니다. 생각보다 단순하였습니다. 이론서에 없는 완전히 새로운 개념의 문제를 풀 때, 마치 국어의 독해와 비슷하였습니다. 문제 안에서 답이 있었고 문제의 흐름과 선지들끼리의 구성을 잘 살펴보면 꼭 맞지 않는 선지가 답이었습니다. 여러 문제를 풀다보면 자신이 느끼는 바가 있을 것입니다. 저는 이번 시험에서 새로운 개념의 문제는 다 맞췄습니다. 이 부분은 저 스</t>
         </is>
       </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37280&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="55" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -3098,6 +3454,11 @@
           <t>판례문제와 법이론 문제를 나눠서 외웠고 판례는 안외워지는 것 위주로 반복해서 보았습니다. 헌법은 초시때 점수가 안나와서 재시때에는 시간을 많이 투자하였습니다. 행정학은 생소한 문제가 계속 출제된다고 생각하여 기출된 주제의 문제는 실수하지 않도록 연습하였고 새로운 주제들은 특강을 들었습니다. 행정법은 황남기 선생님을 들었습니다. 행정법은 판례문제에서 많이 출제된다고 생각하여 판례를 반복하였고 대부분 기출된것에서 출제가 되어 빈출문제를 더 많이 보았습니다.</t>
         </is>
       </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36757&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="55" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
@@ -3134,6 +3495,11 @@
       <c r="H73" s="3" t="inlineStr">
         <is>
           <t>제가 생각하기에 한국사와 행정학은 개념이 중요하다고 생각해서 교재로 회독을 돌렸고, 행정법은 사례가 중요하다고 생각해서 단원별 기출문제집이나 동형문제집으로 회독했습니다.</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36210&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=103</t>
         </is>
       </c>
     </row>
@@ -3166,6 +3532,11 @@
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36190&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=103</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="55" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
@@ -3200,6 +3571,11 @@
           <t>1. 기본 베이스 국어 - 초반에는 한자성어에 약한 편이었습니다. 영어 - 중간 정도의 수준이었고 듣기영역에 약한 정도였습니다. 한국사 - 디테일하게 공부해본 적이 별로 없었습니다. 행정법 - 처음 접하는 과목이었고 용어도 익숙하지 않았었습니다. 행정학 - 처음 접하는 과목이었습니다.</t>
         </is>
       </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36145&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=105</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="55" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -3238,6 +3614,11 @@
           <t>- 행정학 사회과학을 전공해서 베이스가 조금 있었습니다. 강의는 서현 선생님의 강의를 들었습니다. 정리도 깔끔하고 설명도 이해하기 쉬워서 추천드립니다. 전체적으로 무난하게 공부했던 과목입니다.</t>
         </is>
       </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36046&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=109</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="55" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
@@ -3276,6 +3657,11 @@
           <t>2023 지방직 일반행정 최종합격수기  안녕하세요 이번 2023년 지방직에서 최종 합격하게 되었습니다. 제 합격수기를 보시고 공부 방법도 참고하시고 좋은 동기방안을 얻으셨으면 좋겠습니다!  응시 기간: 2021년 9월부터 2023년 9월까지 응시 직렬: 일반행정직 베이스: 행정법, 행정학은 처음 시작했고 학창시절 공부에 관심이 없어 국어도 노베이스였었습니다. 영어와 한국사는 일반행정직 준비하기전 경찰공무원을 준비했을 때 공부하여 어느정도 기본은 잡혀있었습니다.  공부 하루 루틴: 저는 독립된 공간보단 여러 사람들이 있는 스터디 카페나 주변 도서관을 주로 이용했습니다. 아침 7시에 기상해서 30분 동안 준비한 후 30분 정도 거리에 있는 공부 장소로 이동했습니다. 공부에 집중하느라 운동을 소홀히 해서 걷기라도 해보려 했습니다. 그 과정에서 걸으면서 영단어, 한자성어, 속담 등을 외우면서 다녔습니다. 도착하면 8시부터 9시까지 영어 하프 모의고사를 했습니다. 그리고 9시부터 1시까지 한 과목 인강을 들으면 진도를 나갔습니다. 중간에 쉬는 시간도 가지면서 컨디션을 조절했습니다. 그리고 점심시간 1시간 정도 가진 후 오후에는 다른 과목을 1시부터 6시까지 진도를 나</t>
         </is>
       </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36027&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=110</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="55" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -3310,6 +3696,11 @@
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35950&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=113</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="55" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
@@ -3348,6 +3739,11 @@
           <t>행정학 : 뭔가 쉬운데 쉽지 않은 과목이라고 생각합니다. 행정학은 제가 전공했기 때문에 다른 분들보다 확실히 초반에 접근할 때 수월했던 게 사실입니다. 그래서 공부를 많이 하지 않고 시험을 봐도 75점에서 80점대는 유지했고 공부할 때 그렇게 많은 스트레스를 주진 않았던 것 같습니다. 하지만 필수과목이 되면서 그 전보다 확실히 난이도가 올라갔다고 느꼈습니다. 특히 지엽적인 문제빈도가 높아졌다고 느껴지면서 도대체 어디까지 준비해야하나 싶을 정도로 공부 방향성을 잡는 게 쉽지 않아졌다고 생각합니다. 하지만 일단 기본에 충실하면서 기출문제로 지엽적인 부분을 커버하면 어느정도 고득점을 맞는 데 어렵지 않다고 생각합니다. 그런 점에서 서현 선생님의 강의는 어떤 개념이 나오면 그 느낌이 연상되게 해주고 암기할 게 많은 행정학에서 최대한 암기하기 쉽게 해주는 부분이 많아서 좋았습니다.</t>
         </is>
       </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35911&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=114</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="55" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -3390,6 +3786,11 @@
           <t>1. 응시한 시험의 기본정보   ⓐ 응시한 시험 : 지방직 9급   ⓑ 응시한 직렬 : 일반행정   ⓒ 공부 기간 : 8개월   ⓓ 본인만의 합격 노하우 :     기본베이스 : 토익(910점), 한능검 1급     국어(신민숙)   문법, 어휘 기본강의와 문학,비문학 기본강의 문법은 심화강의, 기출문제 강의, 한자성어 300강의를 들었습니다.   특히 신민숙쌤은 문법강의가 너무 좋았습니다. 시험 경향이 쉬워지면서 어려운 문법은 나오지 않아서 심화강의까지는 듣지 않았어도 될 것 같지만 저는 복습하는 의미에서 도움이 되었습니다. 한자성어도 강의를 들으니 더 뚜렷하게 기억에 남습니다. 신민숙 쌤 정말 추천합니다.     영어(비비안)   영어는 기본베이스가 어느정도 있었기에 기본이론 강의는 저에게 너무 진도가 느리다고 느껴져서 문제풀이를 같이하는 문법강의를 들었습니다. 기출문제도 정말 꼼꼼하게 설명을 해주셔서 어떻게 문제를 풀어야 하는지 알 수 있었습니다. 시험 직전 문법 OX문제도 도움이 되었던 것 같습니다. 문법을 정말 꼼꼼하고 깔끔하게 설명해주십니다. 비비안 선생님 정말 추천합니다. 영단어는 매일매일 외웠고 4회독 정도밖에 하지 못했네요.     한국사(이</t>
         </is>
       </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35867&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=116</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="55" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
@@ -3426,6 +3827,11 @@
       <c r="H81" s="3" t="inlineStr">
         <is>
           <t>- 일반적인 기본베이스는 수능기준으로 보았을 때 국어는 3등급 / 영어는 2등급 정도의 실력을 가지고 있었고, 한국사는 4등급에서 5등급을 맞는 수준이었습니다. 나머지 행정학과 행정법 또한 전공이지만 처음 모의고사나 기출 시험을 풀었을 때에는 과락이 나올 정도로 처참했습니다.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35750&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=120</t>
         </is>
       </c>
     </row>
@@ -3458,6 +3864,11 @@
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35634&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=124</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="55" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
@@ -3488,6 +3899,11 @@
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35587&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=125</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="55" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -3518,6 +3934,11 @@
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35435&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=129</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="55" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
@@ -3552,6 +3973,11 @@
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35196&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=136</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="55" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -3582,6 +4008,11 @@
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35192&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=136</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="55" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
@@ -3616,6 +4047,11 @@
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35131&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=139</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="55" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -3654,6 +4090,11 @@
           <t>보건행정학, 공중보건학 - 최성희 선생님 기본이론 강의 부터 기출강의까지 착실하게 따라갔고 선생님께서 개인적으로 만들어주시는 간단한 문제들과 시험문제처럼 만드신 문제들이 이론을 다시 돌아보는데 도움이 됐습니다. 전공은강의 말고 혼자 공부하는 시간을 훨씬 더 많이 할애해야한다고 생각합니다.  방대한 양과 외우기 힘든 수치들, 생소한 행정학 단어들 때문에 막막하겠지만 처음부터 세세히 외우려고 하기보단 책 읽듯이 처음부터 끝까지 읽어보고, 그 다음은 단어의 정의나 설명들을 구분해서 암기하고 천천히 세부적으로 들어가면서 여러번 회독한 후 기출문제 풀고 기출도 3~4회독정도 한다면 충분히 안정적인 점수를 받을 수 있을거라 생각합니다.</t>
         </is>
       </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41370&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="55" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
@@ -3696,6 +4137,11 @@
           <t>행정학 - 90점 행정학은 송상호 선생님의 강의를 들었습니다. '송상호 명품 행정학 기본이론', '송상호 명품 행정학 심화이론'으로 이론을 공부한 다음에, '해커스공무원 명품 행정학 단원별 기출문제집'으로 기출문제를 공부했습니다. 행정학은 여러 주제들이 섞여 있는 학문이어서, 공부를 하고 문제를 계속 풀어도 헷갈리는 지문이 많이 나오는 과목입니다. 송상호 선생님께선 그러한 지점들을 잘 짚어주시고, 중요한 내용들을 강조하시면서 학생들로 하여금 '행정학'이라는 과목에 익숙해지도록 이끌어주십니다.</t>
         </is>
       </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41530&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="55" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -3734,6 +4180,11 @@
           <t>- 2024.07 ~ 2025.06 (약 1년)   2. 기본 베이스 지거국 영어영문학과 / 토익 900점대 후반 / 한능검 1급   3. 하루 루틴 수험 생활 초기에는 집 근처 도서관에서 공부를 했는데 집중이 잘 안 돼, 해커스 스파르타 독서실을 다녔습니다. 월요일부터 토요일까지는 아침 7시에 기상 후 아침 8시부터 밤 10시까지 독서실에서 공부했고 일요일은 쉬었습니다.   4. 공부 방향 공부 방향을 잘 설정하는 것이 단기 합격의 지름길이라고 생각합니다. 국어, 영어는 제가 자신 있어 하는 과목이었고 기초도 어느 정도 있었기 때문에 공부 시간을 최대한 줄이고 남는 시간을 한국사, 행정법, 행정학에 할애했습니다. 한국사 또한 제가 자신 있어 하는 과목으로 기초도 있었지만 국어, 영어와는 다르게 암기 과목이라 휘발성이 강해 공부량을 줄이지는 않았습니다. 공부 시간을 대략적으로 따져본다면 행정학 &gt; 행정법 &gt; 한국사 &gt; 영어 &gt; 국어 순으로 시간을 투자했습니다.   5. 과목별 공부법 국어 95점 국어는 학창 시절 열심히 했었기 때문에 자신 있는 과목이었습니다. 인사혁신처 예시 문제를 풀어보니 별다른 공부 없이도 충분히 풀 수 있는 난도여서 국어에 많은 시간을</t>
         </is>
       </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41522&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="55" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
@@ -3768,6 +4219,11 @@
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41520&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="55" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -3798,6 +4254,11 @@
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41511&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="55" customHeight="1">
       <c r="A93" s="3" t="inlineStr">
@@ -3836,6 +4297,11 @@
           <t>2025년 공무원 시험 합격수기:  강사님들 덕분입니다!! 안녕하십니까. 이번 공무원 시험에 최종 합격한 수험생입니다. 제가 합격이라는 결실을 맺을 수 있었던 가장 큰 비결은, 바로 해커스공무원의 훌륭한 강사진과 커리큘럼을 믿고 흔들림 없이 따라간 덕분입니다. 특히, 제가 선택했던 국어 신민숙, 영어 비비안, 행정법 김대현, 행정학 서현 선생님의 강의는 저의 수험 생활을 관통하는 핵심이었습니다.(한국사는 독학으로 공부했습니다)</t>
         </is>
       </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41463&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=6</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="55" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -3870,6 +4336,11 @@
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41434&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="55" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
@@ -3908,6 +4379,11 @@
           <t>■ 과목별 공부 방법 국어: 신민숙 선생님 강의를 활용했습니다. 문법은 개념부터 다시 정리했고, 새롭게 추가된 논리 파트는 인강으로 보강했습니다. 문학·비문학은 문제풀이 위주로 학습했고, 교재는 선생님 커리큘럼을 따라가며 문제집을 풀었습니다. 영어: 모의고사를 중심으로 공부했습니다. 틀린 문제는 해설과 단어 풀이를 활용해 다시 독해했고, 비비안 선생님 보카 강의를 통해 단어 학습을 보완했습니다. 동의어와 반의어를 함께 익히는 방식이 큰 도움이 되었습니다. 한국사: 이중석 선생님 강의를 통해 개념과 기출을 모두 정리했습니다. 블랭크 노트와 맵핑 수업 방식이 이해도를 높였고, 문제를 풀면서 관련 개념까지 정리하는 방식이 장기 기억에 유리했습니다. 행정법: 함수민 선생님 강의와 교재를 활용했습니다. 선생님의 교재와 강의 양이 많아 처음에는 당황스러웠지만 그만큼 하나라도 알려주시려는 열정이 느껴졌습니다. 처음 접하는 과목이었지만 꼼꼼한 설명 덕분에 기초를 다질 수 있었습니다. 반복적으로 나오는 지문이 많아 회독을 늘릴수록 답안 속도가 빨라지는 효과를 얻을 수 있었습니다. 행정학: 서현 선생님 강의를 수강했습니다. 단순 암기 과목처럼 보이지만 지엽적인 문제가 많아 심</t>
         </is>
       </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41432&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="55" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -3946,6 +4422,11 @@
           <t xml:space="preserve">공부 패턴 저는 보통 오전, 오후, 저녁으로 나누어 공부했고, 밤늦게까지는 하지 않았습니다. 쉬는 날은 토요일 오전과 일요일 정도로 잡았고, 일주일에 1~2회 정도 저녁에 운동을 했습니다. 개인적으로 운동이 중요하다고 생각했습니다. 스트레스도 풀리고, 공부하는 데 체력이 중요하다는 것을 많이 느꼈습니다. 평소 운동을 해 둔 덕분에 시험 전 2~3개월 동안은 공부에만 집중할 수 있었다고 생각합니다. 국어 국어는 신민숙 선생님 강의를 들었습니다. 최대한 학생들이 이해하기 쉽게 설명해 주시고, 중요한 부분들을 짚어 주셔서 공부량을 줄이는 데 많은 도움이 되었습니다. 국어 과목이 개편된 후에는 다양한 문제를 많이 풀어 보는 것이 중요할 것 같습니다. 영어 영어는 비비안 선생님 강의를 들었습니다. 제가 문법에 자신이 없었는데, 깔끔하게 정리된 자료를 배포해 주셔서 기본기를 닦는 데 큰 도움이 되었습니다. 그리고 선생님께서 단어 암기를 강조하시며, 거기에 도움이 되는 다양한 강의를 제공해 주셔서 암기 습관을 만드는 것이 수월했습니다. 한국사 한국사는 이중석 선생님 강의를 들었습니다. 선생님 강의 덕분에 한국사를 재미있게 공부할 수 있었습니다. 강의 시간이 길지만 단순 </t>
         </is>
       </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41388&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="55" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
@@ -3982,6 +4463,11 @@
       <c r="H97" s="3" t="inlineStr">
         <is>
           <t>처음 공무원 시험 준비를 시작할 때 저는 영어를 제외한 4과목이 완전히 노베이스였습니다. 생전 처음 보는 행정법과 행정학 뿐만 아니라 국어와 국사도 중학생 때 이후로 처음이었습니다. 공무원 시험을 치려고 마음을 먹고 바로 수험서로 유명한 해커스에 강의 등록을 했고, 시험이 어느 정도의 난이도로 출제되는지 감을 잡아보려고 특별한 공부나 준비 없이 2024년 지방직 시험을 응시 했었습니다. 결과는 예상보다 더 안좋았습니다. 영어를 제외한 과목은 거의 다 찍는 수준이었고 특히 국어가 고전 시가나 한문 그리고 문법 때문에 너무 어렵게 느껴졌었습니다. 시험을 보고나니 아무리 공부를 더 해도 국어 성적은 올리기가 힘들다는 판단에 시험 자체를 포기해야하나 생각했었습니다.</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41308&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=13</t>
         </is>
       </c>
     </row>
@@ -4018,6 +4504,11 @@
           <t>- 행정법 &amp; 행정학 정말 무슨 자신감인지는 모르겠지만 단 한번도 공부하지 않았었지만 고등학교를 문과로 나오고 선택과목도 법정이었어서 걱정은 많이 없었던 것 같네요.. (근거 없는 자신감이 최고조였던...ㅎㅎ, 마지막까지 발목잡은 행정법...)</t>
         </is>
       </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41258&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="55" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
@@ -4056,6 +4547,11 @@
           <t>- 필기 준비 과정 &gt; 국어 신민숙 선생님 강의를 들으며 문법 개념을 체계적으로 정리했습니다. 또, 대학에서 논리학을 배운 경험 덕분에 논리 문제에서도 큰 도움을 받았습니다. 국어는 초반에 개념을 정리해 두고 논리 문제는 충분히 연습해두면, 시간을 절약할 수 있는 과목이었던 것 같습니다. &gt; 영어 영어는 제 가장 큰 약점이었습니다. 그래서 우선, 비비안 선생님의 기초 강의를 들으며 기본기를 다졌습니다. 설명이 명확해서 이해하기 좋았고 영어에 대한 거리감이 어느 정도는 줄어들었던 것 같습니다. 다만, 충분히 시간을 투자하지 못한 아쉬움이 남습니다. 수험생분들 중에도 특정 과목이 약점이라면, 반드시 학습시간 분배에 신경 쓰시길 바랍니다. &gt; 한국사 이중석 선생님 강의를 들었습니다. 수험 한국사는 처음이었지만, 스토리텔링 방식 덕분에 재미있게 개념을 잡을 수 있었습니다. 다만, 선생님도 늘 강조하시듯 강의만 듣고 끝내면 안 되고, 반드시 스스로 정리하는 복습이 필요합니다. &gt; 행정법 함수민 선생님의 기본+심화 강의를 통해 핵심 판례와 빈출 영역을 집중적으로 학습했습니다. 처음에는 강의 분량이 많아 부담스러웠지만, 시험 막판에는 오히려 시간을 절약할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41253&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="55" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -4094,6 +4590,11 @@
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41233&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="55" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
@@ -4136,6 +4637,11 @@
           <t>행정학 공부방법 행정학은 서현 선생님 개념 강의 수강했습니다.  사실 인강을 많이 들을 시간이 없기도 했고 강의 스타일이 저와 잘 맞지 않아서</t>
         </is>
       </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41220&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="55" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -4170,6 +4676,11 @@
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41215&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="55" customHeight="1">
       <c r="A103" s="3" t="inlineStr">
@@ -4208,6 +4719,11 @@
           <t>행정학/서현 선생님 강의가 좀 길고 방대합니다. 그러나 처음 듣는 사람이 듣기에는 어려움이 없습니다. 기본강의 들을떄는 이해가 되지 않더라도 귀에 익힌다는 생각으로 끝까지 완강을 하는것을 추천드립니다. 서현 선생님의 기출 문제집이 좋습니다. 기본강의 후 기출문제집을 계속 회독하면서 부족한 개념을 계속 암기하는 방법으로 공부하였습니다.</t>
         </is>
       </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41179&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="55" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -4248,6 +4764,11 @@
       <c r="H104" s="2" t="inlineStr">
         <is>
           <t>행정학(90) 서현 선생님 행정학 행정학 기본강의와 심화강의를 들었습니다. 강의를 안듣고 기본서를 보면 무슨말인지 파악이 안됩니다. 기본적인 부분을 필기하고 심화강의를 추가했습니다.700제 문제를 이해되게 잘 설명해주셔서 점수를 잘받을수 있게 되었습니다.단원별 기출문제는 다풀어 보진 못했고 문제와 해설지가 따로여서 해설을 문제에 적으면서 풀려고햇습니다. 쉬운 암기법을 통해 어려운 개념도 정리가 되겠금 가르쳐 주십니다.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41125&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
         </is>
       </c>
     </row>
@@ -4280,6 +4801,11 @@
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr"/>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41099&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=22</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="55" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
@@ -4314,6 +4840,11 @@
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41037&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=25</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="55" customHeight="1">
       <c r="A107" s="3" t="inlineStr">
@@ -4348,6 +4879,11 @@
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr"/>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41031&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=25</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="55" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -4378,6 +4914,11 @@
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40683&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="55" customHeight="1">
       <c r="A109" s="3" t="inlineStr">
@@ -4412,6 +4953,11 @@
           <t>암기과목(한국사, 행정법, 행정학)의 경우 그날 배운 부분을 복습한 뒤 기출문제에서 어떤 식으로 문제가 출제되는지, 중요한 부분이 무엇인지 확인하세요.</t>
         </is>
       </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=44</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="55" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
@@ -4446,6 +4992,11 @@
           <t>(행정학) 행정학의 경우에는 대부분의 수험생들이 그렇듯 시험 직전까지도 가장 자신이 없었습니다. 개념의 범위가 너무 넓고 항상 불의타 문제가 나오기 때문에 대비가 어렵다고 느꼈습니다. 행정학의 경우에는 여러 이론들에 대해서 묻기 때문에 이론 간의 비교에 집중하면서 공부하는게 큰 도움이 됐습니다. 간단하게 비유하자면 단순하게 (a 이론의 특성은 키가 작다) 이런 식으로 외우면  혼동이 생길 때가 많습니다. 왜냐하면 a 이론이 b이론과 비교했을 때는 키가 작았지만, 또 다른 c이론과 비교했을 때는 키가 큰 경우가 있기 때문입니다. 행정학은 법 과목의 판례들처럼 딱 정해진 것이 아니어서 어떤 대상과 비교하냐에 따라서 해당 이론의 특성이 아 다르고 어 다르기 때문에  (a 이론은 b 이론과 비교했을 때는 키가 작다) 이런 식으로 유사한 그룹의 개념들끼리 비교를 잡으면서 개념을 유연성 있게 정리하는게 많은 도움이 됐습니다.   (헌법)) 헌법의 경우 처음 기본 강의를 들을 때는 상대적으로 재밌다고 느꼈습니다. 왜냐하면 다양한 판례들이 나오고 아무래도 판례들이 우리 생활과 밀접해 있다 보니 이러한 경우도 있구나 하면서 상대적으로 즐겁게 기본강의를 들었습니다. 하지만 기</t>
         </is>
       </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="55" customHeight="1">
       <c r="A111" s="3" t="inlineStr">
@@ -4476,6 +5027,11 @@
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr"/>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39633&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="55" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -4510,6 +5066,11 @@
           <t>(4) 행정학 [강의] 서현쌤 기본+심화이론 23년 1회 수강 [강의] 서현쌤 법령특강 1회 수강 [강의] 마니쌤 기본이론 24년 1회 수강 [교재] 서현쌤 기본서 [교재] 마니쌤 기본서 [교재] 서현쌤 기출문제집 9회독 [교재] 마니쌤 OX 3회독 [교재] 경간 소간 국회직 등등 각종 시행처 최신기출</t>
         </is>
       </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39626&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="55" customHeight="1">
       <c r="A113" s="3" t="inlineStr">
@@ -4548,6 +5109,11 @@
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr"/>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38957&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=56</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="55" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -4586,6 +5152,11 @@
           <t>특히, 동형모의고사의 경우 구할 수 있는 대로 구해서 양치기를 했는데, 외웠다고 생각했던 판례, 혹은 요약 되었거나, 전문이 나오면 틀리는 경우가 있었습니다. 하지만, 양치기를 통해 틀렸던 문제의 판례는 다시 기본서로 돌아와 공부하고, 중요한 쟁점, 혹은 자주 나오는 문구에 형광펜을 칠하고 외웠습니다. 아무래도 틀렸던 문제의 경우 기억에 더 잘 남아서, 형광펜 치고 다시 보았던 판례의 기억 저장 시간이 훨씬 길었습니다. 서현 선생님의 강의에서 가장 핵심이 되는 내용은 행정학적 마인드 같습니다. 사실 공부하는 내내 행정학적 마인드를 적립하는데 어려움이 있어서, 어떻게 해야 하지 고민이 많았지만, 강의노트 회독, 문제풀이를 하며 개념을 다잡고 그게 쌓이다 보니 저절로 적립이 가능했습니다.</t>
         </is>
       </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38729&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=66</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="55" customHeight="1">
       <c r="A115" s="3" t="inlineStr">
@@ -4620,6 +5191,11 @@
         </is>
       </c>
       <c r="H115" s="3" t="inlineStr"/>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38522&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=74</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="55" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
@@ -4658,6 +5234,11 @@
           <t>-저는 총 3번의 시도 끝에 합격하게 되었는데요, 처음에는 “행정학과 이니, 대학교를 다니면서 붙어보자!” 라고 생각을 하여 휴학을 하고 공무원 공부를 하였는데 결과는 좋지 않았습니다ㅠㅠ 일단 졸업을 해야 하기 때문에 복학을 하고 병행해서 공부도 해보았지만 결국 한 가지에 집중해야 한다는 교훈만 얻은 채 불합격을 하게 됩니다. 그리고 마지막으로 졸업 후 마지막 기회라고 생각해 해커스 공무원 인강과 함께 도전하게 되었는데요, 가격적인 측면에서도 합리적이고 암기 위주가 아니라 이해 중심의 강의로 이루어져 선택하게 되었습니다! 그리고 다행히도 좋은 결과를 얻게 되어 이렇게 합격수기를 적게 되었습니다!</t>
         </is>
       </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38144&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=81</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="55" customHeight="1">
       <c r="A117" s="3" t="inlineStr">
@@ -4696,6 +5277,11 @@
           <t>- 행정학 : 서현 선생님 강의와 커리큘럼이 짜임새가 있습니다. 강의 경력도 워낙 기시고 전공자셔서 전문성은 말할 것도 없구요. 딕션이나 목소리도 좋으셔서 강의 듣는데에 매우 편했습니다. 입문-기본-심화-문풀-실전동형 이 5단계가 너무나도 튼튼하게 갖추어져 있어서, 커리큘럼대로만 꾸준히 따라가다 보면 서현 선생님이 수업 중 계속해서 강조하시는 행정학적인 마인드가 머리에 장착됩니다.강의의 특장점으로는 현 행정학 강의노트 라는 단권화 노트가 있는데, 따로 개인적으로 단권화할 필요 없이 300페이지 가량 되는 이 책에 강의 들으면서 꾸준히 개념 추가하고, 책정리 해가다 보면 80점 라인 방어하는 데에는 차고 넘칩니다. 기본심화 강의 진행도 기본서는 서브로 하고 이 강의노트 위주로 해 주셔서, 방대한 행정학의 분량을 획기적으로 줄여서 기본을 쌓아올리는 데에 큰 도움이 된 것 같습니다.</t>
         </is>
       </c>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36748&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="55" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -4730,6 +5316,11 @@
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36207&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=103</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="55" customHeight="1">
       <c r="A119" s="3" t="inlineStr">
@@ -4764,6 +5355,11 @@
           <t>1. 기본 베이스 국어 - 초반에는 한자성어에 약한 편이었습니다. 영어 - 중간 정도의 수준이었고 듣기영역에 약한 정도였습니다. 한국사 - 디테일하게 공부해본 적이 별로 없었습니다. 행정법 - 처음 접하는 과목이었고 용어도 익숙하지 않았었습니다. 행정학 - 처음 접하는 과목이었습니다.</t>
         </is>
       </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36145&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=105</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="55" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -4804,6 +5400,11 @@
       <c r="H120" s="2" t="inlineStr">
         <is>
           <t>1. 응시한 시험의 기본정보   ⓐ 응시한 시험 : 지방직 9급   ⓑ 응시한 직렬 : 일반행정   ⓒ 공부 기간 : 8개월   ⓓ 본인만의 합격 노하우 :     기본베이스 : 토익(910점), 한능검 1급     국어(신민숙)   문법, 어휘 기본강의와 문학,비문학 기본강의 문법은 심화강의, 기출문제 강의, 한자성어 300강의를 들었습니다.   특히 신민숙쌤은 문법강의가 너무 좋았습니다. 시험 경향이 쉬워지면서 어려운 문법은 나오지 않아서 심화강의까지는 듣지 않았어도 될 것 같지만 저는 복습하는 의미에서 도움이 되었습니다. 한자성어도 강의를 들으니 더 뚜렷하게 기억에 남습니다. 신민숙 쌤 정말 추천합니다.     영어(비비안)   영어는 기본베이스가 어느정도 있었기에 기본이론 강의는 저에게 너무 진도가 느리다고 느껴져서 문제풀이를 같이하는 문법강의를 들었습니다. 기출문제도 정말 꼼꼼하게 설명을 해주셔서 어떻게 문제를 풀어야 하는지 알 수 있었습니다. 시험 직전 문법 OX문제도 도움이 되었던 것 같습니다. 문법을 정말 꼼꼼하고 깔끔하게 설명해주십니다. 비비안 선생님 정말 추천합니다. 영단어는 매일매일 외웠고 4회독 정도밖에 하지 못했네요.     한국사(이</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35867&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=116</t>
         </is>
       </c>
     </row>
@@ -4836,6 +5437,11 @@
         </is>
       </c>
       <c r="H121" s="3" t="inlineStr"/>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35435&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=129</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="55" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
@@ -4870,6 +5476,11 @@
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41696&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="55" customHeight="1">
       <c r="A123" s="3" t="inlineStr">
@@ -4900,6 +5511,11 @@
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr"/>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41511&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="55" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
@@ -4942,6 +5558,11 @@
           <t>작년 12월에 맘먹고 준비하려고 보니 6월이 시험이더라구요 ㅠ 그때부터 해커스에서 인터넷 강의 신청해서 먼저 양이 많은 한국사(이중석쌤)부터 시작해서 강의 듣기 시작했고 중간에 행정학(서현쌤) 추가해서 하루에 3-4시간씩 나눠서 강의를 들었습니다. 그리고 한국사와 행정학이 어느정도 진도가 나간 후에 행정법(김대현쌤)강의를 뒤늦게 들었습니다 그리고 기본강의 다 듣고 난 뒤에 한국사는 8개년 기출문제집으로 계속 돌려보면서 안외워지는 선택지는 색깔 표시해서 외우고 행정학은 서현쌤 심화강의까지 다 듣고 똑같이 기출문제집으로 계속 돌려보면서 안외워지는 선택지 색깔 표시해서 계속 회독 돌렸어요! 행정법은 일단 너무 두꺼운 교과서 보다 3분의 1로 줄어쓴 책이어서 쉽게 접근이 가능했던 김대현 쌤 강의와 책이 너무 도움이 되었습니다.</t>
         </is>
       </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41451&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=6</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="55" customHeight="1">
       <c r="A125" s="3" t="inlineStr">
@@ -4984,6 +5605,11 @@
           <t>5. 행정학 행정학은 공부하면 할수록 늪에 빠지는 느낌이 많이 든 과목이었습니다. 저는 김만희선생님 강의를 들었는데, 처음엔 이걸 어떻게 공부하지? 생각이 많이 들었던 과목이었습니다. 특히 모의고사 풀 때 점수가 잘 안나오는 과목중 하나였습니다. 이거 되는 시험이 맞는건가? 생각이 많이 들었으나, 기출을 풀면 못 보던 문제 같은데 풀리는걸 보며 모의고사에 너무 연연하지 않고 하던 방식대로 계속 공부했습니다. 마지막 1달 앞두고서는 주요 법령 모아둔 책을 구매하여 외우지는 못해도 기본계획같은 큼직한 년수는 외우려 했습니다. 암기할것은 외워야 하지만 일단 개념이 이해가 잘 되었기 때문에 암기가 크게 어렵지 않았습니다.</t>
         </is>
       </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41439&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="55" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
@@ -5018,6 +5644,11 @@
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41325&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=12</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="55" customHeight="1">
       <c r="A127" s="3" t="inlineStr">
@@ -5056,6 +5687,11 @@
           <t>- 필기 준비 과정 &gt; 국어 신민숙 선생님 강의를 들으며 문법 개념을 체계적으로 정리했습니다. 또, 대학에서 논리학을 배운 경험 덕분에 논리 문제에서도 큰 도움을 받았습니다. 국어는 초반에 개념을 정리해 두고 논리 문제는 충분히 연습해두면, 시간을 절약할 수 있는 과목이었던 것 같습니다. &gt; 영어 영어는 제 가장 큰 약점이었습니다. 그래서 우선, 비비안 선생님의 기초 강의를 들으며 기본기를 다졌습니다. 설명이 명확해서 이해하기 좋았고 영어에 대한 거리감이 어느 정도는 줄어들었던 것 같습니다. 다만, 충분히 시간을 투자하지 못한 아쉬움이 남습니다. 수험생분들 중에도 특정 과목이 약점이라면, 반드시 학습시간 분배에 신경 쓰시길 바랍니다. &gt; 한국사 이중석 선생님 강의를 들었습니다. 수험 한국사는 처음이었지만, 스토리텔링 방식 덕분에 재미있게 개념을 잡을 수 있었습니다. 다만, 선생님도 늘 강조하시듯 강의만 듣고 끝내면 안 되고, 반드시 스스로 정리하는 복습이 필요합니다. &gt; 행정법 함수민 선생님의 기본+심화 강의를 통해 핵심 판례와 빈출 영역을 집중적으로 학습했습니다. 처음에는 강의 분량이 많아 부담스러웠지만, 시험 막판에는 오히려 시간을 절약할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41253&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="55" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -5098,6 +5734,11 @@
           <t>행정학(90) 서현 선생님 행정학 행정학 기본강의와 심화강의를 들었습니다. 강의를 안듣고 기본서를 보면 무슨말인지 파악이 안됩니다. 기본적인 부분을 필기하고 심화강의를 추가했습니다.700제 문제를 이해되게 잘 설명해주셔서 점수를 잘받을수 있게 되었습니다.단원별 기출문제는 다풀어 보진 못했고 문제와 해설지가 따로여서 해설을 문제에 적으면서 풀려고햇습니다. 쉬운 암기법을 통해 어려운 개념도 정리가 되겠금 가르쳐 주십니다.</t>
         </is>
       </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41125&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="55" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
@@ -5136,6 +5777,11 @@
           <t>법과목 또한 너무 생소했고 또 남은 기간이 많지 않았기에 시작은 막막했습니다. 하지만 김대현 선생님은 컴팩트한 교재와 강의를 사용하시기에 현재 제 상황에 딱 맞는 선생님이였습니다. 행정법에서 가장 중요한 건 흐름을 알고 문제가 풀리는 그 순간까지 참고 버티고 공부해 나아가는 것 같습니다.. 처음에는 아무리 풀어보려해도 안 풀리는게 행정법이지만 나중에 효자과목이 된다는 이유를 알게 됐습니다. 국가직땐 행정법에 빠져서 많이 공부하고 풀다보니 국가직땐 65점 나와서 만족했지만 지방직까지 가는 과정중에 국가직 면접과 행정학 빵구 메우기 때문에 집중을 못해서 지방직땐 성적이 비록 떨어졌습니다. 그래서 행정법 또한 기본강의 듣고 회독하고 문제 풀며 어느정도 성적이 올라왔을때 계속 감을 유지하고 부족한 부분을 채워나가는 것이라 생각합니다. 단원만 보고 한 부분만 본다면 어려운 과목이지만 기본강의가 끝나고 여러번 회독 했을때 과목 전체를 보면 행정학보다 훨씬 효자과목이라 생각합니다(기출회독 필수)</t>
         </is>
       </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40996&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=26</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="55" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -5178,6 +5824,11 @@
           <t>- 수강한 선생님&amp;강의&amp;교재 추천 국어: 신민숙 선생님(신민숙 쉬운국어 논리 강화 150제 교재)  영어: 비비안 선생님(해커스공무원 비비안 올인원 영문법, 2025 해커스공무원 영어 구조 독해 007) 한국사: 이중석 선생님(해커스공무원 이중석 맵핑 한국사 올인원 블랭크노트) 행정법: 홍대겸 선생님(2025 해커스 홍대겸 행정법총론 단원별 기출문제집) 행정학: 서현 선생님(2025 해커스공무원 현 행정학 단원별 기출문제집)  모두 큰 도움이 되었습니다.  교재는 위의 교재 등을 위주로 활용했습니다.</t>
         </is>
       </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40541&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=36</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="55" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
@@ -5214,6 +5865,11 @@
       <c r="H131" s="3" t="inlineStr">
         <is>
           <t>행정학(서현/95점) 아~ 행정학 저에겐 너무 어려웠어요 비슷한 내용인데 다른 거고 다른 내용인줄 알았는데? 같은거고 정말 헷갈려서 회독을 많이 하는 수밖에 없었어요 서현쌤 강의 스타일은 암기단어들을 많이 만들어주셔서 암기할게 많은 행정학을 그래도 좀 쉽게 암기하지 않았나 싶습니다</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40388&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=43</t>
         </is>
       </c>
     </row>
@@ -5250,6 +5906,11 @@
           <t>암기과목(한국사, 행정법, 행정학)의 경우 그날 배운 부분을 복습한 뒤 기출문제에서 어떤 식으로 문제가 출제되는지, 중요한 부분이 무엇인지 확인하세요.</t>
         </is>
       </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=44</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="55" customHeight="1">
       <c r="A133" s="3" t="inlineStr">
@@ -5284,6 +5945,11 @@
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr"/>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38878&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=60</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="55" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
@@ -5326,6 +5992,11 @@
           <t>2. 베이스 국어 수능 3등급, 영어 수능 2등급 토익 800점대, 한국사 수능1 한국사검정시험1급, 행정법 행정학 처음 공부함</t>
         </is>
       </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38678&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=68</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="55" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
@@ -5368,6 +6039,11 @@
           <t>한국사(노베이스) 공시공부 시작을 한국사로 하게 되었습니다. 접근성도 나름 높은 것 같았고, 한국사를 알아야 행정법과 행정학이 더 잘 이해가 될 것이라고 생각해서였습니다. 하지만 결코 접근성이 높지만은 않았는지, 다른 사이트에서 타강사님 강의를 듣다가 이해가 너무 안돼서 유튜브 강의를 찾아본 결과 이중석 선생님 강의를 알게 되었는데(불교와 성리학 강의), 듣자마자 '아, 이 선생님이다!'라는 생각이 들어서 바로 결제하게 되었습니다. 이중석 선생님 강의를 듣고 나서는 현대사 끝까지 이해를 잘 하며 공부할 수 있었습니다. 한국사는 이해뿐만 아니라 암기도 중요한데, 암기는 이명호선생님 기본강의를 들으며 암기법도 전수받고, 저만의 암기법도 생각해낼 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38534&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=73</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="55" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
@@ -5404,6 +6080,11 @@
       <c r="H136" s="2" t="inlineStr">
         <is>
           <t>-저는 총 3번의 시도 끝에 합격하게 되었는데요, 처음에는 “행정학과 이니, 대학교를 다니면서 붙어보자!” 라고 생각을 하여 휴학을 하고 공무원 공부를 하였는데 결과는 좋지 않았습니다ㅠㅠ 일단 졸업을 해야 하기 때문에 복학을 하고 병행해서 공부도 해보았지만 결국 한 가지에 집중해야 한다는 교훈만 얻은 채 불합격을 하게 됩니다. 그리고 마지막으로 졸업 후 마지막 기회라고 생각해 해커스 공무원 인강과 함께 도전하게 되었는데요, 가격적인 측면에서도 합리적이고 암기 위주가 아니라 이해 중심의 강의로 이루어져 선택하게 되었습니다! 그리고 다행히도 좋은 결과를 얻게 되어 이렇게 합격수기를 적게 되었습니다!</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38144&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=81</t>
         </is>
       </c>
     </row>
@@ -5440,6 +6121,11 @@
           <t>행정학은 여러 선생님의 기본강의를 들었는데, 전체적으로 흐름을 잡긴 했지만 이해를 못해서 과감하게 포기했던 것 같습니다. 그래서 기출문제집을 풀면서 강의를 발췌해서 들었고 그 부분을 확실히 이해하려고 노력했습니다. 선생님들만의 암기법도 참고하여 다양한 암기법으로 이론을 외웠습니다. 행정학은 무조건 "암기법" 거의 앞글자 따는 거긴 하지만요, 나름 도움됩니다. 3년 동안 까먹은 적 한 번도 없음 ㅎㅎ 그리고 행정학에서 저의 발목은 잡은 부분은 시험에서의 항상 새로운 이론의 등장이었습니다. 저는 그런 문제만 보면 얼음이 되어서 찍거나 대충 풀어버리는 습관이 있었는데, 저는 이러한 이유로 2년간 불합격을 한 것 같습니다. 이 부분을 고치지 않으면 합격하기 힘들겠다는 생각이 들어서 이 부분에 대해 열심히 분석하였습니다. 생각보다 단순하였습니다. 이론서에 없는 완전히 새로운 개념의 문제를 풀 때, 마치 국어의 독해와 비슷하였습니다. 문제 안에서 답이 있었고 문제의 흐름과 선지들끼리의 구성을 잘 살펴보면 꼭 맞지 않는 선지가 답이었습니다. 여러 문제를 풀다보면 자신이 느끼는 바가 있을 것입니다. 저는 이번 시험에서 새로운 개념의 문제는 다 맞췄습니다. 이 부분은 저 스</t>
         </is>
       </c>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37280&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="55" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
@@ -5474,6 +6160,11 @@
           <t>행정학과 지방자치론은 일전에 하던 것이 있어서 인강은 듣지 않고 헌법, 행정법과 마찬가지로 계속 단원별 기출을 풀면서 감을 잃지 않았습니다.</t>
         </is>
       </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37101&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=90</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="55" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
@@ -5510,6 +6201,11 @@
       <c r="H139" s="3" t="inlineStr">
         <is>
           <t>행정학 : 뭔가 쉬운데 쉽지 않은 과목이라고 생각합니다. 행정학은 제가 전공했기 때문에 다른 분들보다 확실히 초반에 접근할 때 수월했던 게 사실입니다. 그래서 공부를 많이 하지 않고 시험을 봐도 75점에서 80점대는 유지했고 공부할 때 그렇게 많은 스트레스를 주진 않았던 것 같습니다. 하지만 필수과목이 되면서 그 전보다 확실히 난이도가 올라갔다고 느꼈습니다. 특히 지엽적인 문제빈도가 높아졌다고 느껴지면서 도대체 어디까지 준비해야하나 싶을 정도로 공부 방향성을 잡는 게 쉽지 않아졌다고 생각합니다. 하지만 일단 기본에 충실하면서 기출문제로 지엽적인 부분을 커버하면 어느정도 고득점을 맞는 데 어렵지 않다고 생각합니다. 그런 점에서 서현 선생님의 강의는 어떤 개념이 나오면 그 느낌이 연상되게 해주고 암기할 게 많은 행정학에서 최대한 암기하기 쉽게 해주는 부분이 많아서 좋았습니다.</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35911&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=114</t>
         </is>
       </c>
     </row>
@@ -5546,6 +6242,11 @@
           <t>2시간~3시간 가량 행정학 문제 오답, 개념서 복습, 모의문제 풀이, 암기 저녁 30분&amp; 국어 사자성어, 국어 한자, 영어 단어 및 숙어 암기 중 택1</t>
         </is>
       </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35789&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=119</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="55" customHeight="1">
       <c r="A141" s="3" t="inlineStr">
@@ -5584,6 +6285,11 @@
           <t>행정학 : 송상호 선생님 (95점) 행정학이 내용 자체도 어렵지만 제출될 수 있는 범위가 광범위하기 때문에 어느 부분에서 문제가 나올 지 감을 잡기 가장 어려운 과목이라고 생각합니다. 본인이 가장 설명을 잘 이해 할 수 있는 선생님을 선택하는게 중요하다고 생각하고 저는 송상호 선생님을 선택했습니다. 우선 선생님이 암기가 아닌 이해 위주의 수업을 해주시기 때문에 처음 공부하는 입장에서 배우기 수월했습니다. 앞 글자 따서 암기하는 것이 처음에는 편할 수 있지만 행정학은 휘발성이 너무 강한 과목이기에 이해를 바탕으로 공부해야 한다고 생각합니다.   국가직이 너무 지엽적인 문제들이 많이 나와서 지엽적인 것도 다 해야하나 고민을 많이하고 스트레스도 받았었는데 선생님께서 배운 지식을 강화하는게 중요하다는 말을 듣고 제가 아는 내용을 최대한 잊어 버리지 않기 위해 노력 하여 지방직에서 좋은 점수를 받을 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35713&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=121</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="55" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
@@ -5620,6 +6326,11 @@
       <c r="H142" s="2" t="inlineStr">
         <is>
           <t>보건행정학, 공중보건학 - 최성희 선생님 기본이론 강의 부터 기출강의까지 착실하게 따라갔고 선생님께서 개인적으로 만들어주시는 간단한 문제들과 시험문제처럼 만드신 문제들이 이론을 다시 돌아보는데 도움이 됐습니다. 전공은강의 말고 혼자 공부하는 시간을 훨씬 더 많이 할애해야한다고 생각합니다.  방대한 양과 외우기 힘든 수치들, 생소한 행정학 단어들 때문에 막막하겠지만 처음부터 세세히 외우려고 하기보단 책 읽듯이 처음부터 끝까지 읽어보고, 그 다음은 단어의 정의나 설명들을 구분해서 암기하고 천천히 세부적으로 들어가면서 여러번 회독한 후 기출문제 풀고 기출도 3~4회독정도 한다면 충분히 안정적인 점수를 받을 수 있을거라 생각합니다.</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41370&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
         </is>
       </c>
     </row>
@@ -5652,6 +6363,11 @@
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr"/>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40556&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=36</t>
+        </is>
+      </c>
     </row>
     <row r="144" ht="55" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
@@ -5690,6 +6406,11 @@
           <t>[행정학-송상호, 타학원 선생님] 네과목중 가장 저를 힘들게했던 과목이었습니다. 저는 이과출신이어서 다른 과목들도 물론 베이스가 없었지만 암기가 무엇보다 우선시되는 행정학은 내용도 방대하고 외울것이 정말 많아서 시험보기 직전까지도 가장 불안한 과목이었습니다. 하지만 행정법과 마찬가지로 최다빈출을 잡고가자는 생각으로 다빈출 지문이나 표는 포스트잇에 써서 책상앞에 붙여두고 공부에 집중이 안될때마다 한번씩 보고, 또 백지에 써보면서 외웠습니다. 사실 포스트잇에 써서 붙여놓기만 하면 잘 외우지 않게되어 공부가 하기 싫을때 노트를 꺼내서 한번씩 쭉 써보는 식으로 암기 했습니다. 또한 두문자를 따는 것이 암기가 필요한 행정학에 큰 도움이 되었다고 생각합니다. 상호쌤도 역시 예시를 잘 들어주셔서 초시생들이나 저같은 무베이스의 수험생들이 듣기에 적합한 강의라고 생각됩니다.</t>
         </is>
       </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36645&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=94</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="55" customHeight="1">
       <c r="A145" s="3" t="inlineStr">
@@ -5724,6 +6445,11 @@
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr"/>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41696&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="55" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
@@ -5760,6 +6486,11 @@
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>- 2024.07 ~ 2025.06 (약 1년)   2. 기본 베이스 지거국 영어영문학과 / 토익 900점대 후반 / 한능검 1급   3. 하루 루틴 수험 생활 초기에는 집 근처 도서관에서 공부를 했는데 집중이 잘 안 돼, 해커스 스파르타 독서실을 다녔습니다. 월요일부터 토요일까지는 아침 7시에 기상 후 아침 8시부터 밤 10시까지 독서실에서 공부했고 일요일은 쉬었습니다.   4. 공부 방향 공부 방향을 잘 설정하는 것이 단기 합격의 지름길이라고 생각합니다. 국어, 영어는 제가 자신 있어 하는 과목이었고 기초도 어느 정도 있었기 때문에 공부 시간을 최대한 줄이고 남는 시간을 한국사, 행정법, 행정학에 할애했습니다. 한국사 또한 제가 자신 있어 하는 과목으로 기초도 있었지만 국어, 영어와는 다르게 암기 과목이라 휘발성이 강해 공부량을 줄이지는 않았습니다. 공부 시간을 대략적으로 따져본다면 행정학 &gt; 행정법 &gt; 한국사 &gt; 영어 &gt; 국어 순으로 시간을 투자했습니다.   5. 과목별 공부법 국어 95점 국어는 학창 시절 열심히 했었기 때문에 자신 있는 과목이었습니다. 인사혁신처 예시 문제를 풀어보니 별다른 공부 없이도 충분히 풀 수 있는 난도여서 국어에 많은 시간을</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41522&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
         </is>
       </c>
     </row>
@@ -5792,6 +6523,11 @@
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr"/>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41511&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="55" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
@@ -5830,6 +6566,11 @@
           <t>2) 한국사(95점-이중석t)/행정법(90점-김대현t)/행정학(100점-김만희t)  암기 과목은 알면 풀고 모르면 못 풀기에..딱히 모의고사 연습의 필요성을 못 느꼈습니다. 인강도 딱 기본강의 들은 이후 정말 기본서를 회독하고 회독하고..시험 며칠 전에 전체 다 푸는데 얼마나 걸리나 시간 재보려고 모의고사 풀어본 것 빼고는 정말 시험 전날까지 기본서만 돌렸습니다. 행정학이 개인적으로 참 스트레스였는데 결국 시험날은 100점 받았네요.  강의는 각각 해커스에서 한국사 이중석 선생님, 행정법 김대현 선생님, 행정학 김만희 선생님 기본강의 수강했습니다.</t>
         </is>
       </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41480&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=5</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="55" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
@@ -5864,6 +6605,11 @@
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr"/>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41475&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=5</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="55" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
@@ -5906,6 +6652,11 @@
           <t>행정학: 서현쌤 기본,심화,기출 강의 다 수강함. 이거는 내용은 괜찮은데 외울게 진짜 너무 많고 방대해서 너무 막막해서 속이 답답했다. 하지만 정공법으로 그냥 강의도 공부다 생각하고 배속으로 듣고 그날 배운건 당일 복습하고 하니 기출까지 완강하니까 대충 뭔지 알겠어서 기출강의 끝나고는 서현쌤 기출문제집 무지성 회독함. 5회독 정도. 이것도 wox회독 나만의 변형버전으로 했음. 국가직때 65점 받고 충격 먹어서 지방직까지 열심히했더니 지방직은 95점 받음.</t>
         </is>
       </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41396&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="55" customHeight="1">
       <c r="A151" s="3" t="inlineStr">
@@ -5944,6 +6695,11 @@
           <t>먼저 국어는 신민숙 선생님의 강의를 수강하였습니다. '쉬운국어 한권으로 끝'이라는 수업을 통해 기본을 다졌고, 독해, 논리, 문법 각각의 '강화 시리즈'를 통해 국어 내의 각 카테고리별로 문제들을 풀어보며 실전 감각을 키웠으며, 이후 '신유형기출 333제'를 통하여 그동안의 기출문제들로 보는 신유형 문제들로서 문제를 푸는 것 자체에 익숙해지려고 노력하였습니다.   다음으로 영어는 비비안 선생님의 강의를 수강하였습니다. 제가 어렸을 때부터 영어과목을 좋아했던 편이라 기본 베이스는 어느 정도 있다고 생각했지만 공무원 시험에 합격하기 위해선 해당 시험을 위한 공부가 필요하다고 생각하여 '공무원 기출보카 4000+' 교재를 구매해 4번 정도 반복하여 외웠습니다. 해당 수업은 듣지 않았고 모르는 단어는 발음을 들어보며 입에 붙도록 웅얼거리며 외웠습니다. 이와 동시에 '공무원 영문법 합격생 필기노트' 수업을 수강하며 공무원 문법의 기본기를 탄탄하게 다지려 하였습니다. 이후에는 '비비안 올인원 영문법'을 들으며 다시 정리한다는 느낌과 회독의 느낌을 가졌고 동시에 '공무원 영어 구조 독해 007' 수업을 들으며 독해 실력 또한 키우고자 하였습니다. 앞선 수업들을 다 수강한</t>
         </is>
       </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41302&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=13</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="55" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
@@ -5986,6 +6742,11 @@
           <t>&lt;행정학&gt;  가장 난이도가 있다고 생각한 행정학부터 공부를 시작하였어요.  선택한 기본서는 송상호 선생님의 명품행정학 (1,2권) 이었고 탁월한 선택이었다고 생각합니다.  이론이 너무 방대하면 부담스럽고 간략하면 이해하기 어려운데 이 부분의 밸런스를 가장 잘 맞춘 교재여서  혼자 회독을 늘려갈때마다 행정학에 대한 자신감도 함께 올릴 수 있었습니다!  많은 문제를 풀어도 계속 모르는 이론이나 헷갈리는 부분들이 많았는데 그럴때마다  '모르는 것이 나와도 당황하지 말고 답을 찾아보자' 라는 마인드를 셋팅하기 위해 노력했어요.</t>
         </is>
       </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41279&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=14</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="55" customHeight="1">
       <c r="A153" s="3" t="inlineStr">
@@ -6024,6 +6785,11 @@
           <t>행정학/서현 선생님 강의가 좀 길고 방대합니다. 그러나 처음 듣는 사람이 듣기에는 어려움이 없습니다. 기본강의 들을떄는 이해가 되지 않더라도 귀에 익힌다는 생각으로 끝까지 완강을 하는것을 추천드립니다. 서현 선생님의 기출 문제집이 좋습니다. 기본강의 후 기출문제집을 계속 회독하면서 부족한 개념을 계속 암기하는 방법으로 공부하였습니다.</t>
         </is>
       </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41179&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="55" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
@@ -6062,6 +6828,11 @@
           <t>법과목 또한 너무 생소했고 또 남은 기간이 많지 않았기에 시작은 막막했습니다. 하지만 김대현 선생님은 컴팩트한 교재와 강의를 사용하시기에 현재 제 상황에 딱 맞는 선생님이였습니다. 행정법에서 가장 중요한 건 흐름을 알고 문제가 풀리는 그 순간까지 참고 버티고 공부해 나아가는 것 같습니다.. 처음에는 아무리 풀어보려해도 안 풀리는게 행정법이지만 나중에 효자과목이 된다는 이유를 알게 됐습니다. 국가직땐 행정법에 빠져서 많이 공부하고 풀다보니 국가직땐 65점 나와서 만족했지만 지방직까지 가는 과정중에 국가직 면접과 행정학 빵구 메우기 때문에 집중을 못해서 지방직땐 성적이 비록 떨어졌습니다. 그래서 행정법 또한 기본강의 듣고 회독하고 문제 풀며 어느정도 성적이 올라왔을때 계속 감을 유지하고 부족한 부분을 채워나가는 것이라 생각합니다. 단원만 보고 한 부분만 본다면 어려운 과목이지만 기본강의가 끝나고 여러번 회독 했을때 과목 전체를 보면 행정학보다 훨씬 효자과목이라 생각합니다(기출회독 필수)</t>
         </is>
       </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40996&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=26</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="55" customHeight="1">
       <c r="A155" s="3" t="inlineStr">
@@ -6096,6 +6867,11 @@
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr"/>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40670&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="55" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
@@ -6130,6 +6906,11 @@
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
         </is>
       </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="55" customHeight="1">
       <c r="A157" s="3" t="inlineStr">
@@ -6172,6 +6953,11 @@
           <t>행정법과 헌법은 황남기 선생님에게 의지했습니다. 교재가 너무 완벽해서 내용이 그 안에서 벗어나지 않았습니다. 역시 기본강의만 들었고, 곧바로 기출회독을 시작했고 이후 모의고사로 법과목을 공부했습니다. 특히 시험을 앞두고 나오는 최신판례 강의에서 그대로 문제가 나왔습니다.  법은 공부하면 하는만큼 나옵니다. 정말 정직합니다. 법에서 최대한 점수 챙긴다고 생각하고 메인으로 공부하세요. 절대 배신 안합니다. 저도 이번에 행정학에서 많이 까먹었지만 헌법 100점, 행정법 92점으로 선방해서 안정적으로 합격할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39624&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="55" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
@@ -6214,6 +7000,11 @@
           <t>행정학 : 송상호 선생님 저에게 가장 고통스러웠던 과목이었습니다. 행정법과 마찬가지로 쌩노베였지만 행정법과는 다르게 썰을 듣는다는 느낌이 아니라 학자들의 견해를 외워야 한다는 느낌이어서 가장 어렵게 다가왔습니다. 교재는 공무원 명품 행정학을 기본서로 이용했고 시험전까지 총 4회독을 하였습니다. 2회독을 한 이후 해커스 기출문제집을 2회독하고 마지막으로 기본서 2회독으로 마무리하였습니다.</t>
         </is>
       </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39106&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=52</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="55" customHeight="1">
       <c r="A159" s="3" t="inlineStr">
@@ -6252,6 +7043,11 @@
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr"/>
+      <c r="I159" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38957&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=56</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="55" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
@@ -6286,6 +7082,11 @@
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr"/>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38788&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=64</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="55" customHeight="1">
       <c r="A161" s="3" t="inlineStr">
@@ -6324,6 +7125,11 @@
           <t>공무원 준비는 부모님 권유로 시작하게 되었습니다. 하루 루틴은 국가직까지 3개월정도가 있었는데 하루에 3~4시간정도 공부했습니다. 국어,영어는 안하고 행정법,행정학,한국사 압축강의(행정법,한국사), 기본강의(행정학)만 봤습니다. 1,4,7,14복습법을 이때만 적용했습니다. 그래도 까먹었는데 깊은 잠재의식속에 남아있지 않았을까 생각됩니다.</t>
         </is>
       </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38757&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=65</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="55" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
@@ -6362,6 +7168,11 @@
           <t>특히, 동형모의고사의 경우 구할 수 있는 대로 구해서 양치기를 했는데, 외웠다고 생각했던 판례, 혹은 요약 되었거나, 전문이 나오면 틀리는 경우가 있었습니다. 하지만, 양치기를 통해 틀렸던 문제의 판례는 다시 기본서로 돌아와 공부하고, 중요한 쟁점, 혹은 자주 나오는 문구에 형광펜을 칠하고 외웠습니다. 아무래도 틀렸던 문제의 경우 기억에 더 잘 남아서, 형광펜 치고 다시 보았던 판례의 기억 저장 시간이 훨씬 길었습니다. 서현 선생님의 강의에서 가장 핵심이 되는 내용은 행정학적 마인드 같습니다. 사실 공부하는 내내 행정학적 마인드를 적립하는데 어려움이 있어서, 어떻게 해야 하지 고민이 많았지만, 강의노트 회독, 문제풀이를 하며 개념을 다잡고 그게 쌓이다 보니 저절로 적립이 가능했습니다.</t>
         </is>
       </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38729&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=66</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="55" customHeight="1">
       <c r="A163" s="3" t="inlineStr">
@@ -6404,6 +7215,11 @@
           <t>2. 베이스 국어 수능 3등급, 영어 수능 2등급 토익 800점대, 한국사 수능1 한국사검정시험1급, 행정법 행정학 처음 공부함</t>
         </is>
       </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38678&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=68</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="55" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
@@ -6440,6 +7256,11 @@
       <c r="H164" s="2" t="inlineStr">
         <is>
           <t>- 행정학 사회과학을 전공해서 베이스가 조금 있었습니다. 강의는 서현 선생님의 강의를 들었습니다. 정리도 깔끔하고 설명도 이해하기 쉬워서 추천드립니다. 전체적으로 무난하게 공부했던 과목입니다.</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36046&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=109</t>
         </is>
       </c>
     </row>
@@ -6472,6 +7293,11 @@
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr"/>
+      <c r="I165" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35634&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=124</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="55" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
@@ -6506,6 +7332,11 @@
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr"/>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35196&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=136</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="55" customHeight="1">
       <c r="A167" s="3" t="inlineStr">
@@ -6544,6 +7375,11 @@
           <t>- 2024.07 ~ 2025.06 (약 1년)   2. 기본 베이스 지거국 영어영문학과 / 토익 900점대 후반 / 한능검 1급   3. 하루 루틴 수험 생활 초기에는 집 근처 도서관에서 공부를 했는데 집중이 잘 안 돼, 해커스 스파르타 독서실을 다녔습니다. 월요일부터 토요일까지는 아침 7시에 기상 후 아침 8시부터 밤 10시까지 독서실에서 공부했고 일요일은 쉬었습니다.   4. 공부 방향 공부 방향을 잘 설정하는 것이 단기 합격의 지름길이라고 생각합니다. 국어, 영어는 제가 자신 있어 하는 과목이었고 기초도 어느 정도 있었기 때문에 공부 시간을 최대한 줄이고 남는 시간을 한국사, 행정법, 행정학에 할애했습니다. 한국사 또한 제가 자신 있어 하는 과목으로 기초도 있었지만 국어, 영어와는 다르게 암기 과목이라 휘발성이 강해 공부량을 줄이지는 않았습니다. 공부 시간을 대략적으로 따져본다면 행정학 &gt; 행정법 &gt; 한국사 &gt; 영어 &gt; 국어 순으로 시간을 투자했습니다.   5. 과목별 공부법 국어 95점 국어는 학창 시절 열심히 했었기 때문에 자신 있는 과목이었습니다. 인사혁신처 예시 문제를 풀어보니 별다른 공부 없이도 충분히 풀 수 있는 난도여서 국어에 많은 시간을</t>
         </is>
       </c>
+      <c r="I167" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41522&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="55" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
@@ -6586,6 +7422,11 @@
           <t>2) 행정학 90점: 해커스 김만희 선생님 행정학은 행정법과 반대로 처음엔 들을 만한데 시간이 지날수록 이게 공부가 되는 건가? 싶었습니다. 이번 지방직 시험 치는 주에 올해 국가직 문제를 풀어봤는데 행정학 때문에 이번엔 힘들겠구나 하고 들어갈 정도였습니다. 역시 행정법과 마찬가지로 5월부터 8월까지 개념강의를 들었지만 머리에 남는 게 없다고 느꼈습니다. 그리고 당시에 헌법 1회독을 같이 진행하던 차라 행정법보다 2회차가 늦어졌습니다. 행정학은 행정법처럼 3월부터 강의 다시 듣지 않고 복습-기출문제 풀기 방식으로 진행해서 6월 중순쯤 2회독을 마무리했습니다. 행정법과 마찬가지로 행정학도 느낌은 노베이스나 마찬가지긴 했지만 1회차를 했다는 게 알게 모르게 2회차에서 큰 도움이 됐습니다. 교재가 꽤 상세하게 개념을 다루고 있고 강의에서 처음에는 어느 것을 먼저 봐야 할지 잡아주시고 복잡한 용어를 실전개념으로 잘 풀어주셔서 도움이 많이 됐습니다. 특히 요약서인 또또북이 잘 정리되어 있는데 2회차 정도부터는 복습하면서 내용을 채워넣으면 단권화가 정말 잘 될 것으로 생각합니다. 저는 시험이 임박해서 또또북을 썼지만 초반부터 사용하면 더 효과가 좋았을 듯합니다. 1회차</t>
         </is>
       </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41486&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=5</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="55" customHeight="1">
       <c r="A169" s="3" t="inlineStr">
@@ -6628,6 +7469,11 @@
           <t>이전부터 여러 짧은 업무를 전전하면서 혹은 전공이외 여러 진로를 고민하던 도중 일반행정 공무원에 도전하기로 마음을 먹었습니다. 그러나 처음 생각을 했던 3~4년여간은 다른 일과 병행으로 사실상 큰 신경을 쓸 수 없었고, 본격적인 공부는 8개월 ~ 1년을 잡고 시작했습니다.   여러 과목이 있었지만 생소했던 과목인 행정학 행정법과 나중에 시험이 임박했을 때 단기적으로 끌어올리기 어려운 영어부터 시작해야 한다고 판단했습니다. 영어 단어는 적어도 이틀에 한 챕터를, 문법은 하루에 하나라도 알고가자는 느낌으로 하루 1시간 정도를 투자했고, 나머지 시간은 기본 강의를 듣는데 충실하려 했습니다. 다른 좋은 강의학원도 많았지만 적극적인 홍보와 집에서의 접근성으로 보아 해커스 패스를 선택하기로 하였습니다.</t>
         </is>
       </c>
+      <c r="I169" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41384&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="55" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
@@ -6662,6 +7508,11 @@
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr"/>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41365&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="55" customHeight="1">
       <c r="A171" s="3" t="inlineStr">
@@ -6696,6 +7547,11 @@
           <t>[공유하고 싶은 학습&amp;시험 꿀팁] 행정학은 서브 노트와 인덱스 카드로 저만의 요약집을 틈틈이 작업해두었습니다. 서브 노트는 주교재를 바탕으로 단원별로 큰 제목과 소제목을 다 적은 후에 계속 헷갈리는 개념들을 옆에 조금씩 적어가며 내용을 붙였습니다. 그래도 자꾸 틀리는 것들, 변수 등 낯설고 휘발성이 강한 내용들은 포스트잇에 적어 인덱스 카드에 서브노트 단원별 순서대로 옮겨 붙여서 독서실에서 집에 가는 동안 계속 눈에 익히려고 노력했습니다.</t>
         </is>
       </c>
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41354&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=11</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="55" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
@@ -6730,6 +7586,11 @@
         </is>
       </c>
       <c r="H172" s="2" t="inlineStr"/>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41345&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=11</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="55" customHeight="1">
       <c r="A173" s="3" t="inlineStr">
@@ -6768,6 +7629,11 @@
           <t>3. 행정학 - 서현 선생님 저는 서현 선생님 강의를 제일 열심히 본 것 같습니다. 행정학도 아예 처음보는 과목이라 감도 안 잡혔고, 직전 해에 아주 어려운 난이도로 나와 긴장이 됐었습니다. 하지만 행정학도 현 행정학 기본을 다 수강하고 본인 나름대로 단권화하여서 시간 날때마다 꾸준히 본다면 충분히 좋은 점수를 얻을 수 있습니다. 전 기본강의만 다보고 문제풀이로 넘어가 모의고사도 다 풀고, 한글 파일로 제가 직접 압축해서 무한 암기 반복했는데, 좋은 점수가 나올 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I173" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41283&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=14</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="55" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
@@ -6806,6 +7672,11 @@
           <t>◆행정학- 서현 선생님 개인적으로 행정학이 제일 어려웠습니다... 처음 접하는 개념들이 많은데 또 이것들이 두루뭉실하게 둥둥 떠다니는 느낌이랄까요... 시간이 없다고 판단해서 심화를 듣지 않고 기본이론에서 바로 기출문제풀이로 넘어갔는데, 고득점을 위해서라면 꼭... 심화를 들으시길... 시험 전에는 행정학 단권화 특강으로 전체적인 개념을 쓱 흝을 수 있어서 좋았습니다. 행정학도 외우지 않으면 못푸는 과목이라고 생각해서 시험이 가까워질 수록 개념과 법령등을 외우는 데 시간을 썼습니다.</t>
         </is>
       </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41205&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=18</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="55" customHeight="1">
       <c r="A175" s="3" t="inlineStr">
@@ -6840,6 +7711,11 @@
         </is>
       </c>
       <c r="H175" s="3" t="inlineStr"/>
+      <c r="I175" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41195&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=18</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="55" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
@@ -6878,6 +7754,11 @@
           <t>행정학 기본문제집보고 기겁했던게 엊그제 같네요. 강사님의 강의노트 덕분에 용기내서 시작했습니다. 요약이 정말 잘 되어있어요. 모든 강의 들을 때 강의노트 옆에 두고 들었습니다. 중요도도 체크해주셔서 복습할 때 그나마 순조로웠어요. 심화강의는 문제풀이 위주로 하시는데, 전 인강 들으면서 풀었습니다. 심화문제 단원별로 끝날 때마다 강의노트와 심화문제 번갈아보면서 복습했습니다. 신경향이론도 특강 강추합니다. 문제 여기서 많이 나왔어요. 배속 1.8</t>
         </is>
       </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41174&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="55" customHeight="1">
       <c r="A177" s="3" t="inlineStr">
@@ -6912,6 +7793,11 @@
         </is>
       </c>
       <c r="H177" s="3" t="inlineStr"/>
+      <c r="I177" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41129&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="55" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
@@ -6946,6 +7832,11 @@
           <t>제 하루 루틴은 오전 7시 기상 후 8시부터 12시까지 기본 이론 복습, 점심 후엔 1시부터 5시까지 문제 풀이, 저녁에는 오답 정리와 암기 위주로 복습하며 총 10시간 이상 공부했습니다. 필수 과목은 행정법과 행정학이었는데, 행정법은 조문과 판례 정리를 반복했고, 행정학은 기출 중심으로 흐름을 파악한 후 단권화를 통해 정리했습니다. 행정법은 처음 공부할 때에는 아무것도 모르고 공부해도 막막한 느낌이 들었지만, 익숙해지고 공부를 하다보니 제일 자신있는 과목이 되었습니다. 행정법이 어렵지만 여러분 할 수 있습니다. 국어는 고혜원 선생님의 문법 정리와 어휘 암기가 큰 도움이 되었고, 한국사는 최진우 선생님의 흐름 중심 강의로 이해력을 높일 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41060&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=24</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="55" customHeight="1">
       <c r="A179" s="3" t="inlineStr">
@@ -6982,6 +7873,11 @@
       <c r="H179" s="3" t="inlineStr">
         <is>
           <t>행정학: 서현 수강 강의 내역: 기본 강의, 기출 강의, 법령 특강 전시리즈, 하프 전시리즈, 실전 동형 강의</t>
+        </is>
+      </c>
+      <c r="I179" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40785&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
         </is>
       </c>
     </row>
@@ -7014,6 +7910,11 @@
         </is>
       </c>
       <c r="H180" s="2" t="inlineStr"/>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40692&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=31</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="55" customHeight="1">
       <c r="A181" s="3" t="inlineStr">
@@ -7044,6 +7945,11 @@
         </is>
       </c>
       <c r="H181" s="3" t="inlineStr"/>
+      <c r="I181" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40688&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="55" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
@@ -7078,6 +7984,11 @@
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr"/>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40670&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="55" customHeight="1">
       <c r="A183" s="3" t="inlineStr">
@@ -7112,6 +8023,11 @@
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
         </is>
       </c>
+      <c r="I183" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="55" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
@@ -7142,6 +8058,11 @@
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr"/>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39664&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="55" customHeight="1">
       <c r="A185" s="3" t="inlineStr">
@@ -7184,6 +8105,11 @@
           <t>행정법과 헌법은 황남기 선생님에게 의지했습니다. 교재가 너무 완벽해서 내용이 그 안에서 벗어나지 않았습니다. 역시 기본강의만 들었고, 곧바로 기출회독을 시작했고 이후 모의고사로 법과목을 공부했습니다. 특히 시험을 앞두고 나오는 최신판례 강의에서 그대로 문제가 나왔습니다.  법은 공부하면 하는만큼 나옵니다. 정말 정직합니다. 법에서 최대한 점수 챙긴다고 생각하고 메인으로 공부하세요. 절대 배신 안합니다. 저도 이번에 행정학에서 많이 까먹었지만 헌법 100점, 행정법 92점으로 선방해서 안정적으로 합격할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I185" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39624&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="55" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
@@ -7218,6 +8144,11 @@
         </is>
       </c>
       <c r="H186" s="2" t="inlineStr"/>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39078&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=52</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="55" customHeight="1">
       <c r="A187" s="3" t="inlineStr">
@@ -7256,6 +8187,11 @@
         </is>
       </c>
       <c r="H187" s="3" t="inlineStr"/>
+      <c r="I187" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38957&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=56</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="55" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
@@ -7290,6 +8226,11 @@
         </is>
       </c>
       <c r="H188" s="2" t="inlineStr"/>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38878&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=60</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="55" customHeight="1">
       <c r="A189" s="3" t="inlineStr">
@@ -7332,6 +8273,11 @@
           <t>2. 베이스 국어 수능 3등급, 영어 수능 2등급 토익 800점대, 한국사 수능1 한국사검정시험1급, 행정법 행정학 처음 공부함</t>
         </is>
       </c>
+      <c r="I189" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38678&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=68</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="55" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
@@ -7370,6 +8316,11 @@
           <t>5.행정학 서현 선생님 강의를 들었습니다. 행정학도 내용이 엄청 방대한데, 단권화 노트로 필요한 것만 볼 수 있어서 좋았습니다. 또한, 저같이 행정학을 전혀 모르는 공대생도 이해할 수 있도록 쉽고 자세히 설명해 주셔서 좋았습니다.</t>
         </is>
       </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38093&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=83</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="55" customHeight="1">
       <c r="A191" s="3" t="inlineStr">
@@ -7408,6 +8359,11 @@
           <t>- 행정학 : 서현 선생님 강의와 커리큘럼이 짜임새가 있습니다. 강의 경력도 워낙 기시고 전공자셔서 전문성은 말할 것도 없구요. 딕션이나 목소리도 좋으셔서 강의 듣는데에 매우 편했습니다. 입문-기본-심화-문풀-실전동형 이 5단계가 너무나도 튼튼하게 갖추어져 있어서, 커리큘럼대로만 꾸준히 따라가다 보면 서현 선생님이 수업 중 계속해서 강조하시는 행정학적인 마인드가 머리에 장착됩니다.강의의 특장점으로는 현 행정학 강의노트 라는 단권화 노트가 있는데, 따로 개인적으로 단권화할 필요 없이 300페이지 가량 되는 이 책에 강의 들으면서 꾸준히 개념 추가하고, 책정리 해가다 보면 80점 라인 방어하는 데에는 차고 넘칩니다. 기본심화 강의 진행도 기본서는 서브로 하고 이 강의노트 위주로 해 주셔서, 방대한 행정학의 분량을 획기적으로 줄여서 기본을 쌓아올리는 데에 큰 도움이 된 것 같습니다.</t>
         </is>
       </c>
+      <c r="I191" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36748&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="55" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
@@ -7446,6 +8402,11 @@
           <t>행정학 서현 교수님 강의를 들었습니다. 기본서 위주의 공부가 아닌 필기노트를 따로 사서 필기노트 위주로 하는 강의였는데 사람마다 호불호가 갈릴 법한 학습방법이란 생각이 들었습니다. 하지만 두꺼운 기본서를 단권화로 양을 줄여 자주 보는 것은 공부의 중요한 과정이니 저는 나쁘지 않은 방식이라 느꼈습니다.</t>
         </is>
       </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36138&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=106</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="55" customHeight="1">
       <c r="A193" s="3" t="inlineStr">
@@ -7484,6 +8445,11 @@
           <t>행정학 (90점) 김만희 선생님 기본이론을 먼저 수강하였고, 이후에 기출 문제집 회독하다가 서현 선생님 모의고사 수강했습니다. 행정학은 하나의 문제집을 여러 번 회독하는 것보다는 여러 문제집을 보며 다양한 표현들을 익히는 게 중요한 것 같습니다. 처음보는 단어나 문제가 등장해도 어떻게 풀어나갈지 요령을 익히는 게 필요해요.</t>
         </is>
       </c>
+      <c r="I193" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40498&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=38</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="55" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
@@ -7522,6 +8488,11 @@
           <t>공무원 준비는 부모님 권유로 시작하게 되었습니다. 하루 루틴은 국가직까지 3개월정도가 있었는데 하루에 3~4시간정도 공부했습니다. 국어,영어는 안하고 행정법,행정학,한국사 압축강의(행정법,한국사), 기본강의(행정학)만 봤습니다. 1,4,7,14복습법을 이때만 적용했습니다. 그래도 까먹었는데 깊은 잠재의식속에 남아있지 않았을까 생각됩니다.</t>
         </is>
       </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38757&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=65</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="55" customHeight="1">
       <c r="A195" s="3" t="inlineStr">
@@ -7556,6 +8527,11 @@
         </is>
       </c>
       <c r="H195" s="3" t="inlineStr"/>
+      <c r="I195" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41900&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="55" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
@@ -7590,6 +8566,11 @@
           <t>3. 나의 수험 계획표 다양한 방법들을 시도해보았지만, 저는 앞서 말했던 것처럼 하루에 4과목을 전부 보는 방식이 저에게 잘 맞아서 그렇게 진행했습니다. 우선 공부는 8시 이전에 열품타 착석스터디를 통해 스스로를 컨트롤 하며 시작했습니다. 행정학 2시간(이때 말하는 시간은 최소 시간입니다. 인강이나 문풀 상황에 따라 10-15분 정도는 더 진행할 때가 많습니다) -&gt; 행정법 1시간 -&gt; 약 12시쯤 점심식사 및 식곤증을 물리치기 위한 샤워 등 재정비 -&gt; 2시 쯤. 경제학 2시간 (그나마 손을 가장 많이 써서 덜 졸려서 이걸 이때 했습니다) -&gt; 1시간 정도 행정법 추가 공부 -&gt; 6시쯤 저녁 식사 후 휴식 -&gt; 2시간 동안 헌법 마무리</t>
         </is>
       </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41729&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="55" customHeight="1">
       <c r="A197" s="3" t="inlineStr">
@@ -7628,6 +8609,11 @@
           <t>1) 4월~6월 : 기본 이론 강의 수강 행정법, 헌법 (홍대겸)/ 행정학 (서현) 기본 강의를 수강하였습니다. 두 분을 선택한 계기는 좀 불순한데, 일단 교재가 없어도 수업을 들을 수 있게 판서 혹은 PPT를 활용하는 수업방식이 마음에 들었습니다. 불순한 계기와 달리, 결과적으로 두 분을 선택하여서 좋은 결과를 얻을 수 있었습니다. 홍대겸 선생님의 가장 큰 장점이자 매력은 컴팩트함입니다. 법학을 이해하는 데 필요한 기본적인 논리는 놓치지 않고 설명해주시되 디테일을 과감하게 생략하며 빠르게 진도를 나가시는 타입이십니다. 그래서 강의 회차와 시간 모두 짧습니다. 가볍고 빠르게 나아가는 수업은 빠르게 기본 이론을 배우고 싶었던 당시의 저에게는 최고의 선택이었습니다. 설명도 가능한 직관적이고 단정적으로 하셔서 법학이 까다롭고 어렵다는 선입견을 깨시고 부담을 많이 덜어주셨습니다. "빠른 1회독" 강의도 큰 도움이 되었습니다. 기초 이론을 가볍게 맛본 수험생을 대상으로 하는 강의인데, 기초 강의 때는 생략하였던 변칙적인 판례를 설명해주시기도 하고, 말 그대로 빠르게 행정법 전체를 복습할 수 있습니다. 서현 선생님의 장점은 체계성입니다. 그동안의 기출 경향을 모두 꿰고</t>
         </is>
       </c>
+      <c r="I197" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41687&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="55" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
@@ -7662,6 +8648,11 @@
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr"/>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41427&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="55" customHeight="1">
       <c r="A199" s="3" t="inlineStr">
@@ -7696,6 +8687,11 @@
         </is>
       </c>
       <c r="H199" s="3" t="inlineStr"/>
+      <c r="I199" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41426&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="55" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
@@ -7734,6 +8730,11 @@
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr"/>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41409&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=8</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="55" customHeight="1">
       <c r="A201" s="3" t="inlineStr">
@@ -7768,6 +8769,11 @@
         </is>
       </c>
       <c r="H201" s="3" t="inlineStr"/>
+      <c r="I201" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41372&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="55" customHeight="1">
       <c r="A202" s="2" t="inlineStr">
@@ -7802,6 +8808,11 @@
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr"/>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41371&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="55" customHeight="1">
       <c r="A203" s="3" t="inlineStr">
@@ -7836,6 +8847,11 @@
         </is>
       </c>
       <c r="H203" s="3" t="inlineStr"/>
+      <c r="I203" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41368&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="55" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
@@ -7870,6 +8886,11 @@
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr"/>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41360&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="55" customHeight="1">
       <c r="A205" s="3" t="inlineStr">
@@ -7908,6 +8929,11 @@
         </is>
       </c>
       <c r="H205" s="3" t="inlineStr"/>
+      <c r="I205" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41337&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=12</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="55" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
@@ -7946,6 +8972,11 @@
         </is>
       </c>
       <c r="H206" s="2" t="inlineStr"/>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41329&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=12</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="55" customHeight="1">
       <c r="A207" s="3" t="inlineStr">
@@ -7980,6 +9011,11 @@
         </is>
       </c>
       <c r="H207" s="3" t="inlineStr"/>
+      <c r="I207" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41322&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=12</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="55" customHeight="1">
       <c r="A208" s="2" t="inlineStr">
@@ -8014,6 +9050,11 @@
         </is>
       </c>
       <c r="H208" s="2" t="inlineStr"/>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41309&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=13</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="55" customHeight="1">
       <c r="A209" s="3" t="inlineStr">
@@ -8048,6 +9089,11 @@
         </is>
       </c>
       <c r="H209" s="3" t="inlineStr"/>
+      <c r="I209" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41280&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=14</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="55" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
@@ -8082,6 +9128,11 @@
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr"/>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41270&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="55" customHeight="1">
       <c r="A211" s="3" t="inlineStr">
@@ -8116,6 +9167,11 @@
         </is>
       </c>
       <c r="H211" s="3" t="inlineStr"/>
+      <c r="I211" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41269&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="55" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
@@ -8146,6 +9202,11 @@
         </is>
       </c>
       <c r="H212" s="2" t="inlineStr"/>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41254&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="55" customHeight="1">
       <c r="A213" s="3" t="inlineStr">
@@ -8176,6 +9237,11 @@
         </is>
       </c>
       <c r="H213" s="3" t="inlineStr"/>
+      <c r="I213" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41244&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=16</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="55" customHeight="1">
       <c r="A214" s="2" t="inlineStr">
@@ -8218,6 +9284,11 @@
           <t>안녕하세요 공부를 시작한 날이 엊그제 같은데 합격 수기를 쓰고 있으니 감회가 새롭습니다. 학창시절 공부를 썩 잘하는 편이 아니었어서 국어 영어 행정학 행정법 4과목은 노베이스로 시작했고, 한국사는 그나마 학창시절에 좋아하던 과목이었어서 기억이 따로 잘 나는 건 아니지만 즐겁게 공부했습니다</t>
         </is>
       </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41237&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=16</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="55" customHeight="1">
       <c r="A215" s="3" t="inlineStr">
@@ -8260,6 +9331,11 @@
           <t>행정학 - 김만희 선생님, 행정학을 3개월만에 마스터해야하는 상황에 막막해 있다가 마니쌤의 OT를 듣고 믿고 따르기로 결정했습니다. 기본이론, 기필코 실력업, 파이널600제 3회독하고 모든 특강을 들었습니다. 600제 2회독 + 스스로 1회독 하니까 어느정도 행정학이 눈에 들어왔고 선생님께서 올해 중요하게 생각하시는 부분들은 보고 또 봤습니다. 시험 전날 푼 작년 지방직문제가 50점정도라 역시 3개월가지고는 되지 않으려나 했지만 시험장에서 문제를 보는데 술술풀렸고 정말 선생님께서 말씀하신 문제가 그대로 나왔습니다. 감탄을 하며 시험을 본 기억이 있습니다ㅎㅎ 저는 행정학은 무조건 마니쌤 추천합니다. 그리고 추가로 또또북은 정말 요물입니다!</t>
         </is>
       </c>
+      <c r="I215" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41232&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="55" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
@@ -8294,6 +9370,11 @@
         </is>
       </c>
       <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41198&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=18</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="55" customHeight="1">
       <c r="A217" s="3" t="inlineStr">
@@ -8324,6 +9405,11 @@
         </is>
       </c>
       <c r="H217" s="3" t="inlineStr"/>
+      <c r="I217" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41194&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="55" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
@@ -8358,6 +9444,11 @@
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41160&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=20</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="55" customHeight="1">
       <c r="A219" s="3" t="inlineStr">
@@ -8392,6 +9483,11 @@
         </is>
       </c>
       <c r="H219" s="3" t="inlineStr"/>
+      <c r="I219" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41134&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="55" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
@@ -8426,6 +9522,11 @@
         </is>
       </c>
       <c r="H220" s="2" t="inlineStr"/>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41102&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=22</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="55" customHeight="1">
       <c r="A221" s="3" t="inlineStr">
@@ -8460,6 +9561,11 @@
         </is>
       </c>
       <c r="H221" s="3" t="inlineStr"/>
+      <c r="I221" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41091&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=22</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="55" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
@@ -8496,6 +9602,11 @@
       <c r="H222" s="2" t="inlineStr">
         <is>
           <t>행정학은 제 전공인지라 학습을 하는 데 있어서 크게 어려움이 없었습니다. 전공 학점도 4점대로 항상 잘 맞아왔기 때문에 한 번씩 들어봤던 용어와 내용인지라 노베이스이신 분들보다는 좀 수월하게 공부했던 것 같습니다. 송상호 선생님은 수업 때도 공부할 것들만 딱 알려주시면서 수업하시고, 최근의 출제 경향까지 알려주시면서 수업해주셔서 강약조절을 할 수 있었습니다. 저는 기본강의와 심화강의를 듣고, 기출문제와 신경향테마, 그리고 모의고사까지 커리큘럼을 따라가며 행정학 학습을 했습니다.</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41079&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=23</t>
         </is>
       </c>
     </row>
@@ -8532,6 +9643,11 @@
           <t>5.행정학 첫 시험에서 거의 과락인 점수를 맞고 기출을 제일 많이 돌렸던 과목이에요  너무 지루하지만 반복하다보니 답을 고르는 요령이 생기더라구요  그리고 행정학은 기출에 모의고사도 추가로 하시면 좋아요!!</t>
         </is>
       </c>
+      <c r="I223" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41046&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=24</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="55" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
@@ -8570,6 +9686,11 @@
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr"/>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41035&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=25</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="55" customHeight="1">
       <c r="A225" s="3" t="inlineStr">
@@ -8604,6 +9725,11 @@
         </is>
       </c>
       <c r="H225" s="3" t="inlineStr"/>
+      <c r="I225" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41028&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=25</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="55" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
@@ -8642,6 +9768,11 @@
         </is>
       </c>
       <c r="H226" s="2" t="inlineStr"/>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40963&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=28</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="55" customHeight="1">
       <c r="A227" s="3" t="inlineStr">
@@ -8676,6 +9807,11 @@
         </is>
       </c>
       <c r="H227" s="3" t="inlineStr"/>
+      <c r="I227" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40778&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="55" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
@@ -8710,6 +9846,11 @@
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr"/>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40707&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=31</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="55" customHeight="1">
       <c r="A229" s="3" t="inlineStr">
@@ -8744,6 +9885,11 @@
         </is>
       </c>
       <c r="H229" s="3" t="inlineStr"/>
+      <c r="I229" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40466&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=40</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="55" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
@@ -8782,6 +9928,11 @@
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr"/>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39770&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="55" customHeight="1">
       <c r="A231" s="3" t="inlineStr">
@@ -8820,6 +9971,11 @@
           <t>오후 3시~4시 30분에는 체력관리와 외부 공기룰 쐬고자 집 앞 공원을 가볍게 뛰고 헬스를 했습니다. 저녁식사 후에는 법 과목과 행정학의 다음날 진도 초반을 용어는 대충 들어보자 하는 마음으로 예습을 시간이 허락하는 만큼 했습니다. - 국어 신민숙 선생님: 처음에는 문법 위주로 강의를 진행하셨습니다. 불규칙한 품사들을 필기해주셨는데 도움이 많이 되었습니다. 문학과 비문학의 경우 제가 속독에 어려움을 느껴 선생님께서 지정해주신 시간 안에 겨우 맞춰 풀었었는데 알려주신 속독 방법을 적용하니 시간이 남아 다시 체크할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I231" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39340&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=49</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="55" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
@@ -8862,6 +10018,11 @@
           <t>올해 : 국어 95 영어 85 한국사 95 행정법 90 행정학 75 코로나 기간에 공시를 시작해서 1달만에 초시를 보고, 작년엔 1년을 열심히 공부했지만 재시에서 면탈했습니다. 그래서 시험은 총 3번을 봤고, 두번째 면접에서 보통을 받아 올해 지방공무원 행정 9급 발령을 받았습니다.</t>
         </is>
       </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39325&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=49</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="55" customHeight="1">
       <c r="A233" s="3" t="inlineStr">
@@ -8900,6 +10061,11 @@
           <t>2024 서울시 일반행정 9급 최종합격 수기입니다.   저의 수험생활은 약 1년 8개월 정도였습니다. 저는 필기 점수가 커트라인보다 1점이 높았기에 면접에도 혼신의 힘을 기울였습니다. 최종발표 때까지 안심을 할 수 없었기에 초조한 마음으로 발표를 기다린 것이 생각납니다.   필기의 경우에는 한국사는 베이스가 있었기에, 나머지 4과목에 시간을 많이 할애하였고, 한국사는 토, 일요일에 기출문제 중심으로 감을 잃지 않게 공부를 하였습니다.   국어는 비문학은 상대적으로 자신이 있었기에, 문법에 시간을 많이 투자하였고, 한자도 틈틈이 짬을 내어 보았습니다. 강의는 신민숙 선생님 강의를 수강하였습니다.   영어는 크게 단어, 문법, 독해로 나누어서 2:3:5의 비율로 공부하였습니다. 비비안 선생님 강의를 들었는데, 큰 도움이 되었습니다. 단어의 경우에는 독해를 하면서 모르는 단어를 중심으로 파생단어까지 공부를 하였는데 괜찮은 효율성을 보인 것 같습니다.   한국사는 이중석 선생님의 기출문제만을 보았습니다.   행정법은 함수민 선생님 강의를 3회독 한 후, 기출문제 강의를 들었습니다. 처음에는 난해하였지만 회독이 늘어날수록 틀이 잡혀서 효자 과목이 되었습니다.   행정</t>
         </is>
       </c>
+      <c r="I233" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39256&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=50</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="55" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
@@ -8942,6 +10108,11 @@
           <t>행정학 - 서현 현 행정학 강의노트에 잘 정리되어있으니까 수업 들으시면서 필요한 내용만 따로 정리하면 됩니다. 기본강의에 충실하시길 바랍니다. 심화강의에서도 기본강의에서 다루신 내용들 그대로 다시 해주셔서 공부하기 편했어요. 기출문제집의 문제 양이 정말 많은데, 저는 세 번 정도 풀었어요. 여러번 풀어도 틀리는 문제는 계속 틀리더라고요. 어제 틀린 문제를 오늘 또 틀리지 않도록, 문제 자체보다는 선지를 하나하나 꼼꼼히 분석하는 게 중요하다고 생각해요. 행정학은 사실 제가 제일 어려워하는 과목이었어요. 2024 지방직 시험이 많이 어려웠어서 솔직히 말하면 마킹 도중에 울었습니다...ㅎㅎ 공부하지 못한 내용을 너무 많이 물어봐서 아쉬웠고, 성적도 많이 낮았지만 역시 다같이 어려웠나봐요.</t>
         </is>
       </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39185&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=51</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="55" customHeight="1">
       <c r="A235" s="3" t="inlineStr">
@@ -8980,6 +10151,11 @@
           <t>23년도 6개월 동안은 서현 선생님 커리를 따랐고, 23년 9월부터 24년 6월 마지막 시험까지는 송상호 선생님 커리를 따랐습니다. 서현 선생님은 두문자를 따주셔서 암기할 때는 도움이 되었습니다만, 배워야하는 이론의 범위가 넓어지면서 그 시험의 추세에는 송상호 선생님의 커리가 도움이 되겠다고 판단하여 선생님을 바꾸어 수강하였습니다. 결론적으로는 맞는 판단을 하였고, 행정학에서 중점되는 이론을 바탕으로 관련 이론으로 확장하여 가르쳐주시기 때문에 처음보는 이론들이라도 당황하지 않고 비슷하게 적용하여 풀어낼 수 있었습니다.   [마치면서] 대부분의 수험생들은 시험을 준비하는 동안에는 쉬어도 마음이 편하지 않아 마음껏 휴식을 취할 수도 없고, 공부를 하면서도 뒤쳐지고 있다는 불안함의 연속일 것이라 생각합니다. 하지만 공부를 더 오래 집중하기 위해서는 잘 쉬는 것 또한 필수이기 때문에 휴식에 너무 큰 죄책감을 가지지 않으면 좋겠습니다.  커뮤니티에 보면 ‘시험 준비 중인데 해외여행가도 될까요?’ ‘주말에 하루종일 쉬었어, 망했다ㅠㅠ’ 라는 글을 종종 보곤했는데, 공부가 너무 안되는 때면 당연히 뇌에도 휴식을 줘야하고, 또 그렇게 푹 쉬어줘야 그 다음날 더 집중해서 공</t>
         </is>
       </c>
+      <c r="I235" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39082&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=52</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="55" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
@@ -9018,6 +10194,11 @@
           <t>3. 공부법&amp; 수강한 선생님  특별히 저만의 공부법이라 할만큼 독특한 무언가를 하지는 않고 거의 대부분 학원의 커리큘럼을 따라갔습니다. 행정법과 행정학은 매년 조금씩 새로운 내용이 나오기 때문에 작년 시험을 대비했었음에도 올해 또 기본과정부터 복습하는 기분으로 순서대로 다시 들었고, 국어의 경우 매년 크게 변하는 것이 없기 때문에 저에게 부족한 부분인 어법과 어휘 위주로 들었습니다.  행정법은 홍대겸 선생님의 과정을 쭉 따라 들었는데 정말 이해하기 쉽게 설명해주시고 재밌어서 좋았습니다. 또 단원별 기출문제집이 얇은 편이라 공부 부담이 적고, 빈출 위주로 구성되어 있어 기본기를 확실히 다지기가 좋았습니다.  행정학의 경우 서현 선생님과 송상호 선생님의 강의를 섞어 들었는데, 신경향 문제가 튀어나오는 것이 신경쓰여 최대한 다양한 이론들을 접하고 싶었기 때문입니다. 시험이 다 끝난 뒤 이리저리 시행착오를 겪었던 것들을 되짚어 생각해보니 신경향도 아주 무시할 수는 없지만 가장 중요한 건 기출문제의 완전한 숙달인 것 같습니다.  국어는 신민숙 선생님의 강의를 통해 준비했습니다. 어휘와 어법은 분량이 방대하다고 생각하는데 선생님이 가장 필요한 부분만 고르고 골라 꼼꼼히</t>
         </is>
       </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39063&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=52</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="55" customHeight="1">
       <c r="A237" s="3" t="inlineStr">
@@ -9056,6 +10237,11 @@
           <t>각 과목을 3회독 정도 했을 경우 어느 정도 중요사항들은 까먹지 않게 되었고 그 이후에는 기출문제를 풀면서 암기내용을 다시 재점검했습니다. 강의는 국어 신민숙 선생님, 영어 비비안 선생님, 행정법 황남기 선생님, 한국사 이중석 선생님, 행정학 서현 선생님 황남기 선생님 기본 개념강의를 듣고 판례 내용만 따로 타이핑 해 뽑아서 들고다니면서 외웠습니다. 행정법의 경우 90% 이상은 판례에서 출제된다고 생각합니다 개념이 많이 어렵더라도 반복해서 접하다 보면 자연스럽게 개념이 이해되었던 것 같습니다.</t>
         </is>
       </c>
+      <c r="I237" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39003&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=54</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="55" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
@@ -9090,6 +10276,11 @@
         </is>
       </c>
       <c r="H238" s="2" t="inlineStr"/>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38989&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=55</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="55" customHeight="1">
       <c r="A239" s="3" t="inlineStr">
@@ -9124,6 +10315,11 @@
           <t>행정학 75 행정학은 한 강사분들을 커리를 타다가 다른 강사님들로 이동하면서 들어서 잘 설명드리기는 어렵지만 이번시험을 통해서 깨달은 것은 기출로 풀수 있는 점수는 확실히 확보한다면 어렵고 지엽적인 문제를 틀려도 합격하는 데에는 큰 요인으로 작용하지 않는다는 것입니다. 왜냐하면 다른 사람들도 다 같이 틀리기 때문입니다. 그러니까 기출을 확실히 정복하는 것이 중요하다고 생각합니다</t>
         </is>
       </c>
+      <c r="I239" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38948&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=57</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="55" customHeight="1">
       <c r="A240" s="2" t="inlineStr">
@@ -9154,6 +10350,11 @@
         </is>
       </c>
       <c r="H240" s="2" t="inlineStr"/>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38942&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=57</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="55" customHeight="1">
       <c r="A241" s="3" t="inlineStr">
@@ -9188,6 +10389,11 @@
         </is>
       </c>
       <c r="H241" s="3" t="inlineStr"/>
+      <c r="I241" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38940&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=57</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="55" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
@@ -9226,6 +10432,11 @@
           <t>-공유하고 싶은 학습 &amp; 시험 꿀팁 : 일단 기본적으로 암기할 건 확실하게 암기를 해줘야 합니다. 국어에서 쉬워졌다고는 하지만 한자나 맞춤법을 외워주고, 영어는 영어단어를 기본으로 문법을 확실히 외워줘야 합니다. 한국사의 경우에는 암기가 당연히 기본이지만 스토리를 생각하며 공부를 하면 시대순도 자연스럽게 학습이 되기 때문에 스토리텔링을 하면서 공부하시면 좋을 거에요. 행정법이나 행정학은 사실 다른 방법이 없습니다. 전공자가 아니라면 정석대로 숙달될때까지 무한 반복을 하셔야 원하는 점수대를 얻으실 수 있을 것입니다.</t>
         </is>
       </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38880&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=60</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="55" customHeight="1">
       <c r="A243" s="3" t="inlineStr">
@@ -9264,6 +10475,11 @@
           <t>2024년도 공무원 시험에 합격하면서 그동안의 노력을 돌아보고, 합격을 준비하는 분들께 조금이나마 도움이 되고자 저의 합격 수기를 공유합니다. 제가 주로 수강한 강좌는 서현 선생님의 행정학 강의, 홍대겸 선생님의 행정법 강의, 그리고 이중석 선생님의 한국사 강의였습니다.</t>
         </is>
       </c>
+      <c r="I243" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38871&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=60</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="55" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
@@ -9302,6 +10518,11 @@
           <t>마지막으로 행정학은 서현 강사님 강의를 들었습니다. 서현 강사님의 가장 큰 장점은 각 주제마다 시험 빈도를 알려주시고 중요도를 정확히 정해주신다는 점이라고 생각합니다. 그래서 공부를 할 때 어느 부분을 집중적으로 해야하는지 알 수 있었습니다. 또한 어려울 수 있는 행정학 내용을 이해하기 쉽게 가르쳐주시고, 기본강의와 심화강의가 나누어져 있어서 좋았습니다.</t>
         </is>
       </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38812&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=63</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="55" customHeight="1">
       <c r="A245" s="3" t="inlineStr">
@@ -9336,6 +10557,11 @@
       </c>
       <c r="G245" s="3" t="inlineStr"/>
       <c r="H245" s="3" t="inlineStr"/>
+      <c r="I245" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38805&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=63</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="55" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
@@ -9370,6 +10596,11 @@
         </is>
       </c>
       <c r="H246" s="2" t="inlineStr"/>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38774&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=64</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="55" customHeight="1">
       <c r="A247" s="3" t="inlineStr">
@@ -9400,6 +10631,11 @@
         </is>
       </c>
       <c r="H247" s="3" t="inlineStr"/>
+      <c r="I247" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38713&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=67</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="55" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
@@ -9434,6 +10670,11 @@
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr"/>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38652&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=69</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="55" customHeight="1">
       <c r="A249" s="3" t="inlineStr">
@@ -9472,6 +10713,11 @@
           <t>&lt;행정학&gt;  서현 선생님 커리큘럼을 쭈욱 따라갔어요. 사실 이번에 합격한 지방직에서는 높은 점수를 받지 못했지만 정말 깔끔하고 체계적인 수업이었구나를 느낀게 두달간 기본 이론 / 심화 이론 이렇게 이론 수업을 빠르게 마치고 국가직 시험을 연습삼아 보았을 때 무려 80점이라는 성적을 받을 수 있었던 것을 보고 행정학이라는 과목은 이대로만 하면 되겠구나 싶기도 했습니다. 법령특강 수업해주시는 것도 도움을 많이 받았습니다! 무료강의이니 꼭 들어보시길 추천해요.</t>
         </is>
       </c>
+      <c r="I249" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38649&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=69</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="55" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
@@ -9510,6 +10756,11 @@
           <t xml:space="preserve">국어 – 신민숙쌤 커리 (90점) 커리대로 선생님이 하라는 대로 하면 실력 느실 거에요! 비문학는 거의 매일 3문제씩 풀려고 노력했고 한자성어300으로 사자성어만이라도 마스터했습니다. 저는 타학원 선생님들 것도 이것저것 많이 푸는 게 도움이 됐어요! 여러 문제지를 접해야 실제 시험에서 당황하지 않게 되더라구요.  영어 – 김송희쌤 커리 (90점) 영어는 쌩노베입니다! 그래서 합격이 오래 걸렸어요ㅜ 문법은 진짜 송희쌤이 도움이 많이 됐습니다. 저는 매일 하루도 안 빠지고 하프로 감을 잃지 않게 매일 풀었습니다.(제일 중요!) 점수에 연연해하지 마시고 꼭 오답만 철저히 하세요. 그리고 전 단어암기에 약해서 무슨 기출보카 4000 이런 건 거의 안 보고 정말 타학원에 콤팩트한 필수단어 100개만 외웠습니다. 이렇게만 외워도 저는 단어가 커버돼서 그런 거니까 따라하지는 마세요ㅜㅜ  한국사 – 이중석쌤 커리 (95점) 강의가 너무 재밌어서 지루하지 않았어요. 하지만 한국사 점수가 증말 안 나와서 꽤 고생했어요... 그래서 그냥 무식하게 외우고 기출 몇 십번 봤습니다. 기출 중요!!!!! 기화펜으로 여러번 푸는 게 짱! 어느 정도 기출이 익숙해지면 꼭 모의고사 여러개 </t>
         </is>
       </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38624&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=70</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="55" customHeight="1">
       <c r="A251" s="3" t="inlineStr">
@@ -9544,6 +10795,11 @@
         </is>
       </c>
       <c r="H251" s="3" t="inlineStr"/>
+      <c r="I251" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38587&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=72</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="55" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
@@ -9582,6 +10838,11 @@
           <t>2년 간의 교육행정직을 준비했지만 합격이 정말 힘들었습니다. 솔직히 2년 준비를 끝으로 포기하려고 했지만 딱 1년만 더 해보자라는 마음으로 일반행정으로 직렬을 바꿔 도전하게 되었습니다. 국어 신민숙 선생님 강의를 들었습니다. 대학 전공수업으로 한자를 배웠어서 한자는 걱정하지 않았습니다. 공부하기 싫을 때는 한자성어 300책 한 번씩 훑으며 눈으로 익혔습니다. 제일 걱정했던 것은 문법이었는데 선생님이 쉽고 깔끔하게 가르쳐주셔서 문제에 적용하기 쉬웠습니다. 선생님 덕분에 좋은 점수를 맞을 수 있었습니다. 한국사 한국사는 이중석 선생님을 듣기 전과 후로 나뉠정도로 정말 큰 도움이 되었습니다. 수업 시작 전 읽어주시는 시도 정말 좋았고 수업도 정말 재밌고 오래 기억할 수 있었습니다. 저는 오히려 강의수가 많은게 꼼꼼하고 천천히 배울 수 있어서 좋았습니다. 좋은 말씀도 많이 해주셔서 수험기간동안 흔들리지 않고 공부할 수 있었습니다. 영어 비비안 선생님 강의를 들었습니다. 초반에는 여러 선생님 강의를 듣다가 비비안 선생님으로 정착했습니다. 완전 노베이스였는데 선생님 강의 들었던게 큰 도움이 되었습니다. 꾸준히 조금씩이라도 문제 푸는게 도움이 되더라구요 행정법 함수민 선</t>
         </is>
       </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38539&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=73</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="55" customHeight="1">
       <c r="A253" s="3" t="inlineStr">
@@ -9624,6 +10885,11 @@
           <t>5과목 공부에 대해 말씀드리면, 일단 영어는 베이스가 어느정도 있어서 계속 안하고 있다가 마지막 1년째에 비비안선생님 문법,구문독해,어휘강의를 들었습니다(어휘강의는 10회독). 비비안선생님은 시험에 나올 주제들을 여러번 반복해주셔서 잊어버리지 않게끔 도움을 주셨습니다. 국어는 문법과 한자 위주로 했었는데요, 신민숙 선생님의 문법 암기법과 한자성어 특강이 정말 좋았습니다. 최정선생님의 고전시가 특강도 좋았구요. 한국사는 제가 이해를 중요시해서 이중석선생님 올인원강의를 들었다가 암기도 강의로 해결해야할 것 같아서 이명호선생님 기본강의를 추가로 들었습니다. 두 분 다 각자의 분야에서 정말 훌륭한 선생님들이십니다. 행정법과 행정학은 너무 어려워서 울면서 공부했던 과목인데요, 먼저 행정법은 친절한 설명을 해주시는 강의를 듣고 싶어서 함수민 선생님 강의를 듣게 되었습니다. 함수민 선생님 교재는 다른 교재에 비해 두껍긴 했는데요, 그래도 그만큼 책이 친절하게 서술되어있어서 행정법을 어려워하는 제가 보기 정말 좋았습니다. ppt로 도식화도 잘 되어있어서 공부하기 편리했어요. 저는 기본강의 위주로 들었는데요, 강의는 10번씩(1~3배속), 책은 20회독 이상 본 것 같습니다</t>
         </is>
       </c>
+      <c r="I253" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38538&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=73</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="55" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
@@ -9662,6 +10928,11 @@
           <t>행정학 송상호 선생님 수업을 들었습니다. 군무원 시험도 함께 준비 중이었어서 군무원 행정학을 들었습니다. 개인적으로 행정학이 제일 어려웠는데 선생님 커리 따라가면서 계속 회독 하니까 자연스럽게 익힐 수 있었고 문제도 쉽게 풀 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38536&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=73</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="55" customHeight="1">
       <c r="A255" s="3" t="inlineStr">
@@ -9696,6 +10967,11 @@
         </is>
       </c>
       <c r="H255" s="3" t="inlineStr"/>
+      <c r="I255" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38528&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=73</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="55" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
@@ -9730,6 +11006,11 @@
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr"/>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38511&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=74</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="55" customHeight="1">
       <c r="A257" s="3" t="inlineStr">
@@ -9764,6 +11045,11 @@
           <t>. 응시한 시험의 기본정보 ⓐ 응시한 시험 : 국가직 우정행정 (서울) ⓑ 응시한 직렬 : ⓒ 공부 기간 : 3년 ⓓ 본인만의 필기 합격 노하우 : 국어: 저는 독해에 자신감이 있었기 때문에 매일 독해감을 놓지않으려 고혜원 국어 하프모의고사를 많이 풀었습니다. 그리고 고득점을 맞기 위해서는 한자, 맞춤법 등 .. 어플을 통해 매일 매일 눈에 익히려고 노력을 해서 고득점을 받았던 것 같습니다. 영어: 단어를 매일매일 하려고 했고, 또 독해를 할 때 정확한 문장을 끊기에 더 신경을 써서 한 것 같습니다. 또 기출을 통해서 영어문법을 잊지 않기위해 노력한 것 같습니다 한국사: 한국사 또한 고종훈 모의고사를 통해서 매일매일 20문제씩 풀고, 틀리면 요약서를 찾아보는 등 최대한 한국사에 비중을 좁히려고 노력했습니다. 쉽게 시험이 나오는 것에 맞추어 사료, 절대 연도를 매일 보면서 잊지 않으려고 노력했습니다. 행정법: 행정법은 용어가 정말 중요하다고 생각합니다. 기각, 각하, 인용, 기속력...등등 법 용어에 익숙해지기 위해서 많이 노력을 했습니다. 모든 합격생들이 말하듯이 특히 행정법은 기출이 정말 중요합니다! 기출을 풀고 또 풀고, 요약서를 통해서 전 범위를 다 보</t>
         </is>
       </c>
+      <c r="I257" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38213&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=79</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="55" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
@@ -9794,6 +11080,11 @@
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr"/>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37336&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="55" customHeight="1">
       <c r="A259" s="3" t="inlineStr">
@@ -9828,6 +11119,11 @@
           <t>전부 찾아보시려면 좀 번거로우실 거에요. 행정학은 특히 생소한 문제가 한두 개 정도 나오는데 거기에 너무 치중하지 마시고 기출 빈도 순으로 중요하다고 생각하시고, 반복해서 풀어보세요. 공부하시다 보면 외워야 할 부분이 많이 나옵니다. 잘 기억이 나지 않는다면 포스트잇에 써서 잘 보이는 곳에 붙이고 외워보시는 건 어떨까요? 자신이 이해할 수 있는 방식으로 간단히 써서 여러 번 보세요.</t>
         </is>
       </c>
+      <c r="I259" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37288&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="55" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
@@ -9858,6 +11154,11 @@
         </is>
       </c>
       <c r="H260" s="2" t="inlineStr"/>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36908&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="55" customHeight="1">
       <c r="A261" s="3" t="inlineStr">
@@ -9894,6 +11195,11 @@
       <c r="H261" s="3" t="inlineStr">
         <is>
           <t>안녕하세요. 처음 공무원 준비를 시작할 때에는 저의 계획이 정말 실현될 수 있을지 저 스스로도 의심하게 되고 막막하였지만 결국 제가 올해 합격을 하게 되었습니다. 저는 단기 합격을 위한 계획을 세웠습니다(5개월 정도). 과정을 이야기하자면, 먼저 저는 1월 말 정도부터 5급 1차 시험을 준비하였습니다. 피셋 공부와 헌법 1회독을 이 시기에 처음 하게 되었습니다. 하지만 1차 시험에서 떨어졌고, 그 충격으로 5월 8일까지 공부를 안하고 놀기만 했습니다. 어버이날이 지나고 더는 부모님께 손벌리기가 싫었고, 사기업에 종사하는 것보다는 국가를 위한 일을 하고자 하는 마음이 있었기 때문에 7급 공무원을 준비하게 되었습니다(진짜입니다). 다행히 1차 시험은 1월에 5급 시험을 준비했던 경험으로 4일 정도 공부하여 붙을 수 있었습니다. 이후 2차 시험을 위해 제가 먼저 준비를 시작했던 과목은 경제학이었습니다. 아무래도 이해가 필요한 과목이고 휘발성이 다른 암기과목들에 비해 낮다고 생각을 하였기 때문에 가장 먼저 준비를 했습니다. 경제학은 일단 처음 들을 때에는 당연히 이해가 잘 안되지만 저는 이해를 해야 넘어가는 스타일이라 조금 까다로웠습니다. 김종국 선생님의 강의를 들</t>
+        </is>
+      </c>
+      <c r="I261" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36756&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
         </is>
       </c>
     </row>
@@ -9926,6 +11232,11 @@
         </is>
       </c>
       <c r="H262" s="2" t="inlineStr"/>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36754&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="55" customHeight="1">
       <c r="A263" s="3" t="inlineStr">
@@ -9960,6 +11271,11 @@
         </is>
       </c>
       <c r="H263" s="3" t="inlineStr"/>
+      <c r="I263" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36747&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="55" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
@@ -9998,6 +11314,11 @@
           <t>-공유하고 싶은 합격 꿀팁 필기합격을 할 수 있었던 제 방법에 대해서 설명해드리려고 합니다 이과생이어서 행정학이나 행정법을 공부할때 가장 어려움을 느꼈던 것 같습니다 아무래도 정답이 정해져 있는 수학 문제보다 전체적인 흐름과 암기가 동반되어야 하는 과목이기 때문에 처음에 적응하는데 시간이 오래 걸렸어요 꼼꼼하게 모든 부분을 심도있게 다 공부하려다보니 전체적인 흐름을 놓치는 경우가 있어서 정작 아는 내용은 많아도 시험에 적용하기가 더 어려웠던 것 같습니다 그래서 저는 해커스 강의를 수강하며 이 괴리감을 줄여나갔습니다 혼자서 기본서를 독파하기보다 송상호교수님이 기본이론 수업으로 가이드라인을 잡아주셔서 시험에 나오지않는 다른 부분을 보기보다 중요한 부분을 한번 더 볼 수 있었습니다 필기를 많이 하지않고 머리속에 한번더 넣고 반복하는 작업을 통해 행정학이라는 과목에 대한 두려움을 줄일 수 있었다고 생각합니다 그리고 필기합격의 평균점수를 높여준 고마운 과목인 국어는 신민숙 교수님의 수업 덕분이라고 생각합니다 교수님만의 유쾌한 에너지 덕분에 수업 내용이 전혀 지루하지않고 오히려 재밌게 공부를 할 수 있었다고 생각해요 특히 어법이 어려웠는데 그 어법을 간결하고도 기억하기</t>
         </is>
       </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36607&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=95</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="55" customHeight="1">
       <c r="A265" s="3" t="inlineStr">
@@ -10036,6 +11357,11 @@
           <t>공무원 시험은 분량이 방대하고, 행정법, 행정학, 한국사 등 암기과목이 많습니다. 그렇기 때문에 몇십편씩 되는 인강을 인내심 갖고 잘 듣는 것도 중요합니다. 특히 저는 인강을 한꺼번에 다 들은 다음에 문제풀이로 들어가는 것은 그다지 효과적이지 않은 전략이라는 것을 깨달았습니다. 기본서와 기출문제집을 동시에 갖춘 다음 인강을 특정 분량만큼 들으면, 즉시 배운 분량을 복습하고, 기본서에 실린 문제와 기출문제집의 해당 분량만큼 푼 다음 다음 인강으로 넘어가는 편이, 인강 여러 편을 한꺼번에 듣는 것보다 더 머리에 리프레시도 되고 배운 분량도 더 기억에 잘 남는다고 느꼈습니다.</t>
         </is>
       </c>
+      <c r="I265" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36604&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=95</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="55" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
@@ -10072,6 +11398,11 @@
       <c r="H266" s="2" t="inlineStr">
         <is>
           <t>-수강한 선생님 &amp; 강의 &amp; 교재 추천 저는 신민숙 교수님의 수업을 제일 좋아했어요  항상 공부의 시작은 국어였습니다 국어 강의는 거의 다 들었던 것 같아요 신민숙 교수님의 파이팅 넘치는 수업이 참 재미있었고 귀에 쏙쏙 들어오는 암기법은 물론  자연스럽게 외울 수 있게 반복해주셔서 시험에서 좋은 결과를 얻을 수 있었다고 생각합니다 토익도 해커스덕분에 900을 넘는 점수를 만들 수 있었기 때문에 해커스는 제게 특히나 이미지가 좋았고  결과적으로도 좋았다고 생각합니다 김송희 교수님의 하프가 매일매일 영어 감각을 깨우는데 큰 도움이 되었습니다 공무원 영어는 토익과 결이 다르기 때문에 그 감을 잡는 것이 중요했던 것 같아요 그리고 처음에 시작할때 행정학이 가장 두려웠는데 송상호 교수님의 기본 이론 수업 덕분에 행정학의 방대함 속에서 기준을 잘 잡을 수 있었다고 생각합니다</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36517&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=95</t>
         </is>
       </c>
     </row>
@@ -10104,6 +11435,11 @@
       <c r="F267" s="3" t="inlineStr"/>
       <c r="G267" s="3" t="inlineStr"/>
       <c r="H267" s="3" t="inlineStr"/>
+      <c r="I267" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36394&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=98</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="55" customHeight="1">
       <c r="A268" s="2" t="inlineStr">
@@ -10142,6 +11478,11 @@
         </is>
       </c>
       <c r="H268" s="2" t="inlineStr"/>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36100&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=107</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="55" customHeight="1">
       <c r="A269" s="3" t="inlineStr">
@@ -10176,6 +11517,11 @@
         </is>
       </c>
       <c r="H269" s="3" t="inlineStr"/>
+      <c r="I269" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36024&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=110</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="55" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
@@ -10214,6 +11560,11 @@
           <t>-본인만의 필수과목or선택과목 학습법: 국어 95점 국어는 신민숙 선생님 커리를 따라갔습니다.  강의 의존형이라 어법, 문학, 기출, 실전동형 거의 커리 다 따라갔습니다.  비문학 분야 비중이 높아진다고 해서 시중에서 파는 비문학 문제집이나 비문학 특강 같은 것들 많이 들었습니다.  영어 95점 영어는 처음 커리는 김송희 선생님과 비비안 선생님 문법 강의를 들었습니다. 독해는 따로 하프 모의고사나 실전 동형 모의고사를 많이 풀고 강의는 듣지 않았습니다.  단어가 중요하다고 생각해서 해커스 보카 계속 돌렸습니다. 비비안 선생님이 동의어 뽑아 주시는 특강이나 문법 특강 해주셨는데 그게 많이 도움이 된 것 같습니다.  한국사 100점 한국사는 이중석 선생님 강의를 들었습니다. 이론 강의가 다른 한국사 선생님에 비해 길긴 한데, 그만큼 기억에도 오래 남고 재미있게 설명해주셔서 저는 오히려 좋았습니다. 이론강의 3개, 단원별 기출 강의, 실전 동형 강의 이렇게 커리 따라 갔는데, 문제 해설해주실 때 처음 가르치는 것처럼? 설명해주셔서 그게 좋았습니다. 아는 부분은 아 이렇구나 이러고 넘어가는데, 생소한 부분은 다시 필기노트 짚고 숙지할 수 있었습니다.  행정법총론 9</t>
         </is>
       </c>
+      <c r="I270" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35962&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=112</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="55" customHeight="1">
       <c r="A271" s="3" t="inlineStr">
@@ -10248,6 +11599,11 @@
         </is>
       </c>
       <c r="H271" s="3" t="inlineStr"/>
+      <c r="I271" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35957&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=112</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="55" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
@@ -10278,6 +11634,11 @@
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr"/>
+      <c r="I272" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35947&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=113</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="55" customHeight="1">
       <c r="A273" s="3" t="inlineStr">
@@ -10312,6 +11673,11 @@
         </is>
       </c>
       <c r="H273" s="3" t="inlineStr"/>
+      <c r="I273" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35895&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=115</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="55" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
@@ -10346,6 +11712,11 @@
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr"/>
+      <c r="I274" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35768&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=119</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="55" customHeight="1">
       <c r="A275" s="3" t="inlineStr">
@@ -10376,6 +11747,11 @@
         </is>
       </c>
       <c r="H275" s="3" t="inlineStr"/>
+      <c r="I275" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=121</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="55" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
@@ -10410,6 +11786,11 @@
         </is>
       </c>
       <c r="H276" s="2" t="inlineStr"/>
+      <c r="I276" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=123</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="55" customHeight="1">
       <c r="A277" s="3" t="inlineStr">
@@ -10444,6 +11825,11 @@
         </is>
       </c>
       <c r="H277" s="3" t="inlineStr"/>
+      <c r="I277" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35658&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=124</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="55" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
@@ -10480,6 +11866,11 @@
       <c r="H278" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">-수험기간: 2022.01 ~2023.04  -기본베이스: 영어(영어영문학과), 한국사(순경합격),  -하루루틴 기상: 일어나고 싶은 시간 취침: 12시에서 1시사이 공부하는 총시간이 중요하다기보다는 공부를 얼마만큼 집중할 수 있는지가 더 중요하다고 생각해서 하루에 7~8시간정도 집중하는 시간을 갖도록 노력했습니다. 하지만 영어단어나 다른 어려운 어휘가 나올 수도 있기 때문에 어려운 단어는 최소 300개이상 보고가려 노력했고 국어도 사자성어는 꼭 맞히려 하루에 15개씩은 보도록 노력했습니다.  -과목학습 국어 95점 (신민숙 선생님): 최근에 국어의 출제경향이 많이 변해서 어려운 어법이나 어휘를 많이 물어보지는 않을 것으로 예상했습니다. 그래서 최대한 문학작품이나 비문학에서 틀리지 않는 방향으로 90점정도만 맞으려 노력했습니다.  또한 한자문제는 투입되는 공부량에 비해서 맞힐 가능성이 다소 적다고 생각했고 커트라인이 90점정도에 형성이 되는 것을 감안하면 한자문제는 틀려도 생각했습니다. 하지만 사자성어 문제는 반드시 맞혀야 되는 문제라 생각했었고 이 방법이 주요했었습니다.  영어 95점 (비비안 선생님): 사실 영어에 대해서는 특별한 방법이 많이 없습니다. </t>
+        </is>
+      </c>
+      <c r="I278" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35515&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=127</t>
         </is>
       </c>
     </row>
@@ -10516,6 +11907,11 @@
           <t>2. 하루 루틴 저는 체력과 멘탈이 시험을 좌우한다고 믿었기 때문에 평일엔 빠지지 않고 스카 바로 위층에 있는 요가를 다녔습니다. (요가 시간은 씻는 시간 포함 오전 9시-10시반 활용했습니다.) 기상 시간은 7시 반정도였고, 스카 도착시간은 8시 반으로, 요가 가기 직전 30분 동안 영어단어를 외웠습니다. 영어단어를 눈으로만 외우면 휘발이 빠르다고 생각해서 귀에 익히는 용도로 비비안쌤의 영단어 인강을 적극 활용했고, 유사 어휘를 차곡차곡 모아 외웠습니다. 잘 외워지지 않는 단어는 포스트잇을 활용해서 벽에 붙여두고 틈틈히 보며 외웠습니다. 운동이 끝나고 본격적으로 11시부터 공부를 시작했는데, 공부 흐름이 끊기는게 싫어서 12시나 1시에 점심을 먹지 않고 4시 반까지 스트레이트로 공부했습니다. 과목은 수시로 바뀌어서 특정하기 어렵기는 하지만, 공부 초반에는 주로 국어/한국사를 했고, 후반부에는 행정학/행정법을 하려고 노력했습니다. (*가장 집중도가 높은 시간대라고 생각했기 때문입니다) 4시 반부터 약 두 시간 동안은 걸어서 15분 거리에 있는 집에 가서 편하게 밥도 먹고 쉬어줬습니다. 저는 책상 앞에 앉아 집중해 공부하는 시간 외에는 책을 잘 보지 않았습니다</t>
         </is>
       </c>
+      <c r="I279" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35248&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=134</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="55" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
@@ -10550,6 +11946,11 @@
       </c>
       <c r="G280" s="2" t="inlineStr"/>
       <c r="H280" s="2" t="inlineStr"/>
+      <c r="I280" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35239&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=134</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="55" customHeight="1">
       <c r="A281" s="3" t="inlineStr">
@@ -10584,6 +11985,11 @@
           <t>1.기본 베이스 저는 국문학 전공이라 국어 어법은 크게 어려울 것 없었고, 한능검1급, 토익 800점대 점수이긴 했지만 문법이 너무 약해서 기본강의 열심히 들었습니다. 국영한은 어느정도 베이스가 있었는데 행정학, 행정법은 정말 아무것도 모르는상태로 시작해서 처음에 좀 힘들었어요. 특히 행정법이 기본적 법률용어를 모르니까 어렵더라구요.</t>
         </is>
       </c>
+      <c r="I281" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35189&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=136</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="55" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
@@ -10614,6 +12020,11 @@
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr"/>
+      <c r="I282" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34959&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=140</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="55" customHeight="1">
       <c r="A283" s="3" t="inlineStr">
@@ -10648,6 +12059,11 @@
           <t>자신 없었던 과목: 2018년도에 세무직 공무원에 합격 했을 때는 선택과목을 행정학 사회를 선택해서 수월하게                    공무원 시험에 합격 했었는데 2025년에는 회계학 세법이 선택과목으로 고정 되어 많은 어려움이                     있었습니다. 회계학 공부 할 때 기본강의를 듣고 문제풀이를 하였고 세법도 기본강의 듣고                    문제 풀이를 하였습니다. 회계하는 개념이 어려워서 도무지 이해하기가 어려웠습니다. 그리고                    세법도 암기사항이 너무 방대하고 이해도 잘 되지 않았습니다.</t>
         </is>
       </c>
+      <c r="I283" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40455&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=40</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="55" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
@@ -10682,6 +12098,11 @@
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr"/>
+      <c r="I284" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41017&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=26</t>
+        </is>
+      </c>
     </row>
     <row r="285" ht="55" customHeight="1">
       <c r="A285" s="3" t="inlineStr">
@@ -10712,6 +12133,11 @@
         </is>
       </c>
       <c r="H285" s="3" t="inlineStr"/>
+      <c r="I285" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39671&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="286" ht="55" customHeight="1">
       <c r="A286" s="2" t="inlineStr">
@@ -10746,6 +12172,11 @@
         </is>
       </c>
       <c r="H286" s="2" t="inlineStr"/>
+      <c r="I286" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39652&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="287" ht="55" customHeight="1">
       <c r="A287" s="3" t="inlineStr">
@@ -10782,6 +12213,11 @@
       <c r="H287" s="3" t="inlineStr">
         <is>
           <t>14시~18시 : 행정학, 행정법 기본이론반, 동형모의고사반, 교육학 수업(7~8월)</t>
+        </is>
+      </c>
+      <c r="I287" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39642&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -10818,6 +12254,11 @@
           <t>공부순서는 국어, 행정학, 행정법 순으로 순차대로 인강 3개씩 보면서 공부했었어요 한개 과목 끝나면 꼭</t>
         </is>
       </c>
+      <c r="I288" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36610&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=94</t>
+        </is>
+      </c>
     </row>
     <row r="289" ht="55" customHeight="1">
       <c r="A289" s="3" t="inlineStr">
@@ -10852,6 +12293,11 @@
           <t>그러나 행정학과 행정법은 타사 인강을 들었지만 잘 이해가 되지 않고 공부 방식이 흐지부지하게 되는 생활이 좀 많았습니다.</t>
         </is>
       </c>
+      <c r="I289" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41382&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="290" ht="55" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
@@ -10882,6 +12328,11 @@
         </is>
       </c>
       <c r="H290" s="2" t="inlineStr"/>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38148&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=81</t>
+        </is>
+      </c>
     </row>
     <row r="291" ht="55" customHeight="1">
       <c r="A291" s="3" t="inlineStr">
@@ -10916,6 +12367,11 @@
           <t>결국 저는 수학적인 머리가 컸고, 문과적인 머리는 별볼일이 없는 단순 무식한 전형적인 이공계형 수학형 머리분야서 빛난다는 것을 해커스사 강의로 8282 뜨게 된것이에요. 흔히 들 이런얘기 하시지오. 안될꺼 빨리 버려라 네  여러분 행정학은 여성암기왕과 남성 분석왕이 즐비합니다. 제 노력과 성실로는 이런분 제끼기 하늘 별따기였습니다. 그러나 해커스공무원강의를 듣고 일행은 일반행정은 단념하는 것이 정신건강에 좋다는 생각을 하였고, 책을 중고나 새책을 사는 경우도 생각날까봐 행정학 행정법 다 찢는 다는 자세로 책 곁에 두지도 않았습니다.</t>
         </is>
       </c>
+      <c r="I291" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35821&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=117</t>
+        </is>
+      </c>
     </row>
     <row r="292" ht="55" customHeight="1">
       <c r="A292" s="2" t="inlineStr">
@@ -10950,6 +12406,11 @@
           <t>결국 저는 수학적인 머리가 컸고, 문과적인 머리는 별볼일이 없는 단순 무식한 전형적인 이공계형 수학형 머리분야서 빛난다는 것을 해커스사 강의로 8282 뜨게 된것이에요. 흔히 들 이런얘기 하시지오. 안될꺼 빨리 버려라 네  여러분 행정학은 여성암기왕과 남성 분석왕이 즐비합니다. 제 노력과 성실로는 이런분 제끼기 하늘 별따기였습니다. 그러나 해커스공무원강의를 듣고 일행은 일반행정은 단념하는 것이 정신건강에 좋다는 생각을 하였고, 책을 중고나 새책을 사는 경우도 생각날까봐 행정학 행정법 다 찢는 다는 자세로 책 곁에 두지도 않았습니다.</t>
         </is>
       </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35820&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=117</t>
+        </is>
+      </c>
     </row>
     <row r="293" ht="55" customHeight="1">
       <c r="A293" s="3" t="inlineStr">
@@ -10980,9 +12441,14 @@
         </is>
       </c>
       <c r="H293" s="3" t="inlineStr"/>
+      <c r="I293" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41922&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H293"/>
+  <autoFilter ref="A1:I293"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10993,7 +12459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:I88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11004,6 +12470,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -11047,6 +12514,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -11081,6 +12553,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41696&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -11111,6 +12588,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41542&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=3</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -11149,6 +12631,11 @@
           <t>- 2024.07 ~ 2025.06 (약 1년)   2. 기본 베이스 지거국 영어영문학과 / 토익 900점대 후반 / 한능검 1급   3. 하루 루틴 수험 생활 초기에는 집 근처 도서관에서 공부를 했는데 집중이 잘 안 돼, 해커스 스파르타 독서실을 다녔습니다. 월요일부터 토요일까지는 아침 7시에 기상 후 아침 8시부터 밤 10시까지 독서실에서 공부했고 일요일은 쉬었습니다.   4. 공부 방향 공부 방향을 잘 설정하는 것이 단기 합격의 지름길이라고 생각합니다. 국어, 영어는 제가 자신 있어 하는 과목이었고 기초도 어느 정도 있었기 때문에 공부 시간을 최대한 줄이고 남는 시간을 한국사, 행정법, 행정학에 할애했습니다. 한국사 또한 제가 자신 있어 하는 과목으로 기초도 있었지만 국어, 영어와는 다르게 암기 과목이라 휘발성이 강해 공부량을 줄이지는 않았습니다. 공부 시간을 대략적으로 따져본다면 행정학 &gt; 행정법 &gt; 한국사 &gt; 영어 &gt; 국어 순으로 시간을 투자했습니다.   5. 과목별 공부법 국어 95점 국어는 학창 시절 열심히 했었기 때문에 자신 있는 과목이었습니다. 인사혁신처 예시 문제를 풀어보니 별다른 공부 없이도 충분히 풀 수 있는 난도여서 국어에 많은 시간을</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41522&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -11183,6 +12670,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41520&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -11221,6 +12713,11 @@
           <t>2025년 공무원 시험 합격수기:  강사님들 덕분입니다!! 안녕하십니까. 이번 공무원 시험에 최종 합격한 수험생입니다. 제가 합격이라는 결실을 맺을 수 있었던 가장 큰 비결은, 바로 해커스공무원의 훌륭한 강사진과 커리큘럼을 믿고 흔들림 없이 따라간 덕분입니다. 특히, 제가 선택했던 국어 신민숙, 영어 비비안, 행정법 김대현, 행정학 서현 선생님의 강의는 저의 수험 생활을 관통하는 핵심이었습니다.(한국사는 독학으로 공부했습니다)</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41463&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=6</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -11255,6 +12752,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41453&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=6</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -11293,6 +12795,11 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41440&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -11335,6 +12842,11 @@
           <t>저는 보통 10~11시 사이에 기상 후, 새벽 3-4시까지 공부하는 편이었습니다. 전공과목 '행정학' &amp; '행정법'은 2일에 1번 반복, 남은 공용과목을 골고루 돌아가면서 공부할 수 있게 1주일 단위로 계획을 주로 짰습니다. 예를 들어,  월 화 수 목 금 토 일 행정학 행정법 행정학 행정법 행정학 행정법 복습DAY 국어 영어 한국사 국어 영어 한국사 이런 식으로 짜서 진행했고 후반 문제풀이 과정으로 넘어갔을 때는 국어와 영어 비중을 줄이고 암기 과목인 '한국사' 에 시간을 더 투자했습니다.</t>
         </is>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41438&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -11373,6 +12885,11 @@
           <t>4년제 지방 국립대에서 공과대학을 졸업하였고, 1년 반 수험생활을 하였습니다. ■인강 국어: 조은정 국어 쌩기초 입문특강/ 조은정 국어 신유형대비 문제풀이 영어: 비비안 선생님의 기출해설강의 한국사: 이중석 선생님의 기본강의(올인원) 행정법,행정학은 기출문제와 여러 선생님들의 모의고사 문제로 해결 ■교재</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41429&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -11407,6 +12924,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41397&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -11449,6 +12971,11 @@
           <t>행정학: 서현쌤 기본,심화,기출 강의 다 수강함. 이거는 내용은 괜찮은데 외울게 진짜 너무 많고 방대해서 너무 막막해서 속이 답답했다. 하지만 정공법으로 그냥 강의도 공부다 생각하고 배속으로 듣고 그날 배운건 당일 복습하고 하니 기출까지 완강하니까 대충 뭔지 알겠어서 기출강의 끝나고는 서현쌤 기출문제집 무지성 회독함. 5회독 정도. 이것도 wox회독 나만의 변형버전으로 했음. 국가직때 65점 받고 충격 먹어서 지방직까지 열심히했더니 지방직은 95점 받음.</t>
         </is>
       </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41396&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -11483,6 +13010,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41345&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=11</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -11517,6 +13049,11 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41344&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=11</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -11553,6 +13090,11 @@
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>처음 시험 공부를 시작했을 때, 국어와 한국사, 영어는 비교적 자신 있는 과목들이었습니다. 특히 국어와 한국사는 기본기가 있었고, 영어도 평소에 꾸준히 공부해왔기 때문에 큰 장벽 없이 진입할 수 있었습니다. 하지만 선택과목인 행정법과 행정학은 전혀 다른 이야기였습니다. 생소한 용어와 복잡한 이론들 앞에서 처음에는 막막함을 느꼈고, 두 과목 모두 기본 강의와 심화 강의를 각각 두 번씩 반복하며 이해를 다졌습니다. 이후에는 기출문제 풀이 강의로 넘어가 실전 적용 능력을 키우는 데 집중했습니다. 공부는 결국 반복과 정리, 그리고 지속적인 피드백이 핵심이라는 것을 느꼈습니다.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41324&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=12</t>
         </is>
       </c>
     </row>
@@ -11585,6 +13127,11 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41298&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=13</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -11619,6 +13166,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41289&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=14</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -11653,6 +13205,11 @@
           <t>- 행정법 &amp; 행정학 정말 무슨 자신감인지는 모르겠지만 단 한번도 공부하지 않았었지만 고등학교를 문과로 나오고 선택과목도 법정이었어서 걱정은 많이 없었던 것 같네요.. (근거 없는 자신감이 최고조였던...ㅎㅎ, 마지막까지 발목잡은 행정법...)</t>
         </is>
       </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41258&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -11691,6 +13248,11 @@
           <t>4년정도 공시생활을 하였네요. 직장 특성상 야근이 잦은편이라, 공부시간확보가 상당히 어려웠습니다. 퇴근 후 밥먹고 씻고하면 공부시간 3~4시간정도,새벽2시까지는해야 5~6시간 겨우 확보되더군요. 야근하는 날에는 거의 공부를 못했구요.(회식있는날도 패스..) 국어는 신민숙선생님 영어는 김송희 선생님 한국사는 이중석 선생님 행정법은 함수민 선생님 행정학은 서현 선생님 강의로 시작했던것 같습니다.</t>
         </is>
       </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41250&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=16</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -11733,6 +13295,11 @@
           <t>약 6개월 간 강의를 수강하며 준비를 한 끝에 지방직에 최종합격하였습니다. 대학교 학과가 행정학과라 어느정도 베이스는 있었지만 강의를 수강하며 저만의 방법으로 암기하고, 학습한 끝에 최종합격이라는 결과를 얻어낸 것 같습니다. 지금부터 6개월간 강의를 수강하며 어떻게 지내왔는지를 소개해보려고 합니다.  - 매일 아침 6시 기상. 기상 후 30분 간 스트레칭 &amp; 걸으며 하루를 시작. 23시 30분 취침. 우선 주말도 예외없이 칼같이 기상시간을 지켰으며 저는 무엇보다 건강이 가장 중요하다고 생각했기에 기상 후 간단하게 조깅을 하거나 스트레칭을 하며 하루를 시작했고 적정한 취침시간을 지켜 강의를 수강하며 피로를 느끼지 않을 수 있도록 하였습니다.  - 오전에는 국어, 영어/ 점심식사 후 한국사/ 이른 저녁 행정학, 행정법 저는 머리가 가장 활발하게 활동하는 시간을 오전과 저녁시간이라고 생각하여 저에게 가장 힘들었던 과목인 국어와 행정법을 활발한 시간에 수강하여 고득점을 얻기 위해 노력하였습니다. 한국사는 제가 가장 좋아하는 과목이었습니다. 그래서 식곤증이 올 수 있는 시간에 수강하여도 재미있고 졸지 않고 수강할 수 있었습니다. 저는 제가 좋아하는 과목이나 잘하는 과</t>
         </is>
       </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41240&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=16</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -11771,6 +13338,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41233&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -11809,6 +13381,11 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41227&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -11847,6 +13424,11 @@
           <t>◆행정학- 서현 선생님 개인적으로 행정학이 제일 어려웠습니다... 처음 접하는 개념들이 많은데 또 이것들이 두루뭉실하게 둥둥 떠다니는 느낌이랄까요... 시간이 없다고 판단해서 심화를 듣지 않고 기본이론에서 바로 기출문제풀이로 넘어갔는데, 고득점을 위해서라면 꼭... 심화를 들으시길... 시험 전에는 행정학 단권화 특강으로 전체적인 개념을 쓱 흝을 수 있어서 좋았습니다. 행정학도 외우지 않으면 못푸는 과목이라고 생각해서 시험이 가까워질 수록 개념과 법령등을 외우는 데 시간을 썼습니다.</t>
         </is>
       </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41205&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=18</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -11885,6 +13467,11 @@
           <t>행정학/서현 선생님 강의가 좀 길고 방대합니다. 그러나 처음 듣는 사람이 듣기에는 어려움이 없습니다. 기본강의 들을떄는 이해가 되지 않더라도 귀에 익힌다는 생각으로 끝까지 완강을 하는것을 추천드립니다. 서현 선생님의 기출 문제집이 좋습니다. 기본강의 후 기출문제집을 계속 회독하면서 부족한 개념을 계속 암기하는 방법으로 공부하였습니다.</t>
         </is>
       </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41179&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -11923,6 +13510,11 @@
           <t>행정학 기본문제집보고 기겁했던게 엊그제 같네요. 강사님의 강의노트 덕분에 용기내서 시작했습니다. 요약이 정말 잘 되어있어요. 모든 강의 들을 때 강의노트 옆에 두고 들었습니다. 중요도도 체크해주셔서 복습할 때 그나마 순조로웠어요. 심화강의는 문제풀이 위주로 하시는데, 전 인강 들으면서 풀었습니다. 심화문제 단원별로 끝날 때마다 강의노트와 심화문제 번갈아보면서 복습했습니다. 신경향이론도 특강 강추합니다. 문제 여기서 많이 나왔어요. 배속 1.8</t>
         </is>
       </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41174&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -11957,6 +13549,11 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41173&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -11995,6 +13592,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41137&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -12033,6 +13635,11 @@
           <t>1. 기본 베이스 / 공무원 준비 계기 &lt;기본 베이스&gt; 국어- 고등학교때까지 꽤 잘하는 편이었음 (모의고사 1~2등급) 영어-못함 (절대평가 모의고사 3~4등급) 한국사 - 한능검 1급 행정법, 행정학 – 노베이스 &lt;공무원 준비 계기&gt; 대학교 졸업반이 되어서 전공을 살릴지 취업을 할지 고민하다가 졸업하기 전에 9급 공무원 시험을 봐보자 라는 생각으로 보게되었습니다.   2. 하루 루틴 (공부&amp;생활습관) 저는 3~4개월 정도 본격적인 공무원 수험생 생활을 했습니다. 제게 주어진 시간이 얼마 없어서 압도적인 공부시간이 필요했습니다. 그래서 저는 순공시간 12시간을 꼭 채우려고 노력했습니다. 매일 아침 8시반쯤에 일어나 준비를 하고 밥을 먹고 10시에 도서관에 도착해서 밤 10시에 집에 갔습니다. 집에 가서 얼른 씻고 다시 12시까지 공부하고 잠에 들었습니다. 점심식사와 저녁식사시간은 30분을 넘기지 않으려고 노력했습니다. 그렇게 공부시간 12시간을 채우려 노력했던 것 같습니다. 10시에 도서관에 도착해서 하루에 내가 했으면 좋겠는 (할 수 있는 x) 공부를 쭉 작성하고 (불가능한 정도의 공부 양이어야 함) 그 불가능한 공부 양을 최대한 하려고 노력했습니다. 그렇</t>
         </is>
       </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41127&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -12071,6 +13678,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41020&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=25</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="55" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -12109,6 +13721,11 @@
           <t>법과목 또한 너무 생소했고 또 남은 기간이 많지 않았기에 시작은 막막했습니다. 하지만 김대현 선생님은 컴팩트한 교재와 강의를 사용하시기에 현재 제 상황에 딱 맞는 선생님이였습니다. 행정법에서 가장 중요한 건 흐름을 알고 문제가 풀리는 그 순간까지 참고 버티고 공부해 나아가는 것 같습니다.. 처음에는 아무리 풀어보려해도 안 풀리는게 행정법이지만 나중에 효자과목이 된다는 이유를 알게 됐습니다. 국가직땐 행정법에 빠져서 많이 공부하고 풀다보니 국가직땐 65점 나와서 만족했지만 지방직까지 가는 과정중에 국가직 면접과 행정학 빵구 메우기 때문에 집중을 못해서 지방직땐 성적이 비록 떨어졌습니다. 그래서 행정법 또한 기본강의 듣고 회독하고 문제 풀며 어느정도 성적이 올라왔을때 계속 감을 유지하고 부족한 부분을 채워나가는 것이라 생각합니다. 단원만 보고 한 부분만 본다면 어려운 과목이지만 기본강의가 끝나고 여러번 회독 했을때 과목 전체를 보면 행정학보다 훨씬 효자과목이라 생각합니다(기출회독 필수)</t>
         </is>
       </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40996&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=26</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -12143,6 +13760,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40995&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=27</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -12181,6 +13803,11 @@
           <t>행정학: 서현 수강 강의 내역: 기본 강의, 기출 강의, 법령 특강 전시리즈, 하프 전시리즈, 실전 동형 강의</t>
         </is>
       </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40785&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="55" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -12219,6 +13846,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40721&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=31</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="55" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -12249,6 +13881,11 @@
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40692&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=31</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="55" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -12279,6 +13916,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40687&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="55" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -12309,6 +13951,11 @@
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40683&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="55" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -12343,6 +13990,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40670&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="55" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -12377,6 +14029,11 @@
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40575&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=35</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="55" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -12419,6 +14076,11 @@
           <t>- 수강한 선생님&amp;강의&amp;교재 추천 국어: 신민숙 선생님(신민숙 쉬운국어 논리 강화 150제 교재)  영어: 비비안 선생님(해커스공무원 비비안 올인원 영문법, 2025 해커스공무원 영어 구조 독해 007) 한국사: 이중석 선생님(해커스공무원 이중석 맵핑 한국사 올인원 블랭크노트) 행정법: 홍대겸 선생님(2025 해커스 홍대겸 행정법총론 단원별 기출문제집) 행정학: 서현 선생님(2025 해커스공무원 현 행정학 단원별 기출문제집)  모두 큰 도움이 되었습니다.  교재는 위의 교재 등을 위주로 활용했습니다.</t>
         </is>
       </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40541&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=36</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="55" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -12457,6 +14119,11 @@
           <t>행정학 (90점) 김만희 선생님 기본이론을 먼저 수강하였고, 이후에 기출 문제집 회독하다가 서현 선생님 모의고사 수강했습니다. 행정학은 하나의 문제집을 여러 번 회독하는 것보다는 여러 문제집을 보며 다양한 표현들을 익히는 게 중요한 것 같습니다. 처음보는 단어나 문제가 등장해도 어떻게 풀어나갈지 요령을 익히는 게 필요해요.</t>
         </is>
       </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40498&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=38</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="55" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -12497,6 +14164,11 @@
       <c r="H41" s="3" t="inlineStr">
         <is>
           <t>행정학 - 서현 행정학은 가장 쉬운 과목이면서도 가장 어려운 과목이었습니다. 서현 쌤의 수업을 들으면 해당 개념이 확실히 쉽게 다가왔는데 행정학 문제의 지문 자체가 귀에 걸면 귀걸이... 코에 걸면 코걸이...라서 많이 헤맸던 것 같습니다. 그럴 때 질문을 많이 했는데 그때마다 친절하게 설명해주셔서 감사했습니다. '강의노트'가 도움이 많이 되었는데 이미 체계적으로 정리되어 있는 강의노트에 수업을 들으며 저만의 방식으로 필기한 내용까지 더해지니 든든한 무기를 하나 손에 넣은 느낌이었습니다. 감사합니다!</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40478&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=39</t>
         </is>
       </c>
     </row>
@@ -12533,6 +14205,11 @@
           <t>암기과목(한국사, 행정법, 행정학)의 경우 그날 배운 부분을 복습한 뒤 기출문제에서 어떤 식으로 문제가 출제되는지, 중요한 부분이 무엇인지 확인하세요.</t>
         </is>
       </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=44</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="55" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -12567,6 +14244,11 @@
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
         </is>
       </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="55" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -12601,6 +14283,11 @@
           <t>(행정학) 행정학의 경우에는 대부분의 수험생들이 그렇듯 시험 직전까지도 가장 자신이 없었습니다. 개념의 범위가 너무 넓고 항상 불의타 문제가 나오기 때문에 대비가 어렵다고 느꼈습니다. 행정학의 경우에는 여러 이론들에 대해서 묻기 때문에 이론 간의 비교에 집중하면서 공부하는게 큰 도움이 됐습니다. 간단하게 비유하자면 단순하게 (a 이론의 특성은 키가 작다) 이런 식으로 외우면  혼동이 생길 때가 많습니다. 왜냐하면 a 이론이 b이론과 비교했을 때는 키가 작았지만, 또 다른 c이론과 비교했을 때는 키가 큰 경우가 있기 때문입니다. 행정학은 법 과목의 판례들처럼 딱 정해진 것이 아니어서 어떤 대상과 비교하냐에 따라서 해당 이론의 특성이 아 다르고 어 다르기 때문에  (a 이론은 b 이론과 비교했을 때는 키가 작다) 이런 식으로 유사한 그룹의 개념들끼리 비교를 잡으면서 개념을 유연성 있게 정리하는게 많은 도움이 됐습니다.   (헌법)) 헌법의 경우 처음 기본 강의를 들을 때는 상대적으로 재밌다고 느꼈습니다. 왜냐하면 다양한 판례들이 나오고 아무래도 판례들이 우리 생활과 밀접해 있다 보니 이러한 경우도 있구나 하면서 상대적으로 즐겁게 기본강의를 들었습니다. 하지만 기</t>
         </is>
       </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="55" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -12635,6 +14322,11 @@
           <t>(4) 행정학 [강의] 서현쌤 기본+심화이론 23년 1회 수강 [강의] 서현쌤 법령특강 1회 수강 [강의] 마니쌤 기본이론 24년 1회 수강 [교재] 서현쌤 기본서 [교재] 마니쌤 기본서 [교재] 서현쌤 기출문제집 9회독 [교재] 마니쌤 OX 3회독 [교재] 경간 소간 국회직 등등 각종 시행처 최신기출</t>
         </is>
       </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39626&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="55" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -12677,6 +14369,11 @@
           <t>행정법과 헌법은 황남기 선생님에게 의지했습니다. 교재가 너무 완벽해서 내용이 그 안에서 벗어나지 않았습니다. 역시 기본강의만 들었고, 곧바로 기출회독을 시작했고 이후 모의고사로 법과목을 공부했습니다. 특히 시험을 앞두고 나오는 최신판례 강의에서 그대로 문제가 나왔습니다.  법은 공부하면 하는만큼 나옵니다. 정말 정직합니다. 법에서 최대한 점수 챙긴다고 생각하고 메인으로 공부하세요. 절대 배신 안합니다. 저도 이번에 행정학에서 많이 까먹었지만 헌법 100점, 행정법 92점으로 선방해서 안정적으로 합격할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39624&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="55" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
@@ -12715,6 +14412,11 @@
           <t>7월 28일부터 8월 11일까지 일요일 동안 송상호 선생님의 신경향 흐름의 주요테마 및 단원별 문제풀이를 수강하였습니다. 9월 22일에 해커스공무원이 시행한 2024 대비 제9회 7급 합격예측 모의고사를 응시하였기에 실전연습을 할 수 있었습니다. 10월 11일까지 헌법은 8회, 행정법은 8회, 행정학은 9회, 경제학(16년-23년 국가직7급, 지방직7급, 국회직8급)은 9회 가량 기출문제집 회독을 할 수 있었습니다. 신동욱 선생님의 헌법, 함수민 선생님의 행정법, 송상호 선생님의 행정학, 김종국 선생님의 경제학 기출문제풀이 강의 덕분에 기출문제집 회독을 효율적으로 할 수 있었고, 2차 합격을 할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39621&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="55" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -12757,6 +14459,11 @@
           <t>저는 해커스와 1년 8개월을 함께하여 25년 서울 지방직 9급 일반행정직에 합격하였습니다. 저는 9급 기적의 합격패스 2년짜리를 등록하여 공부를 하였습니다.   저는 올빼미 형이라서 아침 10시 정도에 일어나서 새벽 2시까지 집에서 공부하는 생활 패턴을 반복하였습니다. 초기에는 월~금요일은 저녁식사 전까지 공통과목인 국어, 영어를 공부하였고, 식사 후에 행정법과 행정학을 공부하였으며, 토요일과 일요일에는 진도가 느렸던 과목과 한국사를 조금 공부하였습니다.   국어는 신민숙 선생님 강의를 들었는데, 문법이 약해서 비문학보다는 문법에 시간을 많이 할애하였습니다. 한자는 공부하다가 싫증이 날 때 틈틈이 보았습니다.   영어는 비비안 선생님 강의를 들었으며, 단어와 문법, 독해를 2:3:5 정도의 비율로 공부하였습니다. 단어는 특별하게 외우기보다는 독해를 하면서 모르는 단어를 암기노트에 적고 파생 단어를 공부하는 식으로 외웠습니다.   한국사는 제가 한능검을 공부하였던 경험이 있기에 어느 정도 기초가 되어 있어서, 바로 이중석 선생님의 기출문제풀이로 공부하였습니다.   행정법은 함수민 선생님의 기본과 심화 강의를 3번 들은 후 기출문제 풀이를 들었습니다.. 행정법은</t>
         </is>
       </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39255&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=50</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="55" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
@@ -12795,6 +14502,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr"/>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39251&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=50</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="55" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -12837,6 +14549,11 @@
           <t>행정학 : 송상호 선생님 저에게 가장 고통스러웠던 과목이었습니다. 행정법과 마찬가지로 쌩노베였지만 행정법과는 다르게 썰을 듣는다는 느낌이 아니라 학자들의 견해를 외워야 한다는 느낌이어서 가장 어렵게 다가왔습니다. 교재는 공무원 명품 행정학을 기본서로 이용했고 시험전까지 총 4회독을 하였습니다. 2회독을 한 이후 해커스 기출문제집을 2회독하고 마지막으로 기본서 2회독으로 마무리하였습니다.</t>
         </is>
       </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39106&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=52</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="55" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
@@ -12871,6 +14588,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39065&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=52</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="55" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -12900,6 +14622,11 @@
         <v/>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39039&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=53</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="55" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
@@ -12942,6 +14669,11 @@
           <t>행정학은 서현쌤 기출문제집이랑 필기노트 보면서 독학으로 공부했습니다. 처음엔 진짜 어려운 과목이긴 한데, 필기노트만 보지 말고, 기출문제도 같이 풀면서 몇 번 회독하다보면 자주 나오는 선지들이 보여서 나름 할만한 과목입니다! 다만, 이번 지방직 시험은 유달리 어렵게 나와서 75점을 받았습니다ㅜ 이렇게 3년 간 공시생 생활의 결실을 국가직 일반행정(교육부), 지방직 일반행정(제주시) 2관왕으로 아름답게 마무리 할 수 있다는 것에 대해 안도감과 동시에 기쁨이 느껴집니다. 공시는 열심히 회독하다보시면 충분히 합격할 수 있으니 이 글을 읽는 여러분들도 꼭 합격하기를 간절히 바랍니다!</t>
         </is>
       </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38968&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=56</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="55" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -12980,6 +14712,11 @@
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38957&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=56</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="55" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
@@ -13010,6 +14747,11 @@
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38932&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=57</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="55" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -13044,6 +14786,11 @@
           <t>안녕하세요. 저는 2024년도 지방직 일반행정에 합격한 합격생입니다. 저는 대학생 4학년 1년간 학교에 다니면서 시험을 준비했습니다. (총 수험기간: 23년 9월~24년 6월) 전 행정학과 학생이고 거의 모든 수업은 아침수업으로 들었고 점심부터는 수험 공부를 시작했습니다. 저는 이동시간이 길어 시간이 부족하다고 생각했기 때문에 점심시간이나 이동시간에는 단어를 외우거나 가벼운 강의를 들으면서 다녔습니다.</t>
         </is>
       </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38915&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=58</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="55" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
@@ -13078,6 +14825,11 @@
         </is>
       </c>
       <c r="H57" s="3" t="inlineStr"/>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38899&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=59</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="55" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -13112,6 +14864,11 @@
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38878&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=60</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="55" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
@@ -13146,6 +14903,11 @@
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38875&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=60</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="55" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -13180,6 +14942,11 @@
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38846&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=61</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="55" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
@@ -13214,6 +14981,11 @@
         </is>
       </c>
       <c r="H61" s="3" t="inlineStr"/>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38788&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=64</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="55" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -13248,6 +15020,11 @@
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38776&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=64</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="55" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
@@ -13286,6 +15063,11 @@
           <t>공무원 준비는 부모님 권유로 시작하게 되었습니다. 하루 루틴은 국가직까지 3개월정도가 있었는데 하루에 3~4시간정도 공부했습니다. 국어,영어는 안하고 행정법,행정학,한국사 압축강의(행정법,한국사), 기본강의(행정학)만 봤습니다. 1,4,7,14복습법을 이때만 적용했습니다. 그래도 까먹었는데 깊은 잠재의식속에 남아있지 않았을까 생각됩니다.</t>
         </is>
       </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38757&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=65</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="55" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -13324,6 +15106,11 @@
           <t>9급, 4지 선지선다이기 때문에 모르는 부분이 있더라도 깊이 파고드는 방법은 적합하지 않다고 생각했어요. 반복, 암기, 반복, 암기, 모르는 부분은 넘어가기 식의 공부방법이 더 잘 맞았어요. 그리고 특히 행정학같은 경우는 흐름을 타기 때문에 기출문제에 집착할 필요 없다고 생각합니다. 책이나 강의는 무조건 최신판으로 구해서 보시고, 작년 기출, 국가직, 바뀐 출제 기조 꼭 참고하셔서 흐름을 찾아가며 공부하는 방식을 추천드립니다.</t>
         </is>
       </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38731&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=66</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="55" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
@@ -13358,6 +15145,11 @@
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38725&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=66</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="55" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -13400,6 +15192,11 @@
           <t>2. 베이스 국어 수능 3등급, 영어 수능 2등급 토익 800점대, 한국사 수능1 한국사검정시험1급, 행정법 행정학 처음 공부함</t>
         </is>
       </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38678&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=68</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="55" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
@@ -13438,6 +15235,11 @@
           <t>행정법, 행정학, 한국사는 반복이 답인 것 같습니다. 처음에 강의 들을 때는 포기하고 싶었는데 꾹 참고 다시 들어보고 기출회독을 하면서  왜 다들 회독이 답이라고 하는지 알 수 있었습니다.  행정학과 한국사는 필기노트로 계속 회독했고 행정법은 기본서, 기출문제 선지를 반복해서 학습했습니다.</t>
         </is>
       </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38659&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=69</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="55" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -13476,6 +15278,11 @@
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38646&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=69</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="55" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
@@ -13512,6 +15319,11 @@
       <c r="H69" s="3" t="inlineStr">
         <is>
           <t>-저는 총 3번의 시도 끝에 합격하게 되었는데요, 처음에는 “행정학과 이니, 대학교를 다니면서 붙어보자!” 라고 생각을 하여 휴학을 하고 공무원 공부를 하였는데 결과는 좋지 않았습니다ㅠㅠ 일단 졸업을 해야 하기 때문에 복학을 하고 병행해서 공부도 해보았지만 결국 한 가지에 집중해야 한다는 교훈만 얻은 채 불합격을 하게 됩니다. 그리고 마지막으로 졸업 후 마지막 기회라고 생각해 해커스 공무원 인강과 함께 도전하게 되었는데요, 가격적인 측면에서도 합리적이고 암기 위주가 아니라 이해 중심의 강의로 이루어져 선택하게 되었습니다! 그리고 다행히도 좋은 결과를 얻게 되어 이렇게 합격수기를 적게 되었습니다!</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38144&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=81</t>
         </is>
       </c>
     </row>
@@ -13544,6 +15356,11 @@
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38021&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=87</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="55" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
@@ -13578,6 +15395,11 @@
           <t>행정학은 여러 선생님의 기본강의를 들었는데, 전체적으로 흐름을 잡긴 했지만 이해를 못해서 과감하게 포기했던 것 같습니다. 그래서 기출문제집을 풀면서 강의를 발췌해서 들었고 그 부분을 확실히 이해하려고 노력했습니다. 선생님들만의 암기법도 참고하여 다양한 암기법으로 이론을 외웠습니다. 행정학은 무조건 "암기법" 거의 앞글자 따는 거긴 하지만요, 나름 도움됩니다. 3년 동안 까먹은 적 한 번도 없음 ㅎㅎ 그리고 행정학에서 저의 발목은 잡은 부분은 시험에서의 항상 새로운 이론의 등장이었습니다. 저는 그런 문제만 보면 얼음이 되어서 찍거나 대충 풀어버리는 습관이 있었는데, 저는 이러한 이유로 2년간 불합격을 한 것 같습니다. 이 부분을 고치지 않으면 합격하기 힘들겠다는 생각이 들어서 이 부분에 대해 열심히 분석하였습니다. 생각보다 단순하였습니다. 이론서에 없는 완전히 새로운 개념의 문제를 풀 때, 마치 국어의 독해와 비슷하였습니다. 문제 안에서 답이 있었고 문제의 흐름과 선지들끼리의 구성을 잘 살펴보면 꼭 맞지 않는 선지가 답이었습니다. 여러 문제를 풀다보면 자신이 느끼는 바가 있을 것입니다. 저는 이번 시험에서 새로운 개념의 문제는 다 맞췄습니다. 이 부분은 저 스</t>
         </is>
       </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37280&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="55" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -13616,6 +15438,11 @@
           <t>판례문제와 법이론 문제를 나눠서 외웠고 판례는 안외워지는 것 위주로 반복해서 보았습니다. 헌법은 초시때 점수가 안나와서 재시때에는 시간을 많이 투자하였습니다. 행정학은 생소한 문제가 계속 출제된다고 생각하여 기출된 주제의 문제는 실수하지 않도록 연습하였고 새로운 주제들은 특강을 들었습니다. 행정법은 황남기 선생님을 들었습니다. 행정법은 판례문제에서 많이 출제된다고 생각하여 판례를 반복하였고 대부분 기출된것에서 출제가 되어 빈출문제를 더 많이 보았습니다.</t>
         </is>
       </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36757&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="55" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
@@ -13652,6 +15479,11 @@
       <c r="H73" s="3" t="inlineStr">
         <is>
           <t>제가 생각하기에 한국사와 행정학은 개념이 중요하다고 생각해서 교재로 회독을 돌렸고, 행정법은 사례가 중요하다고 생각해서 단원별 기출문제집이나 동형문제집으로 회독했습니다.</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36210&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=103</t>
         </is>
       </c>
     </row>
@@ -13684,6 +15516,11 @@
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36190&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=103</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="55" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
@@ -13718,6 +15555,11 @@
           <t>1. 기본 베이스 국어 - 초반에는 한자성어에 약한 편이었습니다. 영어 - 중간 정도의 수준이었고 듣기영역에 약한 정도였습니다. 한국사 - 디테일하게 공부해본 적이 별로 없었습니다. 행정법 - 처음 접하는 과목이었고 용어도 익숙하지 않았었습니다. 행정학 - 처음 접하는 과목이었습니다.</t>
         </is>
       </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36145&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=105</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="55" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -13756,6 +15598,11 @@
           <t>- 행정학 사회과학을 전공해서 베이스가 조금 있었습니다. 강의는 서현 선생님의 강의를 들었습니다. 정리도 깔끔하고 설명도 이해하기 쉬워서 추천드립니다. 전체적으로 무난하게 공부했던 과목입니다.</t>
         </is>
       </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36046&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=109</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="55" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
@@ -13794,6 +15641,11 @@
           <t>2023 지방직 일반행정 최종합격수기  안녕하세요 이번 2023년 지방직에서 최종 합격하게 되었습니다. 제 합격수기를 보시고 공부 방법도 참고하시고 좋은 동기방안을 얻으셨으면 좋겠습니다!  응시 기간: 2021년 9월부터 2023년 9월까지 응시 직렬: 일반행정직 베이스: 행정법, 행정학은 처음 시작했고 학창시절 공부에 관심이 없어 국어도 노베이스였었습니다. 영어와 한국사는 일반행정직 준비하기전 경찰공무원을 준비했을 때 공부하여 어느정도 기본은 잡혀있었습니다.  공부 하루 루틴: 저는 독립된 공간보단 여러 사람들이 있는 스터디 카페나 주변 도서관을 주로 이용했습니다. 아침 7시에 기상해서 30분 동안 준비한 후 30분 정도 거리에 있는 공부 장소로 이동했습니다. 공부에 집중하느라 운동을 소홀히 해서 걷기라도 해보려 했습니다. 그 과정에서 걸으면서 영단어, 한자성어, 속담 등을 외우면서 다녔습니다. 도착하면 8시부터 9시까지 영어 하프 모의고사를 했습니다. 그리고 9시부터 1시까지 한 과목 인강을 들으면 진도를 나갔습니다. 중간에 쉬는 시간도 가지면서 컨디션을 조절했습니다. 그리고 점심시간 1시간 정도 가진 후 오후에는 다른 과목을 1시부터 6시까지 진도를 나</t>
         </is>
       </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36027&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=110</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="55" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -13828,6 +15680,11 @@
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35950&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=113</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="55" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
@@ -13866,6 +15723,11 @@
           <t>행정학 : 뭔가 쉬운데 쉽지 않은 과목이라고 생각합니다. 행정학은 제가 전공했기 때문에 다른 분들보다 확실히 초반에 접근할 때 수월했던 게 사실입니다. 그래서 공부를 많이 하지 않고 시험을 봐도 75점에서 80점대는 유지했고 공부할 때 그렇게 많은 스트레스를 주진 않았던 것 같습니다. 하지만 필수과목이 되면서 그 전보다 확실히 난이도가 올라갔다고 느꼈습니다. 특히 지엽적인 문제빈도가 높아졌다고 느껴지면서 도대체 어디까지 준비해야하나 싶을 정도로 공부 방향성을 잡는 게 쉽지 않아졌다고 생각합니다. 하지만 일단 기본에 충실하면서 기출문제로 지엽적인 부분을 커버하면 어느정도 고득점을 맞는 데 어렵지 않다고 생각합니다. 그런 점에서 서현 선생님의 강의는 어떤 개념이 나오면 그 느낌이 연상되게 해주고 암기할 게 많은 행정학에서 최대한 암기하기 쉽게 해주는 부분이 많아서 좋았습니다.</t>
         </is>
       </c>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35911&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=114</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="55" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -13908,6 +15770,11 @@
           <t>1. 응시한 시험의 기본정보   ⓐ 응시한 시험 : 지방직 9급   ⓑ 응시한 직렬 : 일반행정   ⓒ 공부 기간 : 8개월   ⓓ 본인만의 합격 노하우 :     기본베이스 : 토익(910점), 한능검 1급     국어(신민숙)   문법, 어휘 기본강의와 문학,비문학 기본강의 문법은 심화강의, 기출문제 강의, 한자성어 300강의를 들었습니다.   특히 신민숙쌤은 문법강의가 너무 좋았습니다. 시험 경향이 쉬워지면서 어려운 문법은 나오지 않아서 심화강의까지는 듣지 않았어도 될 것 같지만 저는 복습하는 의미에서 도움이 되었습니다. 한자성어도 강의를 들으니 더 뚜렷하게 기억에 남습니다. 신민숙 쌤 정말 추천합니다.     영어(비비안)   영어는 기본베이스가 어느정도 있었기에 기본이론 강의는 저에게 너무 진도가 느리다고 느껴져서 문제풀이를 같이하는 문법강의를 들었습니다. 기출문제도 정말 꼼꼼하게 설명을 해주셔서 어떻게 문제를 풀어야 하는지 알 수 있었습니다. 시험 직전 문법 OX문제도 도움이 되었던 것 같습니다. 문법을 정말 꼼꼼하고 깔끔하게 설명해주십니다. 비비안 선생님 정말 추천합니다. 영단어는 매일매일 외웠고 4회독 정도밖에 하지 못했네요.     한국사(이</t>
         </is>
       </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35867&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=116</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="55" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
@@ -13944,6 +15811,11 @@
       <c r="H81" s="3" t="inlineStr">
         <is>
           <t>- 일반적인 기본베이스는 수능기준으로 보았을 때 국어는 3등급 / 영어는 2등급 정도의 실력을 가지고 있었고, 한국사는 4등급에서 5등급을 맞는 수준이었습니다. 나머지 행정학과 행정법 또한 전공이지만 처음 모의고사나 기출 시험을 풀었을 때에는 과락이 나올 정도로 처참했습니다.</t>
+        </is>
+      </c>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35750&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=120</t>
         </is>
       </c>
     </row>
@@ -13976,6 +15848,11 @@
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35634&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=124</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="55" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
@@ -14006,6 +15883,11 @@
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35587&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=125</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="55" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -14036,6 +15918,11 @@
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35435&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=129</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="55" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
@@ -14070,6 +15957,11 @@
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr"/>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35196&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=136</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="55" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -14100,6 +15992,11 @@
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35192&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=136</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="55" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
@@ -14134,6 +16031,11 @@
         </is>
       </c>
       <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35131&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=139</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="55" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -14172,9 +16074,14 @@
           <t>보건행정학, 공중보건학 - 최성희 선생님 기본이론 강의 부터 기출강의까지 착실하게 따라갔고 선생님께서 개인적으로 만들어주시는 간단한 문제들과 시험문제처럼 만드신 문제들이 이론을 다시 돌아보는데 도움이 됐습니다. 전공은강의 말고 혼자 공부하는 시간을 훨씬 더 많이 할애해야한다고 생각합니다.  방대한 양과 외우기 힘든 수치들, 생소한 행정학 단어들 때문에 막막하겠지만 처음부터 세세히 외우려고 하기보단 책 읽듯이 처음부터 끝까지 읽어보고, 그 다음은 단어의 정의나 설명들을 구분해서 암기하고 천천히 세부적으로 들어가면서 여러번 회독한 후 기출문제 풀고 기출도 3~4회독정도 한다면 충분히 안정적인 점수를 받을 수 있을거라 생각합니다.</t>
         </is>
       </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41370&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H88"/>
+  <autoFilter ref="A1:I88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -14185,7 +16092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14196,6 +16103,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -14239,6 +16147,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -14281,6 +16194,11 @@
           <t>행정학 - 90점 행정학은 송상호 선생님의 강의를 들었습니다. '송상호 명품 행정학 기본이론', '송상호 명품 행정학 심화이론'으로 이론을 공부한 다음에, '해커스공무원 명품 행정학 단원별 기출문제집'으로 기출문제를 공부했습니다. 행정학은 여러 주제들이 섞여 있는 학문이어서, 공부를 하고 문제를 계속 풀어도 헷갈리는 지문이 많이 나오는 과목입니다. 송상호 선생님께선 그러한 지점들을 잘 짚어주시고, 중요한 내용들을 강조하시면서 학생들로 하여금 '행정학'이라는 과목에 익숙해지도록 이끌어주십니다.</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41530&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -14319,6 +16237,11 @@
           <t>- 2024.07 ~ 2025.06 (약 1년)   2. 기본 베이스 지거국 영어영문학과 / 토익 900점대 후반 / 한능검 1급   3. 하루 루틴 수험 생활 초기에는 집 근처 도서관에서 공부를 했는데 집중이 잘 안 돼, 해커스 스파르타 독서실을 다녔습니다. 월요일부터 토요일까지는 아침 7시에 기상 후 아침 8시부터 밤 10시까지 독서실에서 공부했고 일요일은 쉬었습니다.   4. 공부 방향 공부 방향을 잘 설정하는 것이 단기 합격의 지름길이라고 생각합니다. 국어, 영어는 제가 자신 있어 하는 과목이었고 기초도 어느 정도 있었기 때문에 공부 시간을 최대한 줄이고 남는 시간을 한국사, 행정법, 행정학에 할애했습니다. 한국사 또한 제가 자신 있어 하는 과목으로 기초도 있었지만 국어, 영어와는 다르게 암기 과목이라 휘발성이 강해 공부량을 줄이지는 않았습니다. 공부 시간을 대략적으로 따져본다면 행정학 &gt; 행정법 &gt; 한국사 &gt; 영어 &gt; 국어 순으로 시간을 투자했습니다.   5. 과목별 공부법 국어 95점 국어는 학창 시절 열심히 했었기 때문에 자신 있는 과목이었습니다. 인사혁신처 예시 문제를 풀어보니 별다른 공부 없이도 충분히 풀 수 있는 난도여서 국어에 많은 시간을</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41522&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -14353,6 +16276,11 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41520&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -14383,6 +16311,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41511&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -14421,6 +16354,11 @@
           <t>2025년 공무원 시험 합격수기:  강사님들 덕분입니다!! 안녕하십니까. 이번 공무원 시험에 최종 합격한 수험생입니다. 제가 합격이라는 결실을 맺을 수 있었던 가장 큰 비결은, 바로 해커스공무원의 훌륭한 강사진과 커리큘럼을 믿고 흔들림 없이 따라간 덕분입니다. 특히, 제가 선택했던 국어 신민숙, 영어 비비안, 행정법 김대현, 행정학 서현 선생님의 강의는 저의 수험 생활을 관통하는 핵심이었습니다.(한국사는 독학으로 공부했습니다)</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41463&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=6</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -14455,6 +16393,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41434&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -14493,6 +16436,11 @@
           <t>■ 과목별 공부 방법 국어: 신민숙 선생님 강의를 활용했습니다. 문법은 개념부터 다시 정리했고, 새롭게 추가된 논리 파트는 인강으로 보강했습니다. 문학·비문학은 문제풀이 위주로 학습했고, 교재는 선생님 커리큘럼을 따라가며 문제집을 풀었습니다. 영어: 모의고사를 중심으로 공부했습니다. 틀린 문제는 해설과 단어 풀이를 활용해 다시 독해했고, 비비안 선생님 보카 강의를 통해 단어 학습을 보완했습니다. 동의어와 반의어를 함께 익히는 방식이 큰 도움이 되었습니다. 한국사: 이중석 선생님 강의를 통해 개념과 기출을 모두 정리했습니다. 블랭크 노트와 맵핑 수업 방식이 이해도를 높였고, 문제를 풀면서 관련 개념까지 정리하는 방식이 장기 기억에 유리했습니다. 행정법: 함수민 선생님 강의와 교재를 활용했습니다. 선생님의 교재와 강의 양이 많아 처음에는 당황스러웠지만 그만큼 하나라도 알려주시려는 열정이 느껴졌습니다. 처음 접하는 과목이었지만 꼼꼼한 설명 덕분에 기초를 다질 수 있었습니다. 반복적으로 나오는 지문이 많아 회독을 늘릴수록 답안 속도가 빨라지는 효과를 얻을 수 있었습니다. 행정학: 서현 선생님 강의를 수강했습니다. 단순 암기 과목처럼 보이지만 지엽적인 문제가 많아 심</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41432&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -14531,6 +16479,11 @@
           <t xml:space="preserve">공부 패턴 저는 보통 오전, 오후, 저녁으로 나누어 공부했고, 밤늦게까지는 하지 않았습니다. 쉬는 날은 토요일 오전과 일요일 정도로 잡았고, 일주일에 1~2회 정도 저녁에 운동을 했습니다. 개인적으로 운동이 중요하다고 생각했습니다. 스트레스도 풀리고, 공부하는 데 체력이 중요하다는 것을 많이 느꼈습니다. 평소 운동을 해 둔 덕분에 시험 전 2~3개월 동안은 공부에만 집중할 수 있었다고 생각합니다. 국어 국어는 신민숙 선생님 강의를 들었습니다. 최대한 학생들이 이해하기 쉽게 설명해 주시고, 중요한 부분들을 짚어 주셔서 공부량을 줄이는 데 많은 도움이 되었습니다. 국어 과목이 개편된 후에는 다양한 문제를 많이 풀어 보는 것이 중요할 것 같습니다. 영어 영어는 비비안 선생님 강의를 들었습니다. 제가 문법에 자신이 없었는데, 깔끔하게 정리된 자료를 배포해 주셔서 기본기를 닦는 데 큰 도움이 되었습니다. 그리고 선생님께서 단어 암기를 강조하시며, 거기에 도움이 되는 다양한 강의를 제공해 주셔서 암기 습관을 만드는 것이 수월했습니다. 한국사 한국사는 이중석 선생님 강의를 들었습니다. 선생님 강의 덕분에 한국사를 재미있게 공부할 수 있었습니다. 강의 시간이 길지만 단순 </t>
         </is>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41388&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -14567,6 +16520,11 @@
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>처음 공무원 시험 준비를 시작할 때 저는 영어를 제외한 4과목이 완전히 노베이스였습니다. 생전 처음 보는 행정법과 행정학 뿐만 아니라 국어와 국사도 중학생 때 이후로 처음이었습니다. 공무원 시험을 치려고 마음을 먹고 바로 수험서로 유명한 해커스에 강의 등록을 했고, 시험이 어느 정도의 난이도로 출제되는지 감을 잡아보려고 특별한 공부나 준비 없이 2024년 지방직 시험을 응시 했었습니다. 결과는 예상보다 더 안좋았습니다. 영어를 제외한 과목은 거의 다 찍는 수준이었고 특히 국어가 고전 시가나 한문 그리고 문법 때문에 너무 어렵게 느껴졌었습니다. 시험을 보고나니 아무리 공부를 더 해도 국어 성적은 올리기가 힘들다는 판단에 시험 자체를 포기해야하나 생각했었습니다.</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41308&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=13</t>
         </is>
       </c>
     </row>
@@ -14603,6 +16561,11 @@
           <t>- 행정법 &amp; 행정학 정말 무슨 자신감인지는 모르겠지만 단 한번도 공부하지 않았었지만 고등학교를 문과로 나오고 선택과목도 법정이었어서 걱정은 많이 없었던 것 같네요.. (근거 없는 자신감이 최고조였던...ㅎㅎ, 마지막까지 발목잡은 행정법...)</t>
         </is>
       </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41258&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -14641,6 +16604,11 @@
           <t>- 필기 준비 과정 &gt; 국어 신민숙 선생님 강의를 들으며 문법 개념을 체계적으로 정리했습니다. 또, 대학에서 논리학을 배운 경험 덕분에 논리 문제에서도 큰 도움을 받았습니다. 국어는 초반에 개념을 정리해 두고 논리 문제는 충분히 연습해두면, 시간을 절약할 수 있는 과목이었던 것 같습니다. &gt; 영어 영어는 제 가장 큰 약점이었습니다. 그래서 우선, 비비안 선생님의 기초 강의를 들으며 기본기를 다졌습니다. 설명이 명확해서 이해하기 좋았고 영어에 대한 거리감이 어느 정도는 줄어들었던 것 같습니다. 다만, 충분히 시간을 투자하지 못한 아쉬움이 남습니다. 수험생분들 중에도 특정 과목이 약점이라면, 반드시 학습시간 분배에 신경 쓰시길 바랍니다. &gt; 한국사 이중석 선생님 강의를 들었습니다. 수험 한국사는 처음이었지만, 스토리텔링 방식 덕분에 재미있게 개념을 잡을 수 있었습니다. 다만, 선생님도 늘 강조하시듯 강의만 듣고 끝내면 안 되고, 반드시 스스로 정리하는 복습이 필요합니다. &gt; 행정법 함수민 선생님의 기본+심화 강의를 통해 핵심 판례와 빈출 영역을 집중적으로 학습했습니다. 처음에는 강의 분량이 많아 부담스러웠지만, 시험 막판에는 오히려 시간을 절약할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41253&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -14679,6 +16647,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41233&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -14721,6 +16694,11 @@
           <t>행정학 공부방법 행정학은 서현 선생님 개념 강의 수강했습니다.  사실 인강을 많이 들을 시간이 없기도 했고 강의 스타일이 저와 잘 맞지 않아서</t>
         </is>
       </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41220&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -14755,6 +16733,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41215&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -14793,6 +16776,11 @@
           <t>행정학/서현 선생님 강의가 좀 길고 방대합니다. 그러나 처음 듣는 사람이 듣기에는 어려움이 없습니다. 기본강의 들을떄는 이해가 되지 않더라도 귀에 익힌다는 생각으로 끝까지 완강을 하는것을 추천드립니다. 서현 선생님의 기출 문제집이 좋습니다. 기본강의 후 기출문제집을 계속 회독하면서 부족한 개념을 계속 암기하는 방법으로 공부하였습니다.</t>
         </is>
       </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41179&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -14833,6 +16821,11 @@
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>행정학(90) 서현 선생님 행정학 행정학 기본강의와 심화강의를 들었습니다. 강의를 안듣고 기본서를 보면 무슨말인지 파악이 안됩니다. 기본적인 부분을 필기하고 심화강의를 추가했습니다.700제 문제를 이해되게 잘 설명해주셔서 점수를 잘받을수 있게 되었습니다.단원별 기출문제는 다풀어 보진 못했고 문제와 해설지가 따로여서 해설을 문제에 적으면서 풀려고햇습니다. 쉬운 암기법을 통해 어려운 개념도 정리가 되겠금 가르쳐 주십니다.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41125&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
         </is>
       </c>
     </row>
@@ -14865,6 +16858,11 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41099&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=22</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -14899,6 +16897,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41037&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=25</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -14933,6 +16936,11 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41031&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=25</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -14963,6 +16971,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40683&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -14997,6 +17010,11 @@
           <t>암기과목(한국사, 행정법, 행정학)의 경우 그날 배운 부분을 복습한 뒤 기출문제에서 어떤 식으로 문제가 출제되는지, 중요한 부분이 무엇인지 확인하세요.</t>
         </is>
       </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=44</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -15031,6 +17049,11 @@
           <t>(행정학) 행정학의 경우에는 대부분의 수험생들이 그렇듯 시험 직전까지도 가장 자신이 없었습니다. 개념의 범위가 너무 넓고 항상 불의타 문제가 나오기 때문에 대비가 어렵다고 느꼈습니다. 행정학의 경우에는 여러 이론들에 대해서 묻기 때문에 이론 간의 비교에 집중하면서 공부하는게 큰 도움이 됐습니다. 간단하게 비유하자면 단순하게 (a 이론의 특성은 키가 작다) 이런 식으로 외우면  혼동이 생길 때가 많습니다. 왜냐하면 a 이론이 b이론과 비교했을 때는 키가 작았지만, 또 다른 c이론과 비교했을 때는 키가 큰 경우가 있기 때문입니다. 행정학은 법 과목의 판례들처럼 딱 정해진 것이 아니어서 어떤 대상과 비교하냐에 따라서 해당 이론의 특성이 아 다르고 어 다르기 때문에  (a 이론은 b 이론과 비교했을 때는 키가 작다) 이런 식으로 유사한 그룹의 개념들끼리 비교를 잡으면서 개념을 유연성 있게 정리하는게 많은 도움이 됐습니다.   (헌법)) 헌법의 경우 처음 기본 강의를 들을 때는 상대적으로 재밌다고 느꼈습니다. 왜냐하면 다양한 판례들이 나오고 아무래도 판례들이 우리 생활과 밀접해 있다 보니 이러한 경우도 있구나 하면서 상대적으로 즐겁게 기본강의를 들었습니다. 하지만 기</t>
         </is>
       </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -15061,6 +17084,11 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39633&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -15095,6 +17123,11 @@
           <t>(4) 행정학 [강의] 서현쌤 기본+심화이론 23년 1회 수강 [강의] 서현쌤 법령특강 1회 수강 [강의] 마니쌤 기본이론 24년 1회 수강 [교재] 서현쌤 기본서 [교재] 마니쌤 기본서 [교재] 서현쌤 기출문제집 9회독 [교재] 마니쌤 OX 3회독 [교재] 경간 소간 국회직 등등 각종 시행처 최신기출</t>
         </is>
       </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39626&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -15133,6 +17166,11 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38957&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=56</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -15171,6 +17209,11 @@
           <t>특히, 동형모의고사의 경우 구할 수 있는 대로 구해서 양치기를 했는데, 외웠다고 생각했던 판례, 혹은 요약 되었거나, 전문이 나오면 틀리는 경우가 있었습니다. 하지만, 양치기를 통해 틀렸던 문제의 판례는 다시 기본서로 돌아와 공부하고, 중요한 쟁점, 혹은 자주 나오는 문구에 형광펜을 칠하고 외웠습니다. 아무래도 틀렸던 문제의 경우 기억에 더 잘 남아서, 형광펜 치고 다시 보았던 판례의 기억 저장 시간이 훨씬 길었습니다. 서현 선생님의 강의에서 가장 핵심이 되는 내용은 행정학적 마인드 같습니다. 사실 공부하는 내내 행정학적 마인드를 적립하는데 어려움이 있어서, 어떻게 해야 하지 고민이 많았지만, 강의노트 회독, 문제풀이를 하며 개념을 다잡고 그게 쌓이다 보니 저절로 적립이 가능했습니다.</t>
         </is>
       </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38729&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=66</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -15205,6 +17248,11 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38522&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=74</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -15243,6 +17291,11 @@
           <t>-저는 총 3번의 시도 끝에 합격하게 되었는데요, 처음에는 “행정학과 이니, 대학교를 다니면서 붙어보자!” 라고 생각을 하여 휴학을 하고 공무원 공부를 하였는데 결과는 좋지 않았습니다ㅠㅠ 일단 졸업을 해야 하기 때문에 복학을 하고 병행해서 공부도 해보았지만 결국 한 가지에 집중해야 한다는 교훈만 얻은 채 불합격을 하게 됩니다. 그리고 마지막으로 졸업 후 마지막 기회라고 생각해 해커스 공무원 인강과 함께 도전하게 되었는데요, 가격적인 측면에서도 합리적이고 암기 위주가 아니라 이해 중심의 강의로 이루어져 선택하게 되었습니다! 그리고 다행히도 좋은 결과를 얻게 되어 이렇게 합격수기를 적게 되었습니다!</t>
         </is>
       </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38144&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=81</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="55" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -15281,6 +17334,11 @@
           <t>- 행정학 : 서현 선생님 강의와 커리큘럼이 짜임새가 있습니다. 강의 경력도 워낙 기시고 전공자셔서 전문성은 말할 것도 없구요. 딕션이나 목소리도 좋으셔서 강의 듣는데에 매우 편했습니다. 입문-기본-심화-문풀-실전동형 이 5단계가 너무나도 튼튼하게 갖추어져 있어서, 커리큘럼대로만 꾸준히 따라가다 보면 서현 선생님이 수업 중 계속해서 강조하시는 행정학적인 마인드가 머리에 장착됩니다.강의의 특장점으로는 현 행정학 강의노트 라는 단권화 노트가 있는데, 따로 개인적으로 단권화할 필요 없이 300페이지 가량 되는 이 책에 강의 들으면서 꾸준히 개념 추가하고, 책정리 해가다 보면 80점 라인 방어하는 데에는 차고 넘칩니다. 기본심화 강의 진행도 기본서는 서브로 하고 이 강의노트 위주로 해 주셔서, 방대한 행정학의 분량을 획기적으로 줄여서 기본을 쌓아올리는 데에 큰 도움이 된 것 같습니다.</t>
         </is>
       </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36748&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -15315,6 +17373,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36207&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=103</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -15349,6 +17412,11 @@
           <t>1. 기본 베이스 국어 - 초반에는 한자성어에 약한 편이었습니다. 영어 - 중간 정도의 수준이었고 듣기영역에 약한 정도였습니다. 한국사 - 디테일하게 공부해본 적이 별로 없었습니다. 행정법 - 처음 접하는 과목이었고 용어도 익숙하지 않았었습니다. 행정학 - 처음 접하는 과목이었습니다.</t>
         </is>
       </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36145&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=105</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="55" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -15389,6 +17457,11 @@
       <c r="H33" s="3" t="inlineStr">
         <is>
           <t>1. 응시한 시험의 기본정보   ⓐ 응시한 시험 : 지방직 9급   ⓑ 응시한 직렬 : 일반행정   ⓒ 공부 기간 : 8개월   ⓓ 본인만의 합격 노하우 :     기본베이스 : 토익(910점), 한능검 1급     국어(신민숙)   문법, 어휘 기본강의와 문학,비문학 기본강의 문법은 심화강의, 기출문제 강의, 한자성어 300강의를 들었습니다.   특히 신민숙쌤은 문법강의가 너무 좋았습니다. 시험 경향이 쉬워지면서 어려운 문법은 나오지 않아서 심화강의까지는 듣지 않았어도 될 것 같지만 저는 복습하는 의미에서 도움이 되었습니다. 한자성어도 강의를 들으니 더 뚜렷하게 기억에 남습니다. 신민숙 쌤 정말 추천합니다.     영어(비비안)   영어는 기본베이스가 어느정도 있었기에 기본이론 강의는 저에게 너무 진도가 느리다고 느껴져서 문제풀이를 같이하는 문법강의를 들었습니다. 기출문제도 정말 꼼꼼하게 설명을 해주셔서 어떻게 문제를 풀어야 하는지 알 수 있었습니다. 시험 직전 문법 OX문제도 도움이 되었던 것 같습니다. 문법을 정말 꼼꼼하고 깔끔하게 설명해주십니다. 비비안 선생님 정말 추천합니다. 영단어는 매일매일 외웠고 4회독 정도밖에 하지 못했네요.     한국사(이</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35867&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=116</t>
         </is>
       </c>
     </row>
@@ -15421,9 +17494,14 @@
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35435&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=129</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H34"/>
+  <autoFilter ref="A1:I34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15434,7 +17512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15445,6 +17523,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -15488,6 +17567,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -15522,6 +17606,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41696&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -15552,6 +17641,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41511&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -15594,6 +17688,11 @@
           <t>작년 12월에 맘먹고 준비하려고 보니 6월이 시험이더라구요 ㅠ 그때부터 해커스에서 인터넷 강의 신청해서 먼저 양이 많은 한국사(이중석쌤)부터 시작해서 강의 듣기 시작했고 중간에 행정학(서현쌤) 추가해서 하루에 3-4시간씩 나눠서 강의를 들었습니다. 그리고 한국사와 행정학이 어느정도 진도가 나간 후에 행정법(김대현쌤)강의를 뒤늦게 들었습니다 그리고 기본강의 다 듣고 난 뒤에 한국사는 8개년 기출문제집으로 계속 돌려보면서 안외워지는 선택지는 색깔 표시해서 외우고 행정학은 서현쌤 심화강의까지 다 듣고 똑같이 기출문제집으로 계속 돌려보면서 안외워지는 선택지 색깔 표시해서 계속 회독 돌렸어요! 행정법은 일단 너무 두꺼운 교과서 보다 3분의 1로 줄어쓴 책이어서 쉽게 접근이 가능했던 김대현 쌤 강의와 책이 너무 도움이 되었습니다.</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41451&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=6</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -15636,6 +17735,11 @@
           <t>5. 행정학 행정학은 공부하면 할수록 늪에 빠지는 느낌이 많이 든 과목이었습니다. 저는 김만희선생님 강의를 들었는데, 처음엔 이걸 어떻게 공부하지? 생각이 많이 들었던 과목이었습니다. 특히 모의고사 풀 때 점수가 잘 안나오는 과목중 하나였습니다. 이거 되는 시험이 맞는건가? 생각이 많이 들었으나, 기출을 풀면 못 보던 문제 같은데 풀리는걸 보며 모의고사에 너무 연연하지 않고 하던 방식대로 계속 공부했습니다. 마지막 1달 앞두고서는 주요 법령 모아둔 책을 구매하여 외우지는 못해도 기본계획같은 큼직한 년수는 외우려 했습니다. 암기할것은 외워야 하지만 일단 개념이 이해가 잘 되었기 때문에 암기가 크게 어렵지 않았습니다.</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41439&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -15670,6 +17774,11 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41325&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=12</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -15708,6 +17817,11 @@
           <t>- 필기 준비 과정 &gt; 국어 신민숙 선생님 강의를 들으며 문법 개념을 체계적으로 정리했습니다. 또, 대학에서 논리학을 배운 경험 덕분에 논리 문제에서도 큰 도움을 받았습니다. 국어는 초반에 개념을 정리해 두고 논리 문제는 충분히 연습해두면, 시간을 절약할 수 있는 과목이었던 것 같습니다. &gt; 영어 영어는 제 가장 큰 약점이었습니다. 그래서 우선, 비비안 선생님의 기초 강의를 들으며 기본기를 다졌습니다. 설명이 명확해서 이해하기 좋았고 영어에 대한 거리감이 어느 정도는 줄어들었던 것 같습니다. 다만, 충분히 시간을 투자하지 못한 아쉬움이 남습니다. 수험생분들 중에도 특정 과목이 약점이라면, 반드시 학습시간 분배에 신경 쓰시길 바랍니다. &gt; 한국사 이중석 선생님 강의를 들었습니다. 수험 한국사는 처음이었지만, 스토리텔링 방식 덕분에 재미있게 개념을 잡을 수 있었습니다. 다만, 선생님도 늘 강조하시듯 강의만 듣고 끝내면 안 되고, 반드시 스스로 정리하는 복습이 필요합니다. &gt; 행정법 함수민 선생님의 기본+심화 강의를 통해 핵심 판례와 빈출 영역을 집중적으로 학습했습니다. 처음에는 강의 분량이 많아 부담스러웠지만, 시험 막판에는 오히려 시간을 절약할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41253&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -15750,6 +17864,11 @@
           <t>행정학(90) 서현 선생님 행정학 행정학 기본강의와 심화강의를 들었습니다. 강의를 안듣고 기본서를 보면 무슨말인지 파악이 안됩니다. 기본적인 부분을 필기하고 심화강의를 추가했습니다.700제 문제를 이해되게 잘 설명해주셔서 점수를 잘받을수 있게 되었습니다.단원별 기출문제는 다풀어 보진 못했고 문제와 해설지가 따로여서 해설을 문제에 적으면서 풀려고햇습니다. 쉬운 암기법을 통해 어려운 개념도 정리가 되겠금 가르쳐 주십니다.</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41125&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -15788,6 +17907,11 @@
           <t>법과목 또한 너무 생소했고 또 남은 기간이 많지 않았기에 시작은 막막했습니다. 하지만 김대현 선생님은 컴팩트한 교재와 강의를 사용하시기에 현재 제 상황에 딱 맞는 선생님이였습니다. 행정법에서 가장 중요한 건 흐름을 알고 문제가 풀리는 그 순간까지 참고 버티고 공부해 나아가는 것 같습니다.. 처음에는 아무리 풀어보려해도 안 풀리는게 행정법이지만 나중에 효자과목이 된다는 이유를 알게 됐습니다. 국가직땐 행정법에 빠져서 많이 공부하고 풀다보니 국가직땐 65점 나와서 만족했지만 지방직까지 가는 과정중에 국가직 면접과 행정학 빵구 메우기 때문에 집중을 못해서 지방직땐 성적이 비록 떨어졌습니다. 그래서 행정법 또한 기본강의 듣고 회독하고 문제 풀며 어느정도 성적이 올라왔을때 계속 감을 유지하고 부족한 부분을 채워나가는 것이라 생각합니다. 단원만 보고 한 부분만 본다면 어려운 과목이지만 기본강의가 끝나고 여러번 회독 했을때 과목 전체를 보면 행정학보다 훨씬 효자과목이라 생각합니다(기출회독 필수)</t>
         </is>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40996&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=26</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -15830,6 +17954,11 @@
           <t>- 수강한 선생님&amp;강의&amp;교재 추천 국어: 신민숙 선생님(신민숙 쉬운국어 논리 강화 150제 교재)  영어: 비비안 선생님(해커스공무원 비비안 올인원 영문법, 2025 해커스공무원 영어 구조 독해 007) 한국사: 이중석 선생님(해커스공무원 이중석 맵핑 한국사 올인원 블랭크노트) 행정법: 홍대겸 선생님(2025 해커스 홍대겸 행정법총론 단원별 기출문제집) 행정학: 서현 선생님(2025 해커스공무원 현 행정학 단원별 기출문제집)  모두 큰 도움이 되었습니다.  교재는 위의 교재 등을 위주로 활용했습니다.</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40541&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=36</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -15866,6 +17995,11 @@
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>행정학(서현/95점) 아~ 행정학 저에겐 너무 어려웠어요 비슷한 내용인데 다른 거고 다른 내용인줄 알았는데? 같은거고 정말 헷갈려서 회독을 많이 하는 수밖에 없었어요 서현쌤 강의 스타일은 암기단어들을 많이 만들어주셔서 암기할게 많은 행정학을 그래도 좀 쉽게 암기하지 않았나 싶습니다</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40388&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=43</t>
         </is>
       </c>
     </row>
@@ -15902,6 +18036,11 @@
           <t>암기과목(한국사, 행정법, 행정학)의 경우 그날 배운 부분을 복습한 뒤 기출문제에서 어떤 식으로 문제가 출제되는지, 중요한 부분이 무엇인지 확인하세요.</t>
         </is>
       </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=44</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -15936,6 +18075,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38878&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=60</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -15978,6 +18122,11 @@
           <t>2. 베이스 국어 수능 3등급, 영어 수능 2등급 토익 800점대, 한국사 수능1 한국사검정시험1급, 행정법 행정학 처음 공부함</t>
         </is>
       </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38678&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=68</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -16020,6 +18169,11 @@
           <t>한국사(노베이스) 공시공부 시작을 한국사로 하게 되었습니다. 접근성도 나름 높은 것 같았고, 한국사를 알아야 행정법과 행정학이 더 잘 이해가 될 것이라고 생각해서였습니다. 하지만 결코 접근성이 높지만은 않았는지, 다른 사이트에서 타강사님 강의를 듣다가 이해가 너무 안돼서 유튜브 강의를 찾아본 결과 이중석 선생님 강의를 알게 되었는데(불교와 성리학 강의), 듣자마자 '아, 이 선생님이다!'라는 생각이 들어서 바로 결제하게 되었습니다. 이중석 선생님 강의를 듣고 나서는 현대사 끝까지 이해를 잘 하며 공부할 수 있었습니다. 한국사는 이해뿐만 아니라 암기도 중요한데, 암기는 이명호선생님 기본강의를 들으며 암기법도 전수받고, 저만의 암기법도 생각해낼 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38534&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=73</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -16056,6 +18210,11 @@
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-저는 총 3번의 시도 끝에 합격하게 되었는데요, 처음에는 “행정학과 이니, 대학교를 다니면서 붙어보자!” 라고 생각을 하여 휴학을 하고 공무원 공부를 하였는데 결과는 좋지 않았습니다ㅠㅠ 일단 졸업을 해야 하기 때문에 복학을 하고 병행해서 공부도 해보았지만 결국 한 가지에 집중해야 한다는 교훈만 얻은 채 불합격을 하게 됩니다. 그리고 마지막으로 졸업 후 마지막 기회라고 생각해 해커스 공무원 인강과 함께 도전하게 되었는데요, 가격적인 측면에서도 합리적이고 암기 위주가 아니라 이해 중심의 강의로 이루어져 선택하게 되었습니다! 그리고 다행히도 좋은 결과를 얻게 되어 이렇게 합격수기를 적게 되었습니다!</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38144&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=81</t>
         </is>
       </c>
     </row>
@@ -16092,6 +18251,11 @@
           <t>행정학은 여러 선생님의 기본강의를 들었는데, 전체적으로 흐름을 잡긴 했지만 이해를 못해서 과감하게 포기했던 것 같습니다. 그래서 기출문제집을 풀면서 강의를 발췌해서 들었고 그 부분을 확실히 이해하려고 노력했습니다. 선생님들만의 암기법도 참고하여 다양한 암기법으로 이론을 외웠습니다. 행정학은 무조건 "암기법" 거의 앞글자 따는 거긴 하지만요, 나름 도움됩니다. 3년 동안 까먹은 적 한 번도 없음 ㅎㅎ 그리고 행정학에서 저의 발목은 잡은 부분은 시험에서의 항상 새로운 이론의 등장이었습니다. 저는 그런 문제만 보면 얼음이 되어서 찍거나 대충 풀어버리는 습관이 있었는데, 저는 이러한 이유로 2년간 불합격을 한 것 같습니다. 이 부분을 고치지 않으면 합격하기 힘들겠다는 생각이 들어서 이 부분에 대해 열심히 분석하였습니다. 생각보다 단순하였습니다. 이론서에 없는 완전히 새로운 개념의 문제를 풀 때, 마치 국어의 독해와 비슷하였습니다. 문제 안에서 답이 있었고 문제의 흐름과 선지들끼리의 구성을 잘 살펴보면 꼭 맞지 않는 선지가 답이었습니다. 여러 문제를 풀다보면 자신이 느끼는 바가 있을 것입니다. 저는 이번 시험에서 새로운 개념의 문제는 다 맞췄습니다. 이 부분은 저 스</t>
         </is>
       </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37280&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -16126,6 +18290,11 @@
           <t>행정학과 지방자치론은 일전에 하던 것이 있어서 인강은 듣지 않고 헌법, 행정법과 마찬가지로 계속 단원별 기출을 풀면서 감을 잃지 않았습니다.</t>
         </is>
       </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37101&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=90</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -16162,6 +18331,11 @@
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>행정학 : 뭔가 쉬운데 쉽지 않은 과목이라고 생각합니다. 행정학은 제가 전공했기 때문에 다른 분들보다 확실히 초반에 접근할 때 수월했던 게 사실입니다. 그래서 공부를 많이 하지 않고 시험을 봐도 75점에서 80점대는 유지했고 공부할 때 그렇게 많은 스트레스를 주진 않았던 것 같습니다. 하지만 필수과목이 되면서 그 전보다 확실히 난이도가 올라갔다고 느꼈습니다. 특히 지엽적인 문제빈도가 높아졌다고 느껴지면서 도대체 어디까지 준비해야하나 싶을 정도로 공부 방향성을 잡는 게 쉽지 않아졌다고 생각합니다. 하지만 일단 기본에 충실하면서 기출문제로 지엽적인 부분을 커버하면 어느정도 고득점을 맞는 데 어렵지 않다고 생각합니다. 그런 점에서 서현 선생님의 강의는 어떤 개념이 나오면 그 느낌이 연상되게 해주고 암기할 게 많은 행정학에서 최대한 암기하기 쉽게 해주는 부분이 많아서 좋았습니다.</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35911&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=114</t>
         </is>
       </c>
     </row>
@@ -16198,6 +18372,11 @@
           <t>2시간~3시간 가량 행정학 문제 오답, 개념서 복습, 모의문제 풀이, 암기 저녁 30분&amp; 국어 사자성어, 국어 한자, 영어 단어 및 숙어 암기 중 택1</t>
         </is>
       </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35789&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=119</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -16236,6 +18415,11 @@
           <t>행정학 : 송상호 선생님 (95점) 행정학이 내용 자체도 어렵지만 제출될 수 있는 범위가 광범위하기 때문에 어느 부분에서 문제가 나올 지 감을 잡기 가장 어려운 과목이라고 생각합니다. 본인이 가장 설명을 잘 이해 할 수 있는 선생님을 선택하는게 중요하다고 생각하고 저는 송상호 선생님을 선택했습니다. 우선 선생님이 암기가 아닌 이해 위주의 수업을 해주시기 때문에 처음 공부하는 입장에서 배우기 수월했습니다. 앞 글자 따서 암기하는 것이 처음에는 편할 수 있지만 행정학은 휘발성이 너무 강한 과목이기에 이해를 바탕으로 공부해야 한다고 생각합니다.   국가직이 너무 지엽적인 문제들이 많이 나와서 지엽적인 것도 다 해야하나 고민을 많이하고 스트레스도 받았었는데 선생님께서 배운 지식을 강화하는게 중요하다는 말을 듣고 제가 아는 내용을 최대한 잊어 버리지 않기 위해 노력 하여 지방직에서 좋은 점수를 받을 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35713&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=121</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -16272,6 +18456,11 @@
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>보건행정학, 공중보건학 - 최성희 선생님 기본이론 강의 부터 기출강의까지 착실하게 따라갔고 선생님께서 개인적으로 만들어주시는 간단한 문제들과 시험문제처럼 만드신 문제들이 이론을 다시 돌아보는데 도움이 됐습니다. 전공은강의 말고 혼자 공부하는 시간을 훨씬 더 많이 할애해야한다고 생각합니다.  방대한 양과 외우기 힘든 수치들, 생소한 행정학 단어들 때문에 막막하겠지만 처음부터 세세히 외우려고 하기보단 책 읽듯이 처음부터 끝까지 읽어보고, 그 다음은 단어의 정의나 설명들을 구분해서 암기하고 천천히 세부적으로 들어가면서 여러번 회독한 후 기출문제 풀고 기출도 3~4회독정도 한다면 충분히 안정적인 점수를 받을 수 있을거라 생각합니다.</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41370&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
         </is>
       </c>
     </row>
@@ -16304,6 +18493,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40556&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=36</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -16342,9 +18536,14 @@
           <t>[행정학-송상호, 타학원 선생님] 네과목중 가장 저를 힘들게했던 과목이었습니다. 저는 이과출신이어서 다른 과목들도 물론 베이스가 없었지만 암기가 무엇보다 우선시되는 행정학은 내용도 방대하고 외울것이 정말 많아서 시험보기 직전까지도 가장 불안한 과목이었습니다. 하지만 행정법과 마찬가지로 최다빈출을 잡고가자는 생각으로 다빈출 지문이나 표는 포스트잇에 써서 책상앞에 붙여두고 공부에 집중이 안될때마다 한번씩 보고, 또 백지에 써보면서 외웠습니다. 사실 포스트잇에 써서 붙여놓기만 하면 잘 외우지 않게되어 공부가 하기 싫을때 노트를 꺼내서 한번씩 쭉 써보는 식으로 암기 했습니다. 또한 두문자를 따는 것이 암기가 필요한 행정학에 큰 도움이 되었다고 생각합니다. 상호쌤도 역시 예시를 잘 들어주셔서 초시생들이나 저같은 무베이스의 수험생들이 듣기에 적합한 강의라고 생각됩니다.</t>
         </is>
       </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36645&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=94</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H24"/>
+  <autoFilter ref="A1:I24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16355,7 +18554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16366,6 +18565,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -16409,6 +18609,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -16443,6 +18648,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41696&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -16479,6 +18689,11 @@
       <c r="H3" s="3" t="inlineStr">
         <is>
           <t>- 2024.07 ~ 2025.06 (약 1년)   2. 기본 베이스 지거국 영어영문학과 / 토익 900점대 후반 / 한능검 1급   3. 하루 루틴 수험 생활 초기에는 집 근처 도서관에서 공부를 했는데 집중이 잘 안 돼, 해커스 스파르타 독서실을 다녔습니다. 월요일부터 토요일까지는 아침 7시에 기상 후 아침 8시부터 밤 10시까지 독서실에서 공부했고 일요일은 쉬었습니다.   4. 공부 방향 공부 방향을 잘 설정하는 것이 단기 합격의 지름길이라고 생각합니다. 국어, 영어는 제가 자신 있어 하는 과목이었고 기초도 어느 정도 있었기 때문에 공부 시간을 최대한 줄이고 남는 시간을 한국사, 행정법, 행정학에 할애했습니다. 한국사 또한 제가 자신 있어 하는 과목으로 기초도 있었지만 국어, 영어와는 다르게 암기 과목이라 휘발성이 강해 공부량을 줄이지는 않았습니다. 공부 시간을 대략적으로 따져본다면 행정학 &gt; 행정법 &gt; 한국사 &gt; 영어 &gt; 국어 순으로 시간을 투자했습니다.   5. 과목별 공부법 국어 95점 국어는 학창 시절 열심히 했었기 때문에 자신 있는 과목이었습니다. 인사혁신처 예시 문제를 풀어보니 별다른 공부 없이도 충분히 풀 수 있는 난도여서 국어에 많은 시간을</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41522&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
         </is>
       </c>
     </row>
@@ -16511,6 +18726,11 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41511&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -16549,6 +18769,11 @@
           <t>2) 한국사(95점-이중석t)/행정법(90점-김대현t)/행정학(100점-김만희t)  암기 과목은 알면 풀고 모르면 못 풀기에..딱히 모의고사 연습의 필요성을 못 느꼈습니다. 인강도 딱 기본강의 들은 이후 정말 기본서를 회독하고 회독하고..시험 며칠 전에 전체 다 푸는데 얼마나 걸리나 시간 재보려고 모의고사 풀어본 것 빼고는 정말 시험 전날까지 기본서만 돌렸습니다. 행정학이 개인적으로 참 스트레스였는데 결국 시험날은 100점 받았네요.  강의는 각각 해커스에서 한국사 이중석 선생님, 행정법 김대현 선생님, 행정학 김만희 선생님 기본강의 수강했습니다.</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41480&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=5</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -16583,6 +18808,11 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41475&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=5</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -16625,6 +18855,11 @@
           <t>행정학: 서현쌤 기본,심화,기출 강의 다 수강함. 이거는 내용은 괜찮은데 외울게 진짜 너무 많고 방대해서 너무 막막해서 속이 답답했다. 하지만 정공법으로 그냥 강의도 공부다 생각하고 배속으로 듣고 그날 배운건 당일 복습하고 하니 기출까지 완강하니까 대충 뭔지 알겠어서 기출강의 끝나고는 서현쌤 기출문제집 무지성 회독함. 5회독 정도. 이것도 wox회독 나만의 변형버전으로 했음. 국가직때 65점 받고 충격 먹어서 지방직까지 열심히했더니 지방직은 95점 받음.</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41396&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -16663,6 +18898,11 @@
           <t>먼저 국어는 신민숙 선생님의 강의를 수강하였습니다. '쉬운국어 한권으로 끝'이라는 수업을 통해 기본을 다졌고, 독해, 논리, 문법 각각의 '강화 시리즈'를 통해 국어 내의 각 카테고리별로 문제들을 풀어보며 실전 감각을 키웠으며, 이후 '신유형기출 333제'를 통하여 그동안의 기출문제들로 보는 신유형 문제들로서 문제를 푸는 것 자체에 익숙해지려고 노력하였습니다.   다음으로 영어는 비비안 선생님의 강의를 수강하였습니다. 제가 어렸을 때부터 영어과목을 좋아했던 편이라 기본 베이스는 어느 정도 있다고 생각했지만 공무원 시험에 합격하기 위해선 해당 시험을 위한 공부가 필요하다고 생각하여 '공무원 기출보카 4000+' 교재를 구매해 4번 정도 반복하여 외웠습니다. 해당 수업은 듣지 않았고 모르는 단어는 발음을 들어보며 입에 붙도록 웅얼거리며 외웠습니다. 이와 동시에 '공무원 영문법 합격생 필기노트' 수업을 수강하며 공무원 문법의 기본기를 탄탄하게 다지려 하였습니다. 이후에는 '비비안 올인원 영문법'을 들으며 다시 정리한다는 느낌과 회독의 느낌을 가졌고 동시에 '공무원 영어 구조 독해 007' 수업을 들으며 독해 실력 또한 키우고자 하였습니다. 앞선 수업들을 다 수강한</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41302&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=13</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -16705,6 +18945,11 @@
           <t>&lt;행정학&gt;  가장 난이도가 있다고 생각한 행정학부터 공부를 시작하였어요.  선택한 기본서는 송상호 선생님의 명품행정학 (1,2권) 이었고 탁월한 선택이었다고 생각합니다.  이론이 너무 방대하면 부담스럽고 간략하면 이해하기 어려운데 이 부분의 밸런스를 가장 잘 맞춘 교재여서  혼자 회독을 늘려갈때마다 행정학에 대한 자신감도 함께 올릴 수 있었습니다!  많은 문제를 풀어도 계속 모르는 이론이나 헷갈리는 부분들이 많았는데 그럴때마다  '모르는 것이 나와도 당황하지 말고 답을 찾아보자' 라는 마인드를 셋팅하기 위해 노력했어요.</t>
         </is>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41279&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=14</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -16743,6 +18988,11 @@
           <t>행정학/서현 선생님 강의가 좀 길고 방대합니다. 그러나 처음 듣는 사람이 듣기에는 어려움이 없습니다. 기본강의 들을떄는 이해가 되지 않더라도 귀에 익힌다는 생각으로 끝까지 완강을 하는것을 추천드립니다. 서현 선생님의 기출 문제집이 좋습니다. 기본강의 후 기출문제집을 계속 회독하면서 부족한 개념을 계속 암기하는 방법으로 공부하였습니다.</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41179&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -16781,6 +19031,11 @@
           <t>법과목 또한 너무 생소했고 또 남은 기간이 많지 않았기에 시작은 막막했습니다. 하지만 김대현 선생님은 컴팩트한 교재와 강의를 사용하시기에 현재 제 상황에 딱 맞는 선생님이였습니다. 행정법에서 가장 중요한 건 흐름을 알고 문제가 풀리는 그 순간까지 참고 버티고 공부해 나아가는 것 같습니다.. 처음에는 아무리 풀어보려해도 안 풀리는게 행정법이지만 나중에 효자과목이 된다는 이유를 알게 됐습니다. 국가직땐 행정법에 빠져서 많이 공부하고 풀다보니 국가직땐 65점 나와서 만족했지만 지방직까지 가는 과정중에 국가직 면접과 행정학 빵구 메우기 때문에 집중을 못해서 지방직땐 성적이 비록 떨어졌습니다. 그래서 행정법 또한 기본강의 듣고 회독하고 문제 풀며 어느정도 성적이 올라왔을때 계속 감을 유지하고 부족한 부분을 채워나가는 것이라 생각합니다. 단원만 보고 한 부분만 본다면 어려운 과목이지만 기본강의가 끝나고 여러번 회독 했을때 과목 전체를 보면 행정학보다 훨씬 효자과목이라 생각합니다(기출회독 필수)</t>
         </is>
       </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40996&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=26</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -16815,6 +19070,11 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40670&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -16849,6 +19109,11 @@
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
         </is>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -16891,6 +19156,11 @@
           <t>행정법과 헌법은 황남기 선생님에게 의지했습니다. 교재가 너무 완벽해서 내용이 그 안에서 벗어나지 않았습니다. 역시 기본강의만 들었고, 곧바로 기출회독을 시작했고 이후 모의고사로 법과목을 공부했습니다. 특히 시험을 앞두고 나오는 최신판례 강의에서 그대로 문제가 나왔습니다.  법은 공부하면 하는만큼 나옵니다. 정말 정직합니다. 법에서 최대한 점수 챙긴다고 생각하고 메인으로 공부하세요. 절대 배신 안합니다. 저도 이번에 행정학에서 많이 까먹었지만 헌법 100점, 행정법 92점으로 선방해서 안정적으로 합격할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39624&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -16933,6 +19203,11 @@
           <t>행정학 : 송상호 선생님 저에게 가장 고통스러웠던 과목이었습니다. 행정법과 마찬가지로 쌩노베였지만 행정법과는 다르게 썰을 듣는다는 느낌이 아니라 학자들의 견해를 외워야 한다는 느낌이어서 가장 어렵게 다가왔습니다. 교재는 공무원 명품 행정학을 기본서로 이용했고 시험전까지 총 4회독을 하였습니다. 2회독을 한 이후 해커스 기출문제집을 2회독하고 마지막으로 기본서 2회독으로 마무리하였습니다.</t>
         </is>
       </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39106&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=52</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -16971,6 +19246,11 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38957&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=56</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -17005,6 +19285,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38788&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=64</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -17043,6 +19328,11 @@
           <t>공무원 준비는 부모님 권유로 시작하게 되었습니다. 하루 루틴은 국가직까지 3개월정도가 있었는데 하루에 3~4시간정도 공부했습니다. 국어,영어는 안하고 행정법,행정학,한국사 압축강의(행정법,한국사), 기본강의(행정학)만 봤습니다. 1,4,7,14복습법을 이때만 적용했습니다. 그래도 까먹었는데 깊은 잠재의식속에 남아있지 않았을까 생각됩니다.</t>
         </is>
       </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38757&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=65</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -17081,6 +19371,11 @@
           <t>특히, 동형모의고사의 경우 구할 수 있는 대로 구해서 양치기를 했는데, 외웠다고 생각했던 판례, 혹은 요약 되었거나, 전문이 나오면 틀리는 경우가 있었습니다. 하지만, 양치기를 통해 틀렸던 문제의 판례는 다시 기본서로 돌아와 공부하고, 중요한 쟁점, 혹은 자주 나오는 문구에 형광펜을 칠하고 외웠습니다. 아무래도 틀렸던 문제의 경우 기억에 더 잘 남아서, 형광펜 치고 다시 보았던 판례의 기억 저장 시간이 훨씬 길었습니다. 서현 선생님의 강의에서 가장 핵심이 되는 내용은 행정학적 마인드 같습니다. 사실 공부하는 내내 행정학적 마인드를 적립하는데 어려움이 있어서, 어떻게 해야 하지 고민이 많았지만, 강의노트 회독, 문제풀이를 하며 개념을 다잡고 그게 쌓이다 보니 저절로 적립이 가능했습니다.</t>
         </is>
       </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38729&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=66</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -17123,6 +19418,11 @@
           <t>2. 베이스 국어 수능 3등급, 영어 수능 2등급 토익 800점대, 한국사 수능1 한국사검정시험1급, 행정법 행정학 처음 공부함</t>
         </is>
       </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38678&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=68</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -17159,6 +19459,11 @@
       <c r="H21" s="3" t="inlineStr">
         <is>
           <t>- 행정학 사회과학을 전공해서 베이스가 조금 있었습니다. 강의는 서현 선생님의 강의를 들었습니다. 정리도 깔끔하고 설명도 이해하기 쉬워서 추천드립니다. 전체적으로 무난하게 공부했던 과목입니다.</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36046&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=109</t>
         </is>
       </c>
     </row>
@@ -17191,6 +19496,11 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35634&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=124</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -17225,9 +19535,14 @@
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35196&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=136</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H23"/>
+  <autoFilter ref="A1:I23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17238,7 +19553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -17249,6 +19564,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -17292,6 +19608,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -17330,6 +19651,11 @@
           <t>- 2024.07 ~ 2025.06 (약 1년)   2. 기본 베이스 지거국 영어영문학과 / 토익 900점대 후반 / 한능검 1급   3. 하루 루틴 수험 생활 초기에는 집 근처 도서관에서 공부를 했는데 집중이 잘 안 돼, 해커스 스파르타 독서실을 다녔습니다. 월요일부터 토요일까지는 아침 7시에 기상 후 아침 8시부터 밤 10시까지 독서실에서 공부했고 일요일은 쉬었습니다.   4. 공부 방향 공부 방향을 잘 설정하는 것이 단기 합격의 지름길이라고 생각합니다. 국어, 영어는 제가 자신 있어 하는 과목이었고 기초도 어느 정도 있었기 때문에 공부 시간을 최대한 줄이고 남는 시간을 한국사, 행정법, 행정학에 할애했습니다. 한국사 또한 제가 자신 있어 하는 과목으로 기초도 있었지만 국어, 영어와는 다르게 암기 과목이라 휘발성이 강해 공부량을 줄이지는 않았습니다. 공부 시간을 대략적으로 따져본다면 행정학 &gt; 행정법 &gt; 한국사 &gt; 영어 &gt; 국어 순으로 시간을 투자했습니다.   5. 과목별 공부법 국어 95점 국어는 학창 시절 열심히 했었기 때문에 자신 있는 과목이었습니다. 인사혁신처 예시 문제를 풀어보니 별다른 공부 없이도 충분히 풀 수 있는 난도여서 국어에 많은 시간을</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41522&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=4</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -17372,6 +19698,11 @@
           <t>2) 행정학 90점: 해커스 김만희 선생님 행정학은 행정법과 반대로 처음엔 들을 만한데 시간이 지날수록 이게 공부가 되는 건가? 싶었습니다. 이번 지방직 시험 치는 주에 올해 국가직 문제를 풀어봤는데 행정학 때문에 이번엔 힘들겠구나 하고 들어갈 정도였습니다. 역시 행정법과 마찬가지로 5월부터 8월까지 개념강의를 들었지만 머리에 남는 게 없다고 느꼈습니다. 그리고 당시에 헌법 1회독을 같이 진행하던 차라 행정법보다 2회차가 늦어졌습니다. 행정학은 행정법처럼 3월부터 강의 다시 듣지 않고 복습-기출문제 풀기 방식으로 진행해서 6월 중순쯤 2회독을 마무리했습니다. 행정법과 마찬가지로 행정학도 느낌은 노베이스나 마찬가지긴 했지만 1회차를 했다는 게 알게 모르게 2회차에서 큰 도움이 됐습니다. 교재가 꽤 상세하게 개념을 다루고 있고 강의에서 처음에는 어느 것을 먼저 봐야 할지 잡아주시고 복잡한 용어를 실전개념으로 잘 풀어주셔서 도움이 많이 됐습니다. 특히 요약서인 또또북이 잘 정리되어 있는데 2회차 정도부터는 복습하면서 내용을 채워넣으면 단권화가 정말 잘 될 것으로 생각합니다. 저는 시험이 임박해서 또또북을 썼지만 초반부터 사용하면 더 효과가 좋았을 듯합니다. 1회차</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41486&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=5</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -17414,6 +19745,11 @@
           <t>이전부터 여러 짧은 업무를 전전하면서 혹은 전공이외 여러 진로를 고민하던 도중 일반행정 공무원에 도전하기로 마음을 먹었습니다. 그러나 처음 생각을 했던 3~4년여간은 다른 일과 병행으로 사실상 큰 신경을 쓸 수 없었고, 본격적인 공부는 8개월 ~ 1년을 잡고 시작했습니다.   여러 과목이 있었지만 생소했던 과목인 행정학 행정법과 나중에 시험이 임박했을 때 단기적으로 끌어올리기 어려운 영어부터 시작해야 한다고 판단했습니다. 영어 단어는 적어도 이틀에 한 챕터를, 문법은 하루에 하나라도 알고가자는 느낌으로 하루 1시간 정도를 투자했고, 나머지 시간은 기본 강의를 듣는데 충실하려 했습니다. 다른 좋은 강의학원도 많았지만 적극적인 홍보와 집에서의 접근성으로 보아 해커스 패스를 선택하기로 하였습니다.</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41384&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -17448,6 +19784,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41365&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -17482,6 +19823,11 @@
           <t>[공유하고 싶은 학습&amp;시험 꿀팁] 행정학은 서브 노트와 인덱스 카드로 저만의 요약집을 틈틈이 작업해두었습니다. 서브 노트는 주교재를 바탕으로 단원별로 큰 제목과 소제목을 다 적은 후에 계속 헷갈리는 개념들을 옆에 조금씩 적어가며 내용을 붙였습니다. 그래도 자꾸 틀리는 것들, 변수 등 낯설고 휘발성이 강한 내용들은 포스트잇에 적어 인덱스 카드에 서브노트 단원별 순서대로 옮겨 붙여서 독서실에서 집에 가는 동안 계속 눈에 익히려고 노력했습니다.</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41354&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=11</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -17516,6 +19862,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41345&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=11</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -17554,6 +19905,11 @@
           <t>3. 행정학 - 서현 선생님 저는 서현 선생님 강의를 제일 열심히 본 것 같습니다. 행정학도 아예 처음보는 과목이라 감도 안 잡혔고, 직전 해에 아주 어려운 난이도로 나와 긴장이 됐었습니다. 하지만 행정학도 현 행정학 기본을 다 수강하고 본인 나름대로 단권화하여서 시간 날때마다 꾸준히 본다면 충분히 좋은 점수를 얻을 수 있습니다. 전 기본강의만 다보고 문제풀이로 넘어가 모의고사도 다 풀고, 한글 파일로 제가 직접 압축해서 무한 암기 반복했는데, 좋은 점수가 나올 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41283&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=14</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -17592,6 +19948,11 @@
           <t>◆행정학- 서현 선생님 개인적으로 행정학이 제일 어려웠습니다... 처음 접하는 개념들이 많은데 또 이것들이 두루뭉실하게 둥둥 떠다니는 느낌이랄까요... 시간이 없다고 판단해서 심화를 듣지 않고 기본이론에서 바로 기출문제풀이로 넘어갔는데, 고득점을 위해서라면 꼭... 심화를 들으시길... 시험 전에는 행정학 단권화 특강으로 전체적인 개념을 쓱 흝을 수 있어서 좋았습니다. 행정학도 외우지 않으면 못푸는 과목이라고 생각해서 시험이 가까워질 수록 개념과 법령등을 외우는 데 시간을 썼습니다.</t>
         </is>
       </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41205&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=18</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -17626,6 +19987,11 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41195&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=18</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -17664,6 +20030,11 @@
           <t>행정학 기본문제집보고 기겁했던게 엊그제 같네요. 강사님의 강의노트 덕분에 용기내서 시작했습니다. 요약이 정말 잘 되어있어요. 모든 강의 들을 때 강의노트 옆에 두고 들었습니다. 중요도도 체크해주셔서 복습할 때 그나마 순조로웠어요. 심화강의는 문제풀이 위주로 하시는데, 전 인강 들으면서 풀었습니다. 심화문제 단원별로 끝날 때마다 강의노트와 심화문제 번갈아보면서 복습했습니다. 신경향이론도 특강 강추합니다. 문제 여기서 많이 나왔어요. 배속 1.8</t>
         </is>
       </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41174&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -17698,6 +20069,11 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41129&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -17732,6 +20108,11 @@
           <t>제 하루 루틴은 오전 7시 기상 후 8시부터 12시까지 기본 이론 복습, 점심 후엔 1시부터 5시까지 문제 풀이, 저녁에는 오답 정리와 암기 위주로 복습하며 총 10시간 이상 공부했습니다. 필수 과목은 행정법과 행정학이었는데, 행정법은 조문과 판례 정리를 반복했고, 행정학은 기출 중심으로 흐름을 파악한 후 단권화를 통해 정리했습니다. 행정법은 처음 공부할 때에는 아무것도 모르고 공부해도 막막한 느낌이 들었지만, 익숙해지고 공부를 하다보니 제일 자신있는 과목이 되었습니다. 행정법이 어렵지만 여러분 할 수 있습니다. 국어는 고혜원 선생님의 문법 정리와 어휘 암기가 큰 도움이 되었고, 한국사는 최진우 선생님의 흐름 중심 강의로 이해력을 높일 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41060&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=24</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -17768,6 +20149,11 @@
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>행정학: 서현 수강 강의 내역: 기본 강의, 기출 강의, 법령 특강 전시리즈, 하프 전시리즈, 실전 동형 강의</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40785&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
         </is>
       </c>
     </row>
@@ -17800,6 +20186,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40692&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=31</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -17830,6 +20221,11 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40688&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -17864,6 +20260,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40670&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -17898,6 +20299,11 @@
           <t>10월부터 기본강의를 듣고 시험 직전에 법령특강, 최신판례특강을 들었습니다. 기본강의를 2배속으로 빠르게 듣고 듣는 중에 기출문제를 바로바로 풀었습니다. 기본강의 끝낸 후에는 기출 회독을 계속 돌렸고, 강의 중에 회독 돌리는 방법을 알려주셔서 시험 한 달 전까지는 계속 기출만 보았으며, 한 달 남았을 때는 법령과 최신판례를 같이 보았습니다. 기출을 많이 보다보면 기본서를 후에 회독 돌릴 때에는 생소한 부분만 보이기 때문에 더 빠르게 회독을 돌릴 수 있었습니다. 황남기 선생님은 특별히 외우는 방법을 알려주시지는 않지만 판례 배경 등을 설명해주셔서 더 기억에 남을 수 있었던 것 같습니다. 또한 비슷한 주제로 위헌, 합헌으로 나뉘는 판례들은 암기하기 위해 따로 노트를 만들었는데 시험 직전에 다시 정리했던 것이 실제 시험장에서 너무 큰 도움이 되었습니다.   (행정법-황남기 선생님, 함수민 선생님) 헌법을 먼저 들었기 때문에 행정법 또한 황남기 선생님을 선택해서 들었습니다. 헌법과 공부방법은 비슷하나 행정법각론 부분은 시험 3달 전에 전년도 강의를 가볍게 황남기 선생님 강의로 듣고 2달 전에는 당해연도 함수민 선생님 강의를 들었고, 시험 한 달 전부터는 각론기출문제</t>
         </is>
       </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -17928,6 +20334,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39664&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -17970,6 +20381,11 @@
           <t>행정법과 헌법은 황남기 선생님에게 의지했습니다. 교재가 너무 완벽해서 내용이 그 안에서 벗어나지 않았습니다. 역시 기본강의만 들었고, 곧바로 기출회독을 시작했고 이후 모의고사로 법과목을 공부했습니다. 특히 시험을 앞두고 나오는 최신판례 강의에서 그대로 문제가 나왔습니다.  법은 공부하면 하는만큼 나옵니다. 정말 정직합니다. 법에서 최대한 점수 챙긴다고 생각하고 메인으로 공부하세요. 절대 배신 안합니다. 저도 이번에 행정학에서 많이 까먹었지만 헌법 100점, 행정법 92점으로 선방해서 안정적으로 합격할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39624&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -18004,6 +20420,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39078&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=52</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -18042,6 +20463,11 @@
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38957&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=56</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -18076,6 +20502,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38878&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=60</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -18118,6 +20549,11 @@
           <t>2. 베이스 국어 수능 3등급, 영어 수능 2등급 토익 800점대, 한국사 수능1 한국사검정시험1급, 행정법 행정학 처음 공부함</t>
         </is>
       </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38678&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=68</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -18156,6 +20592,11 @@
           <t>5.행정학 서현 선생님 강의를 들었습니다. 행정학도 내용이 엄청 방대한데, 단권화 노트로 필요한 것만 볼 수 있어서 좋았습니다. 또한, 저같이 행정학을 전혀 모르는 공대생도 이해할 수 있도록 쉽고 자세히 설명해 주셔서 좋았습니다.</t>
         </is>
       </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38093&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=83</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -18194,6 +20635,11 @@
           <t>- 행정학 : 서현 선생님 강의와 커리큘럼이 짜임새가 있습니다. 강의 경력도 워낙 기시고 전공자셔서 전문성은 말할 것도 없구요. 딕션이나 목소리도 좋으셔서 강의 듣는데에 매우 편했습니다. 입문-기본-심화-문풀-실전동형 이 5단계가 너무나도 튼튼하게 갖추어져 있어서, 커리큘럼대로만 꾸준히 따라가다 보면 서현 선생님이 수업 중 계속해서 강조하시는 행정학적인 마인드가 머리에 장착됩니다.강의의 특장점으로는 현 행정학 강의노트 라는 단권화 노트가 있는데, 따로 개인적으로 단권화할 필요 없이 300페이지 가량 되는 이 책에 강의 들으면서 꾸준히 개념 추가하고, 책정리 해가다 보면 80점 라인 방어하는 데에는 차고 넘칩니다. 기본심화 강의 진행도 기본서는 서브로 하고 이 강의노트 위주로 해 주셔서, 방대한 행정학의 분량을 획기적으로 줄여서 기본을 쌓아올리는 데에 큰 도움이 된 것 같습니다.</t>
         </is>
       </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36748&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -18232,9 +20678,14 @@
           <t>행정학 서현 교수님 강의를 들었습니다. 기본서 위주의 공부가 아닌 필기노트를 따로 사서 필기노트 위주로 하는 강의였는데 사람마다 호불호가 갈릴 법한 학습방법이란 생각이 들었습니다. 하지만 두꺼운 기본서를 단권화로 양을 줄여 자주 보는 것은 공부의 중요한 과정이니 저는 나쁘지 않은 방식이라 느꼈습니다.</t>
         </is>
       </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36138&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=106</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H27"/>
+  <autoFilter ref="A1:I27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18245,7 +20696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18256,6 +20707,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -18299,6 +20751,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -18337,6 +20794,11 @@
           <t>행정학 (90점) 김만희 선생님 기본이론을 먼저 수강하였고, 이후에 기출 문제집 회독하다가 서현 선생님 모의고사 수강했습니다. 행정학은 하나의 문제집을 여러 번 회독하는 것보다는 여러 문제집을 보며 다양한 표현들을 익히는 게 중요한 것 같습니다. 처음보는 단어나 문제가 등장해도 어떻게 풀어나갈지 요령을 익히는 게 필요해요.</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40498&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=38</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -18375,9 +20837,14 @@
           <t>공무원 준비는 부모님 권유로 시작하게 되었습니다. 하루 루틴은 국가직까지 3개월정도가 있었는데 하루에 3~4시간정도 공부했습니다. 국어,영어는 안하고 행정법,행정학,한국사 압축강의(행정법,한국사), 기본강의(행정학)만 봤습니다. 1,4,7,14복습법을 이때만 적용했습니다. 그래도 까먹었는데 깊은 잠재의식속에 남아있지 않았을까 생각됩니다.</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38757&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=65</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:I3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18388,7 +20855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -18399,6 +20866,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -18442,6 +20910,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -18476,6 +20949,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41900&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -18510,6 +20988,11 @@
           <t>3. 나의 수험 계획표 다양한 방법들을 시도해보았지만, 저는 앞서 말했던 것처럼 하루에 4과목을 전부 보는 방식이 저에게 잘 맞아서 그렇게 진행했습니다. 우선 공부는 8시 이전에 열품타 착석스터디를 통해 스스로를 컨트롤 하며 시작했습니다. 행정학 2시간(이때 말하는 시간은 최소 시간입니다. 인강이나 문풀 상황에 따라 10-15분 정도는 더 진행할 때가 많습니다) -&gt; 행정법 1시간 -&gt; 약 12시쯤 점심식사 및 식곤증을 물리치기 위한 샤워 등 재정비 -&gt; 2시 쯤. 경제학 2시간 (그나마 손을 가장 많이 써서 덜 졸려서 이걸 이때 했습니다) -&gt; 1시간 정도 행정법 추가 공부 -&gt; 6시쯤 저녁 식사 후 휴식 -&gt; 2시간 동안 헌법 마무리</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41729&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -18548,6 +21031,11 @@
           <t>1) 4월~6월 : 기본 이론 강의 수강 행정법, 헌법 (홍대겸)/ 행정학 (서현) 기본 강의를 수강하였습니다. 두 분을 선택한 계기는 좀 불순한데, 일단 교재가 없어도 수업을 들을 수 있게 판서 혹은 PPT를 활용하는 수업방식이 마음에 들었습니다. 불순한 계기와 달리, 결과적으로 두 분을 선택하여서 좋은 결과를 얻을 수 있었습니다. 홍대겸 선생님의 가장 큰 장점이자 매력은 컴팩트함입니다. 법학을 이해하는 데 필요한 기본적인 논리는 놓치지 않고 설명해주시되 디테일을 과감하게 생략하며 빠르게 진도를 나가시는 타입이십니다. 그래서 강의 회차와 시간 모두 짧습니다. 가볍고 빠르게 나아가는 수업은 빠르게 기본 이론을 배우고 싶었던 당시의 저에게는 최고의 선택이었습니다. 설명도 가능한 직관적이고 단정적으로 하셔서 법학이 까다롭고 어렵다는 선입견을 깨시고 부담을 많이 덜어주셨습니다. "빠른 1회독" 강의도 큰 도움이 되었습니다. 기초 이론을 가볍게 맛본 수험생을 대상으로 하는 강의인데, 기초 강의 때는 생략하였던 변칙적인 판례를 설명해주시기도 하고, 말 그대로 빠르게 행정법 전체를 복습할 수 있습니다. 서현 선생님의 장점은 체계성입니다. 그동안의 기출 경향을 모두 꿰고</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41687&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -18582,6 +21070,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41427&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -18616,6 +21109,11 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41426&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -18654,6 +21152,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41409&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=8</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -18688,6 +21191,11 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41372&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -18722,6 +21230,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41371&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -18756,6 +21269,11 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41368&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -18790,6 +21308,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41360&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -18828,6 +21351,11 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41337&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=12</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -18866,6 +21394,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr"/>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41329&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=12</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -18900,6 +21433,11 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41322&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=12</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -18934,6 +21472,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41309&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=13</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -18968,6 +21511,11 @@
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41280&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=14</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -19002,6 +21550,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41270&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -19036,6 +21589,11 @@
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41269&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -19066,6 +21624,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41254&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=15</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -19096,6 +21659,11 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41244&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=16</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -19138,6 +21706,11 @@
           <t>안녕하세요 공부를 시작한 날이 엊그제 같은데 합격 수기를 쓰고 있으니 감회가 새롭습니다. 학창시절 공부를 썩 잘하는 편이 아니었어서 국어 영어 행정학 행정법 4과목은 노베이스로 시작했고, 한국사는 그나마 학창시절에 좋아하던 과목이었어서 기억이 따로 잘 나는 건 아니지만 즐겁게 공부했습니다</t>
         </is>
       </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41237&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=16</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -19180,6 +21753,11 @@
           <t>행정학 - 김만희 선생님, 행정학을 3개월만에 마스터해야하는 상황에 막막해 있다가 마니쌤의 OT를 듣고 믿고 따르기로 결정했습니다. 기본이론, 기필코 실력업, 파이널600제 3회독하고 모든 특강을 들었습니다. 600제 2회독 + 스스로 1회독 하니까 어느정도 행정학이 눈에 들어왔고 선생님께서 올해 중요하게 생각하시는 부분들은 보고 또 봤습니다. 시험 전날 푼 작년 지방직문제가 50점정도라 역시 3개월가지고는 되지 않으려나 했지만 시험장에서 문제를 보는데 술술풀렸고 정말 선생님께서 말씀하신 문제가 그대로 나왔습니다. 감탄을 하며 시험을 본 기억이 있습니다ㅎㅎ 저는 행정학은 무조건 마니쌤 추천합니다. 그리고 추가로 또또북은 정말 요물입니다!</t>
         </is>
       </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41232&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -19214,6 +21792,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41198&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=18</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -19244,6 +21827,11 @@
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41194&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=19</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -19278,6 +21866,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41160&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=20</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -19312,6 +21905,11 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41134&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -19346,6 +21944,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41102&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=22</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -19380,6 +21983,11 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41091&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=22</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -19416,6 +22024,11 @@
       <c r="H29" s="3" t="inlineStr">
         <is>
           <t>행정학은 제 전공인지라 학습을 하는 데 있어서 크게 어려움이 없었습니다. 전공 학점도 4점대로 항상 잘 맞아왔기 때문에 한 번씩 들어봤던 용어와 내용인지라 노베이스이신 분들보다는 좀 수월하게 공부했던 것 같습니다. 송상호 선생님은 수업 때도 공부할 것들만 딱 알려주시면서 수업하시고, 최근의 출제 경향까지 알려주시면서 수업해주셔서 강약조절을 할 수 있었습니다. 저는 기본강의와 심화강의를 듣고, 기출문제와 신경향테마, 그리고 모의고사까지 커리큘럼을 따라가며 행정학 학습을 했습니다.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41079&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=23</t>
         </is>
       </c>
     </row>
@@ -19452,6 +22065,11 @@
           <t>5.행정학 첫 시험에서 거의 과락인 점수를 맞고 기출을 제일 많이 돌렸던 과목이에요  너무 지루하지만 반복하다보니 답을 고르는 요령이 생기더라구요  그리고 행정학은 기출에 모의고사도 추가로 하시면 좋아요!!</t>
         </is>
       </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41046&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=24</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -19490,6 +22108,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41035&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=25</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -19524,6 +22147,11 @@
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41028&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=25</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="55" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -19562,6 +22190,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40963&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=28</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="55" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -19596,6 +22229,11 @@
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40778&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="55" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -19630,6 +22268,11 @@
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr"/>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40707&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=31</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="55" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -19664,6 +22307,11 @@
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40466&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=40</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="55" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -19702,6 +22350,11 @@
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr"/>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39770&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="55" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -19740,6 +22393,11 @@
           <t>오후 3시~4시 30분에는 체력관리와 외부 공기룰 쐬고자 집 앞 공원을 가볍게 뛰고 헬스를 했습니다. 저녁식사 후에는 법 과목과 행정학의 다음날 진도 초반을 용어는 대충 들어보자 하는 마음으로 예습을 시간이 허락하는 만큼 했습니다. - 국어 신민숙 선생님: 처음에는 문법 위주로 강의를 진행하셨습니다. 불규칙한 품사들을 필기해주셨는데 도움이 많이 되었습니다. 문학과 비문학의 경우 제가 속독에 어려움을 느껴 선생님께서 지정해주신 시간 안에 겨우 맞춰 풀었었는데 알려주신 속독 방법을 적용하니 시간이 남아 다시 체크할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39340&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=49</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="55" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -19782,6 +22440,11 @@
           <t>올해 : 국어 95 영어 85 한국사 95 행정법 90 행정학 75 코로나 기간에 공시를 시작해서 1달만에 초시를 보고, 작년엔 1년을 열심히 공부했지만 재시에서 면탈했습니다. 그래서 시험은 총 3번을 봤고, 두번째 면접에서 보통을 받아 올해 지방공무원 행정 9급 발령을 받았습니다.</t>
         </is>
       </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39325&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=49</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="55" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -19820,6 +22483,11 @@
           <t>2024 서울시 일반행정 9급 최종합격 수기입니다.   저의 수험생활은 약 1년 8개월 정도였습니다. 저는 필기 점수가 커트라인보다 1점이 높았기에 면접에도 혼신의 힘을 기울였습니다. 최종발표 때까지 안심을 할 수 없었기에 초조한 마음으로 발표를 기다린 것이 생각납니다.   필기의 경우에는 한국사는 베이스가 있었기에, 나머지 4과목에 시간을 많이 할애하였고, 한국사는 토, 일요일에 기출문제 중심으로 감을 잃지 않게 공부를 하였습니다.   국어는 비문학은 상대적으로 자신이 있었기에, 문법에 시간을 많이 투자하였고, 한자도 틈틈이 짬을 내어 보았습니다. 강의는 신민숙 선생님 강의를 수강하였습니다.   영어는 크게 단어, 문법, 독해로 나누어서 2:3:5의 비율로 공부하였습니다. 비비안 선생님 강의를 들었는데, 큰 도움이 되었습니다. 단어의 경우에는 독해를 하면서 모르는 단어를 중심으로 파생단어까지 공부를 하였는데 괜찮은 효율성을 보인 것 같습니다.   한국사는 이중석 선생님의 기출문제만을 보았습니다.   행정법은 함수민 선생님 강의를 3회독 한 후, 기출문제 강의를 들었습니다. 처음에는 난해하였지만 회독이 늘어날수록 틀이 잡혀서 효자 과목이 되었습니다.   행정</t>
         </is>
       </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39256&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=50</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="55" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
@@ -19862,6 +22530,11 @@
           <t>행정학 - 서현 현 행정학 강의노트에 잘 정리되어있으니까 수업 들으시면서 필요한 내용만 따로 정리하면 됩니다. 기본강의에 충실하시길 바랍니다. 심화강의에서도 기본강의에서 다루신 내용들 그대로 다시 해주셔서 공부하기 편했어요. 기출문제집의 문제 양이 정말 많은데, 저는 세 번 정도 풀었어요. 여러번 풀어도 틀리는 문제는 계속 틀리더라고요. 어제 틀린 문제를 오늘 또 틀리지 않도록, 문제 자체보다는 선지를 하나하나 꼼꼼히 분석하는 게 중요하다고 생각해요. 행정학은 사실 제가 제일 어려워하는 과목이었어요. 2024 지방직 시험이 많이 어려웠어서 솔직히 말하면 마킹 도중에 울었습니다...ㅎㅎ 공부하지 못한 내용을 너무 많이 물어봐서 아쉬웠고, 성적도 많이 낮았지만 역시 다같이 어려웠나봐요.</t>
         </is>
       </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39185&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=51</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="55" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -19900,6 +22573,11 @@
           <t>23년도 6개월 동안은 서현 선생님 커리를 따랐고, 23년 9월부터 24년 6월 마지막 시험까지는 송상호 선생님 커리를 따랐습니다. 서현 선생님은 두문자를 따주셔서 암기할 때는 도움이 되었습니다만, 배워야하는 이론의 범위가 넓어지면서 그 시험의 추세에는 송상호 선생님의 커리가 도움이 되겠다고 판단하여 선생님을 바꾸어 수강하였습니다. 결론적으로는 맞는 판단을 하였고, 행정학에서 중점되는 이론을 바탕으로 관련 이론으로 확장하여 가르쳐주시기 때문에 처음보는 이론들이라도 당황하지 않고 비슷하게 적용하여 풀어낼 수 있었습니다.   [마치면서] 대부분의 수험생들은 시험을 준비하는 동안에는 쉬어도 마음이 편하지 않아 마음껏 휴식을 취할 수도 없고, 공부를 하면서도 뒤쳐지고 있다는 불안함의 연속일 것이라 생각합니다. 하지만 공부를 더 오래 집중하기 위해서는 잘 쉬는 것 또한 필수이기 때문에 휴식에 너무 큰 죄책감을 가지지 않으면 좋겠습니다.  커뮤니티에 보면 ‘시험 준비 중인데 해외여행가도 될까요?’ ‘주말에 하루종일 쉬었어, 망했다ㅠㅠ’ 라는 글을 종종 보곤했는데, 공부가 너무 안되는 때면 당연히 뇌에도 휴식을 줘야하고, 또 그렇게 푹 쉬어줘야 그 다음날 더 집중해서 공</t>
         </is>
       </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39082&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=52</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="55" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -19938,6 +22616,11 @@
           <t>3. 공부법&amp; 수강한 선생님  특별히 저만의 공부법이라 할만큼 독특한 무언가를 하지는 않고 거의 대부분 학원의 커리큘럼을 따라갔습니다. 행정법과 행정학은 매년 조금씩 새로운 내용이 나오기 때문에 작년 시험을 대비했었음에도 올해 또 기본과정부터 복습하는 기분으로 순서대로 다시 들었고, 국어의 경우 매년 크게 변하는 것이 없기 때문에 저에게 부족한 부분인 어법과 어휘 위주로 들었습니다.  행정법은 홍대겸 선생님의 과정을 쭉 따라 들었는데 정말 이해하기 쉽게 설명해주시고 재밌어서 좋았습니다. 또 단원별 기출문제집이 얇은 편이라 공부 부담이 적고, 빈출 위주로 구성되어 있어 기본기를 확실히 다지기가 좋았습니다.  행정학의 경우 서현 선생님과 송상호 선생님의 강의를 섞어 들었는데, 신경향 문제가 튀어나오는 것이 신경쓰여 최대한 다양한 이론들을 접하고 싶었기 때문입니다. 시험이 다 끝난 뒤 이리저리 시행착오를 겪었던 것들을 되짚어 생각해보니 신경향도 아주 무시할 수는 없지만 가장 중요한 건 기출문제의 완전한 숙달인 것 같습니다.  국어는 신민숙 선생님의 강의를 통해 준비했습니다. 어휘와 어법은 분량이 방대하다고 생각하는데 선생님이 가장 필요한 부분만 고르고 골라 꼼꼼히</t>
         </is>
       </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39063&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=52</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="55" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -19976,6 +22659,11 @@
           <t>각 과목을 3회독 정도 했을 경우 어느 정도 중요사항들은 까먹지 않게 되었고 그 이후에는 기출문제를 풀면서 암기내용을 다시 재점검했습니다. 강의는 국어 신민숙 선생님, 영어 비비안 선생님, 행정법 황남기 선생님, 한국사 이중석 선생님, 행정학 서현 선생님 황남기 선생님 기본 개념강의를 듣고 판례 내용만 따로 타이핑 해 뽑아서 들고다니면서 외웠습니다. 행정법의 경우 90% 이상은 판례에서 출제된다고 생각합니다 개념이 많이 어렵더라도 반복해서 접하다 보면 자연스럽게 개념이 이해되었던 것 같습니다.</t>
         </is>
       </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39003&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=54</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="55" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -20010,6 +22698,11 @@
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr"/>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38989&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=55</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="55" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -20044,6 +22737,11 @@
           <t>행정학 75 행정학은 한 강사분들을 커리를 타다가 다른 강사님들로 이동하면서 들어서 잘 설명드리기는 어렵지만 이번시험을 통해서 깨달은 것은 기출로 풀수 있는 점수는 확실히 확보한다면 어렵고 지엽적인 문제를 틀려도 합격하는 데에는 큰 요인으로 작용하지 않는다는 것입니다. 왜냐하면 다른 사람들도 다 같이 틀리기 때문입니다. 그러니까 기출을 확실히 정복하는 것이 중요하다고 생각합니다</t>
         </is>
       </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38948&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=57</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="55" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
@@ -20074,6 +22772,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38942&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=57</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="55" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -20108,6 +22811,11 @@
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38940&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=57</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="55" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
@@ -20146,6 +22854,11 @@
           <t>-공유하고 싶은 학습 &amp; 시험 꿀팁 : 일단 기본적으로 암기할 건 확실하게 암기를 해줘야 합니다. 국어에서 쉬워졌다고는 하지만 한자나 맞춤법을 외워주고, 영어는 영어단어를 기본으로 문법을 확실히 외워줘야 합니다. 한국사의 경우에는 암기가 당연히 기본이지만 스토리를 생각하며 공부를 하면 시대순도 자연스럽게 학습이 되기 때문에 스토리텔링을 하면서 공부하시면 좋을 거에요. 행정법이나 행정학은 사실 다른 방법이 없습니다. 전공자가 아니라면 정석대로 숙달될때까지 무한 반복을 하셔야 원하는 점수대를 얻으실 수 있을 것입니다.</t>
         </is>
       </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38880&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=60</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="55" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -20184,6 +22897,11 @@
           <t>2024년도 공무원 시험에 합격하면서 그동안의 노력을 돌아보고, 합격을 준비하는 분들께 조금이나마 도움이 되고자 저의 합격 수기를 공유합니다. 제가 주로 수강한 강좌는 서현 선생님의 행정학 강의, 홍대겸 선생님의 행정법 강의, 그리고 이중석 선생님의 한국사 강의였습니다.</t>
         </is>
       </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38871&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=60</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="55" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
@@ -20222,6 +22940,11 @@
           <t>마지막으로 행정학은 서현 강사님 강의를 들었습니다. 서현 강사님의 가장 큰 장점은 각 주제마다 시험 빈도를 알려주시고 중요도를 정확히 정해주신다는 점이라고 생각합니다. 그래서 공부를 할 때 어느 부분을 집중적으로 해야하는지 알 수 있었습니다. 또한 어려울 수 있는 행정학 내용을 이해하기 쉽게 가르쳐주시고, 기본강의와 심화강의가 나누어져 있어서 좋았습니다.</t>
         </is>
       </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38812&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=63</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="55" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -20256,6 +22979,11 @@
       </c>
       <c r="G52" s="2" t="inlineStr"/>
       <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38805&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=63</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="55" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
@@ -20290,6 +23018,11 @@
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38774&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=64</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="55" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -20320,6 +23053,11 @@
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38713&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=67</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="55" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
@@ -20354,6 +23092,11 @@
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38652&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=69</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="55" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -20392,6 +23135,11 @@
           <t>&lt;행정학&gt;  서현 선생님 커리큘럼을 쭈욱 따라갔어요. 사실 이번에 합격한 지방직에서는 높은 점수를 받지 못했지만 정말 깔끔하고 체계적인 수업이었구나를 느낀게 두달간 기본 이론 / 심화 이론 이렇게 이론 수업을 빠르게 마치고 국가직 시험을 연습삼아 보았을 때 무려 80점이라는 성적을 받을 수 있었던 것을 보고 행정학이라는 과목은 이대로만 하면 되겠구나 싶기도 했습니다. 법령특강 수업해주시는 것도 도움을 많이 받았습니다! 무료강의이니 꼭 들어보시길 추천해요.</t>
         </is>
       </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38649&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=69</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="55" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
@@ -20430,6 +23178,11 @@
           <t xml:space="preserve">국어 – 신민숙쌤 커리 (90점) 커리대로 선생님이 하라는 대로 하면 실력 느실 거에요! 비문학는 거의 매일 3문제씩 풀려고 노력했고 한자성어300으로 사자성어만이라도 마스터했습니다. 저는 타학원 선생님들 것도 이것저것 많이 푸는 게 도움이 됐어요! 여러 문제지를 접해야 실제 시험에서 당황하지 않게 되더라구요.  영어 – 김송희쌤 커리 (90점) 영어는 쌩노베입니다! 그래서 합격이 오래 걸렸어요ㅜ 문법은 진짜 송희쌤이 도움이 많이 됐습니다. 저는 매일 하루도 안 빠지고 하프로 감을 잃지 않게 매일 풀었습니다.(제일 중요!) 점수에 연연해하지 마시고 꼭 오답만 철저히 하세요. 그리고 전 단어암기에 약해서 무슨 기출보카 4000 이런 건 거의 안 보고 정말 타학원에 콤팩트한 필수단어 100개만 외웠습니다. 이렇게만 외워도 저는 단어가 커버돼서 그런 거니까 따라하지는 마세요ㅜㅜ  한국사 – 이중석쌤 커리 (95점) 강의가 너무 재밌어서 지루하지 않았어요. 하지만 한국사 점수가 증말 안 나와서 꽤 고생했어요... 그래서 그냥 무식하게 외우고 기출 몇 십번 봤습니다. 기출 중요!!!!! 기화펜으로 여러번 푸는 게 짱! 어느 정도 기출이 익숙해지면 꼭 모의고사 여러개 </t>
         </is>
       </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38624&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=70</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="55" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -20464,6 +23217,11 @@
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38587&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=72</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="55" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
@@ -20502,6 +23260,11 @@
           <t>2년 간의 교육행정직을 준비했지만 합격이 정말 힘들었습니다. 솔직히 2년 준비를 끝으로 포기하려고 했지만 딱 1년만 더 해보자라는 마음으로 일반행정으로 직렬을 바꿔 도전하게 되었습니다. 국어 신민숙 선생님 강의를 들었습니다. 대학 전공수업으로 한자를 배웠어서 한자는 걱정하지 않았습니다. 공부하기 싫을 때는 한자성어 300책 한 번씩 훑으며 눈으로 익혔습니다. 제일 걱정했던 것은 문법이었는데 선생님이 쉽고 깔끔하게 가르쳐주셔서 문제에 적용하기 쉬웠습니다. 선생님 덕분에 좋은 점수를 맞을 수 있었습니다. 한국사 한국사는 이중석 선생님을 듣기 전과 후로 나뉠정도로 정말 큰 도움이 되었습니다. 수업 시작 전 읽어주시는 시도 정말 좋았고 수업도 정말 재밌고 오래 기억할 수 있었습니다. 저는 오히려 강의수가 많은게 꼼꼼하고 천천히 배울 수 있어서 좋았습니다. 좋은 말씀도 많이 해주셔서 수험기간동안 흔들리지 않고 공부할 수 있었습니다. 영어 비비안 선생님 강의를 들었습니다. 초반에는 여러 선생님 강의를 듣다가 비비안 선생님으로 정착했습니다. 완전 노베이스였는데 선생님 강의 들었던게 큰 도움이 되었습니다. 꾸준히 조금씩이라도 문제 푸는게 도움이 되더라구요 행정법 함수민 선</t>
         </is>
       </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38539&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=73</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="55" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -20544,6 +23307,11 @@
           <t>5과목 공부에 대해 말씀드리면, 일단 영어는 베이스가 어느정도 있어서 계속 안하고 있다가 마지막 1년째에 비비안선생님 문법,구문독해,어휘강의를 들었습니다(어휘강의는 10회독). 비비안선생님은 시험에 나올 주제들을 여러번 반복해주셔서 잊어버리지 않게끔 도움을 주셨습니다. 국어는 문법과 한자 위주로 했었는데요, 신민숙 선생님의 문법 암기법과 한자성어 특강이 정말 좋았습니다. 최정선생님의 고전시가 특강도 좋았구요. 한국사는 제가 이해를 중요시해서 이중석선생님 올인원강의를 들었다가 암기도 강의로 해결해야할 것 같아서 이명호선생님 기본강의를 추가로 들었습니다. 두 분 다 각자의 분야에서 정말 훌륭한 선생님들이십니다. 행정법과 행정학은 너무 어려워서 울면서 공부했던 과목인데요, 먼저 행정법은 친절한 설명을 해주시는 강의를 듣고 싶어서 함수민 선생님 강의를 듣게 되었습니다. 함수민 선생님 교재는 다른 교재에 비해 두껍긴 했는데요, 그래도 그만큼 책이 친절하게 서술되어있어서 행정법을 어려워하는 제가 보기 정말 좋았습니다. ppt로 도식화도 잘 되어있어서 공부하기 편리했어요. 저는 기본강의 위주로 들었는데요, 강의는 10번씩(1~3배속), 책은 20회독 이상 본 것 같습니다</t>
         </is>
       </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38538&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=73</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="55" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
@@ -20582,6 +23350,11 @@
           <t>행정학 송상호 선생님 수업을 들었습니다. 군무원 시험도 함께 준비 중이었어서 군무원 행정학을 들었습니다. 개인적으로 행정학이 제일 어려웠는데 선생님 커리 따라가면서 계속 회독 하니까 자연스럽게 익힐 수 있었고 문제도 쉽게 풀 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38536&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=73</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="55" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -20616,6 +23389,11 @@
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38528&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=73</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="55" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
@@ -20650,6 +23428,11 @@
         </is>
       </c>
       <c r="H63" s="3" t="inlineStr"/>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38511&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=74</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="55" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -20684,6 +23467,11 @@
           <t>. 응시한 시험의 기본정보 ⓐ 응시한 시험 : 국가직 우정행정 (서울) ⓑ 응시한 직렬 : ⓒ 공부 기간 : 3년 ⓓ 본인만의 필기 합격 노하우 : 국어: 저는 독해에 자신감이 있었기 때문에 매일 독해감을 놓지않으려 고혜원 국어 하프모의고사를 많이 풀었습니다. 그리고 고득점을 맞기 위해서는 한자, 맞춤법 등 .. 어플을 통해 매일 매일 눈에 익히려고 노력을 해서 고득점을 받았던 것 같습니다. 영어: 단어를 매일매일 하려고 했고, 또 독해를 할 때 정확한 문장을 끊기에 더 신경을 써서 한 것 같습니다. 또 기출을 통해서 영어문법을 잊지 않기위해 노력한 것 같습니다 한국사: 한국사 또한 고종훈 모의고사를 통해서 매일매일 20문제씩 풀고, 틀리면 요약서를 찾아보는 등 최대한 한국사에 비중을 좁히려고 노력했습니다. 쉽게 시험이 나오는 것에 맞추어 사료, 절대 연도를 매일 보면서 잊지 않으려고 노력했습니다. 행정법: 행정법은 용어가 정말 중요하다고 생각합니다. 기각, 각하, 인용, 기속력...등등 법 용어에 익숙해지기 위해서 많이 노력을 했습니다. 모든 합격생들이 말하듯이 특히 행정법은 기출이 정말 중요합니다! 기출을 풀고 또 풀고, 요약서를 통해서 전 범위를 다 보</t>
         </is>
       </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38213&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=79</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="55" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
@@ -20714,6 +23502,11 @@
         </is>
       </c>
       <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37336&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="55" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -20748,6 +23541,11 @@
           <t>전부 찾아보시려면 좀 번거로우실 거에요. 행정학은 특히 생소한 문제가 한두 개 정도 나오는데 거기에 너무 치중하지 마시고 기출 빈도 순으로 중요하다고 생각하시고, 반복해서 풀어보세요. 공부하시다 보면 외워야 할 부분이 많이 나옵니다. 잘 기억이 나지 않는다면 포스트잇에 써서 잘 보이는 곳에 붙이고 외워보시는 건 어떨까요? 자신이 이해할 수 있는 방식으로 간단히 써서 여러 번 보세요.</t>
         </is>
       </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37288&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="55" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
@@ -20778,6 +23576,11 @@
         </is>
       </c>
       <c r="H67" s="3" t="inlineStr"/>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36908&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="55" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -20814,6 +23617,11 @@
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>안녕하세요. 처음 공무원 준비를 시작할 때에는 저의 계획이 정말 실현될 수 있을지 저 스스로도 의심하게 되고 막막하였지만 결국 제가 올해 합격을 하게 되었습니다. 저는 단기 합격을 위한 계획을 세웠습니다(5개월 정도). 과정을 이야기하자면, 먼저 저는 1월 말 정도부터 5급 1차 시험을 준비하였습니다. 피셋 공부와 헌법 1회독을 이 시기에 처음 하게 되었습니다. 하지만 1차 시험에서 떨어졌고, 그 충격으로 5월 8일까지 공부를 안하고 놀기만 했습니다. 어버이날이 지나고 더는 부모님께 손벌리기가 싫었고, 사기업에 종사하는 것보다는 국가를 위한 일을 하고자 하는 마음이 있었기 때문에 7급 공무원을 준비하게 되었습니다(진짜입니다). 다행히 1차 시험은 1월에 5급 시험을 준비했던 경험으로 4일 정도 공부하여 붙을 수 있었습니다. 이후 2차 시험을 위해 제가 먼저 준비를 시작했던 과목은 경제학이었습니다. 아무래도 이해가 필요한 과목이고 휘발성이 다른 암기과목들에 비해 낮다고 생각을 하였기 때문에 가장 먼저 준비를 했습니다. 경제학은 일단 처음 들을 때에는 당연히 이해가 잘 안되지만 저는 이해를 해야 넘어가는 스타일이라 조금 까다로웠습니다. 김종국 선생님의 강의를 들</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36756&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
         </is>
       </c>
     </row>
@@ -20846,6 +23654,11 @@
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36754&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="55" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -20880,6 +23693,11 @@
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36747&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="55" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
@@ -20918,6 +23736,11 @@
           <t>-공유하고 싶은 합격 꿀팁 필기합격을 할 수 있었던 제 방법에 대해서 설명해드리려고 합니다 이과생이어서 행정학이나 행정법을 공부할때 가장 어려움을 느꼈던 것 같습니다 아무래도 정답이 정해져 있는 수학 문제보다 전체적인 흐름과 암기가 동반되어야 하는 과목이기 때문에 처음에 적응하는데 시간이 오래 걸렸어요 꼼꼼하게 모든 부분을 심도있게 다 공부하려다보니 전체적인 흐름을 놓치는 경우가 있어서 정작 아는 내용은 많아도 시험에 적용하기가 더 어려웠던 것 같습니다 그래서 저는 해커스 강의를 수강하며 이 괴리감을 줄여나갔습니다 혼자서 기본서를 독파하기보다 송상호교수님이 기본이론 수업으로 가이드라인을 잡아주셔서 시험에 나오지않는 다른 부분을 보기보다 중요한 부분을 한번 더 볼 수 있었습니다 필기를 많이 하지않고 머리속에 한번더 넣고 반복하는 작업을 통해 행정학이라는 과목에 대한 두려움을 줄일 수 있었다고 생각합니다 그리고 필기합격의 평균점수를 높여준 고마운 과목인 국어는 신민숙 교수님의 수업 덕분이라고 생각합니다 교수님만의 유쾌한 에너지 덕분에 수업 내용이 전혀 지루하지않고 오히려 재밌게 공부를 할 수 있었다고 생각해요 특히 어법이 어려웠는데 그 어법을 간결하고도 기억하기</t>
         </is>
       </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36607&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=95</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="55" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -20956,6 +23779,11 @@
           <t>공무원 시험은 분량이 방대하고, 행정법, 행정학, 한국사 등 암기과목이 많습니다. 그렇기 때문에 몇십편씩 되는 인강을 인내심 갖고 잘 듣는 것도 중요합니다. 특히 저는 인강을 한꺼번에 다 들은 다음에 문제풀이로 들어가는 것은 그다지 효과적이지 않은 전략이라는 것을 깨달았습니다. 기본서와 기출문제집을 동시에 갖춘 다음 인강을 특정 분량만큼 들으면, 즉시 배운 분량을 복습하고, 기본서에 실린 문제와 기출문제집의 해당 분량만큼 푼 다음 다음 인강으로 넘어가는 편이, 인강 여러 편을 한꺼번에 듣는 것보다 더 머리에 리프레시도 되고 배운 분량도 더 기억에 잘 남는다고 느꼈습니다.</t>
         </is>
       </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36604&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=95</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="55" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
@@ -20992,6 +23820,11 @@
       <c r="H73" s="3" t="inlineStr">
         <is>
           <t>-수강한 선생님 &amp; 강의 &amp; 교재 추천 저는 신민숙 교수님의 수업을 제일 좋아했어요  항상 공부의 시작은 국어였습니다 국어 강의는 거의 다 들었던 것 같아요 신민숙 교수님의 파이팅 넘치는 수업이 참 재미있었고 귀에 쏙쏙 들어오는 암기법은 물론  자연스럽게 외울 수 있게 반복해주셔서 시험에서 좋은 결과를 얻을 수 있었다고 생각합니다 토익도 해커스덕분에 900을 넘는 점수를 만들 수 있었기 때문에 해커스는 제게 특히나 이미지가 좋았고  결과적으로도 좋았다고 생각합니다 김송희 교수님의 하프가 매일매일 영어 감각을 깨우는데 큰 도움이 되었습니다 공무원 영어는 토익과 결이 다르기 때문에 그 감을 잡는 것이 중요했던 것 같아요 그리고 처음에 시작할때 행정학이 가장 두려웠는데 송상호 교수님의 기본 이론 수업 덕분에 행정학의 방대함 속에서 기준을 잘 잡을 수 있었다고 생각합니다</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36517&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=95</t>
         </is>
       </c>
     </row>
@@ -21024,6 +23857,11 @@
       <c r="F74" s="2" t="inlineStr"/>
       <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36394&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=98</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="55" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
@@ -21062,6 +23900,11 @@
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36100&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=107</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="55" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -21096,6 +23939,11 @@
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36024&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=110</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="55" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
@@ -21134,6 +23982,11 @@
           <t>-본인만의 필수과목or선택과목 학습법: 국어 95점 국어는 신민숙 선생님 커리를 따라갔습니다.  강의 의존형이라 어법, 문학, 기출, 실전동형 거의 커리 다 따라갔습니다.  비문학 분야 비중이 높아진다고 해서 시중에서 파는 비문학 문제집이나 비문학 특강 같은 것들 많이 들었습니다.  영어 95점 영어는 처음 커리는 김송희 선생님과 비비안 선생님 문법 강의를 들었습니다. 독해는 따로 하프 모의고사나 실전 동형 모의고사를 많이 풀고 강의는 듣지 않았습니다.  단어가 중요하다고 생각해서 해커스 보카 계속 돌렸습니다. 비비안 선생님이 동의어 뽑아 주시는 특강이나 문법 특강 해주셨는데 그게 많이 도움이 된 것 같습니다.  한국사 100점 한국사는 이중석 선생님 강의를 들었습니다. 이론 강의가 다른 한국사 선생님에 비해 길긴 한데, 그만큼 기억에도 오래 남고 재미있게 설명해주셔서 저는 오히려 좋았습니다. 이론강의 3개, 단원별 기출 강의, 실전 동형 강의 이렇게 커리 따라 갔는데, 문제 해설해주실 때 처음 가르치는 것처럼? 설명해주셔서 그게 좋았습니다. 아는 부분은 아 이렇구나 이러고 넘어가는데, 생소한 부분은 다시 필기노트 짚고 숙지할 수 있었습니다.  행정법총론 9</t>
         </is>
       </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35962&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=112</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="55" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -21168,6 +24021,11 @@
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35957&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=112</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="55" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
@@ -21198,6 +24056,11 @@
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35947&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=113</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="55" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -21232,6 +24095,11 @@
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35895&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=115</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="55" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
@@ -21266,6 +24134,11 @@
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35768&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=119</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="55" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -21296,6 +24169,11 @@
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=121</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="55" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
@@ -21330,6 +24208,11 @@
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr"/>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=123</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="55" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -21364,6 +24247,11 @@
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35658&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=124</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="55" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
@@ -21400,6 +24288,11 @@
       <c r="H85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">-수험기간: 2022.01 ~2023.04  -기본베이스: 영어(영어영문학과), 한국사(순경합격),  -하루루틴 기상: 일어나고 싶은 시간 취침: 12시에서 1시사이 공부하는 총시간이 중요하다기보다는 공부를 얼마만큼 집중할 수 있는지가 더 중요하다고 생각해서 하루에 7~8시간정도 집중하는 시간을 갖도록 노력했습니다. 하지만 영어단어나 다른 어려운 어휘가 나올 수도 있기 때문에 어려운 단어는 최소 300개이상 보고가려 노력했고 국어도 사자성어는 꼭 맞히려 하루에 15개씩은 보도록 노력했습니다.  -과목학습 국어 95점 (신민숙 선생님): 최근에 국어의 출제경향이 많이 변해서 어려운 어법이나 어휘를 많이 물어보지는 않을 것으로 예상했습니다. 그래서 최대한 문학작품이나 비문학에서 틀리지 않는 방향으로 90점정도만 맞으려 노력했습니다.  또한 한자문제는 투입되는 공부량에 비해서 맞힐 가능성이 다소 적다고 생각했고 커트라인이 90점정도에 형성이 되는 것을 감안하면 한자문제는 틀려도 생각했습니다. 하지만 사자성어 문제는 반드시 맞혀야 되는 문제라 생각했었고 이 방법이 주요했었습니다.  영어 95점 (비비안 선생님): 사실 영어에 대해서는 특별한 방법이 많이 없습니다. </t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35515&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=127</t>
         </is>
       </c>
     </row>
@@ -21436,6 +24329,11 @@
           <t>2. 하루 루틴 저는 체력과 멘탈이 시험을 좌우한다고 믿었기 때문에 평일엔 빠지지 않고 스카 바로 위층에 있는 요가를 다녔습니다. (요가 시간은 씻는 시간 포함 오전 9시-10시반 활용했습니다.) 기상 시간은 7시 반정도였고, 스카 도착시간은 8시 반으로, 요가 가기 직전 30분 동안 영어단어를 외웠습니다. 영어단어를 눈으로만 외우면 휘발이 빠르다고 생각해서 귀에 익히는 용도로 비비안쌤의 영단어 인강을 적극 활용했고, 유사 어휘를 차곡차곡 모아 외웠습니다. 잘 외워지지 않는 단어는 포스트잇을 활용해서 벽에 붙여두고 틈틈히 보며 외웠습니다. 운동이 끝나고 본격적으로 11시부터 공부를 시작했는데, 공부 흐름이 끊기는게 싫어서 12시나 1시에 점심을 먹지 않고 4시 반까지 스트레이트로 공부했습니다. 과목은 수시로 바뀌어서 특정하기 어렵기는 하지만, 공부 초반에는 주로 국어/한국사를 했고, 후반부에는 행정학/행정법을 하려고 노력했습니다. (*가장 집중도가 높은 시간대라고 생각했기 때문입니다) 4시 반부터 약 두 시간 동안은 걸어서 15분 거리에 있는 집에 가서 편하게 밥도 먹고 쉬어줬습니다. 저는 책상 앞에 앉아 집중해 공부하는 시간 외에는 책을 잘 보지 않았습니다</t>
         </is>
       </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35248&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=134</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="55" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
@@ -21470,6 +24368,11 @@
       </c>
       <c r="G87" s="3" t="inlineStr"/>
       <c r="H87" s="3" t="inlineStr"/>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35239&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=134</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="55" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -21504,6 +24407,11 @@
           <t>1.기본 베이스 저는 국문학 전공이라 국어 어법은 크게 어려울 것 없었고, 한능검1급, 토익 800점대 점수이긴 했지만 문법이 너무 약해서 기본강의 열심히 들었습니다. 국영한은 어느정도 베이스가 있었는데 행정학, 행정법은 정말 아무것도 모르는상태로 시작해서 처음에 좀 힘들었어요. 특히 행정법이 기본적 법률용어를 모르니까 어렵더라구요.</t>
         </is>
       </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35189&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=136</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="55" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
@@ -21534,6 +24442,11 @@
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr"/>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34959&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=140</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="55" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -21568,6 +24481,11 @@
           <t>자신 없었던 과목: 2018년도에 세무직 공무원에 합격 했을 때는 선택과목을 행정학 사회를 선택해서 수월하게                    공무원 시험에 합격 했었는데 2025년에는 회계학 세법이 선택과목으로 고정 되어 많은 어려움이                     있었습니다. 회계학 공부 할 때 기본강의를 듣고 문제풀이를 하였고 세법도 기본강의 듣고                    문제 풀이를 하였습니다. 회계하는 개념이 어려워서 도무지 이해하기가 어려웠습니다. 그리고                    세법도 암기사항이 너무 방대하고 이해도 잘 되지 않았습니다.</t>
         </is>
       </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40455&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=40</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="55" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
@@ -21602,6 +24520,11 @@
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr"/>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41017&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=26</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="55" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -21632,6 +24555,11 @@
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39671&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="55" customHeight="1">
       <c r="A93" s="3" t="inlineStr">
@@ -21666,6 +24594,11 @@
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr"/>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39652&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="55" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -21702,6 +24635,11 @@
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>14시~18시 : 행정학, 행정법 기본이론반, 동형모의고사반, 교육학 수업(7~8월)</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39642&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -21738,6 +24676,11 @@
           <t>공부순서는 국어, 행정학, 행정법 순으로 순차대로 인강 3개씩 보면서 공부했었어요 한개 과목 끝나면 꼭</t>
         </is>
       </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36610&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=94</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="55" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -21772,6 +24715,11 @@
           <t>그러나 행정학과 행정법은 타사 인강을 들었지만 잘 이해가 되지 않고 공부 방식이 흐지부지하게 되는 생활이 좀 많았습니다.</t>
         </is>
       </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41382&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="55" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
@@ -21802,6 +24750,11 @@
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr"/>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38148&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=81</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="55" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -21836,6 +24789,11 @@
           <t>결국 저는 수학적인 머리가 컸고, 문과적인 머리는 별볼일이 없는 단순 무식한 전형적인 이공계형 수학형 머리분야서 빛난다는 것을 해커스사 강의로 8282 뜨게 된것이에요. 흔히 들 이런얘기 하시지오. 안될꺼 빨리 버려라 네  여러분 행정학은 여성암기왕과 남성 분석왕이 즐비합니다. 제 노력과 성실로는 이런분 제끼기 하늘 별따기였습니다. 그러나 해커스공무원강의를 듣고 일행은 일반행정은 단념하는 것이 정신건강에 좋다는 생각을 하였고, 책을 중고나 새책을 사는 경우도 생각날까봐 행정학 행정법 다 찢는 다는 자세로 책 곁에 두지도 않았습니다.</t>
         </is>
       </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35821&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=117</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="55" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
@@ -21870,6 +24828,11 @@
           <t>결국 저는 수학적인 머리가 컸고, 문과적인 머리는 별볼일이 없는 단순 무식한 전형적인 이공계형 수학형 머리분야서 빛난다는 것을 해커스사 강의로 8282 뜨게 된것이에요. 흔히 들 이런얘기 하시지오. 안될꺼 빨리 버려라 네  여러분 행정학은 여성암기왕과 남성 분석왕이 즐비합니다. 제 노력과 성실로는 이런분 제끼기 하늘 별따기였습니다. 그러나 해커스공무원강의를 듣고 일행은 일반행정은 단념하는 것이 정신건강에 좋다는 생각을 하였고, 책을 중고나 새책을 사는 경우도 생각날까봐 행정학 행정법 다 찢는 다는 자세로 책 곁에 두지도 않았습니다.</t>
         </is>
       </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35820&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=117</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="55" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -21900,9 +24863,14 @@
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41922&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H100"/>
+  <autoFilter ref="A1:I100"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>